--- a/artfynd/A 53969-2024 artfynd.xlsx
+++ b/artfynd/A 53969-2024 artfynd.xlsx
@@ -1894,10 +1894,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>125231779</v>
+        <v>125227661</v>
       </c>
       <c r="B13" t="n">
-        <v>79920</v>
+        <v>98101</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1906,30 +1906,35 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6462</v>
+        <v>220787</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="J13" t="inlineStr"/>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
       <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
@@ -1937,10 +1942,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>745323</v>
+        <v>745280</v>
       </c>
       <c r="R13" t="n">
-        <v>7107772</v>
+        <v>7107827</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1988,22 +1993,22 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Patrik Nygren</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Patrik Nygren</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>125227661</v>
+        <v>125231779</v>
       </c>
       <c r="B14" t="n">
-        <v>98101</v>
+        <v>79920</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2012,35 +2017,30 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>220787</v>
+        <v>6462</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="J14" t="inlineStr"/>
       <c r="K14" t="inlineStr"/>
-      <c r="L14" t="inlineStr"/>
       <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
@@ -2048,10 +2048,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>745280</v>
+        <v>745323</v>
       </c>
       <c r="R14" t="n">
-        <v>7107827</v>
+        <v>7107772</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2099,19 +2099,19 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Patrik Nygren</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Patrik Nygren</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>125226783</v>
+        <v>125231342</v>
       </c>
       <c r="B15" t="n">
         <v>98101</v>
@@ -2145,11 +2145,7 @@
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="J15" t="inlineStr"/>
       <c r="K15" t="inlineStr"/>
       <c r="L15" t="inlineStr"/>
       <c r="N15" t="inlineStr"/>
@@ -2159,10 +2155,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>745294</v>
+        <v>745267</v>
       </c>
       <c r="R15" t="n">
-        <v>7107772</v>
+        <v>7107907</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2210,19 +2206,19 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Patrik Nygren</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Patrik Nygren</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>125231342</v>
+        <v>125226783</v>
       </c>
       <c r="B16" t="n">
         <v>98101</v>
@@ -2256,7 +2252,11 @@
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
-      <c r="J16" t="inlineStr"/>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K16" t="inlineStr"/>
       <c r="L16" t="inlineStr"/>
       <c r="N16" t="inlineStr"/>
@@ -2266,10 +2266,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>745267</v>
+        <v>745294</v>
       </c>
       <c r="R16" t="n">
-        <v>7107907</v>
+        <v>7107772</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2317,12 +2317,12 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Patrik Nygren</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Patrik Nygren</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
@@ -2768,10 +2768,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>125231983</v>
+        <v>125222083</v>
       </c>
       <c r="B21" t="n">
-        <v>98101</v>
+        <v>91361</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2784,27 +2784,30 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>220787</v>
+        <v>2062</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ulltickeporing</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Skeletocutis brevispora</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
-      <c r="J21" t="inlineStr"/>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K21" t="inlineStr"/>
-      <c r="L21" t="inlineStr"/>
       <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
@@ -2812,10 +2815,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>745279</v>
+        <v>745262</v>
       </c>
       <c r="R21" t="n">
-        <v>7107767</v>
+        <v>7107946</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2863,19 +2866,19 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Patrik Nygren</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Patrik Nygren</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>125231838</v>
+        <v>125227728</v>
       </c>
       <c r="B22" t="n">
         <v>98101</v>
@@ -2909,7 +2912,11 @@
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
-      <c r="J22" t="inlineStr"/>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K22" t="inlineStr"/>
       <c r="L22" t="inlineStr"/>
       <c r="N22" t="inlineStr"/>
@@ -2919,10 +2926,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>745310</v>
+        <v>745279</v>
       </c>
       <c r="R22" t="n">
-        <v>7107765</v>
+        <v>7107831</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2970,22 +2977,22 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Patrik Nygren</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Patrik Nygren</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>125222083</v>
+        <v>125228007</v>
       </c>
       <c r="B23" t="n">
-        <v>91361</v>
+        <v>57529</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2994,34 +3001,35 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>2062</v>
+        <v>100049</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Ulltickeporing</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Skeletocutis brevispora</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
-      <c r="J23" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
       <c r="K23" t="inlineStr"/>
+      <c r="L23" t="inlineStr"/>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
@@ -3029,10 +3037,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>745262</v>
+        <v>745249</v>
       </c>
       <c r="R23" t="n">
-        <v>7107946</v>
+        <v>7107940</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3067,13 +3075,17 @@
           <t>2025-05-18</t>
         </is>
       </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>hackat hål i gran</t>
+        </is>
+      </c>
       <c r="AD23" t="b">
         <v>0</v>
       </c>
       <c r="AE23" t="b">
         <v>0</v>
       </c>
-      <c r="AF23" t="inlineStr"/>
       <c r="AG23" t="b">
         <v>0</v>
       </c>
@@ -3092,7 +3104,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>125227728</v>
+        <v>125231983</v>
       </c>
       <c r="B24" t="n">
         <v>98101</v>
@@ -3126,11 +3138,7 @@
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
-      <c r="J24" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="J24" t="inlineStr"/>
       <c r="K24" t="inlineStr"/>
       <c r="L24" t="inlineStr"/>
       <c r="N24" t="inlineStr"/>
@@ -3143,7 +3151,7 @@
         <v>745279</v>
       </c>
       <c r="R24" t="n">
-        <v>7107831</v>
+        <v>7107767</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3191,22 +3199,22 @@
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Patrik Nygren</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Patrik Nygren</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>125228007</v>
+        <v>125231838</v>
       </c>
       <c r="B25" t="n">
-        <v>57529</v>
+        <v>98101</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3215,35 +3223,31 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
+      <c r="J25" t="inlineStr"/>
       <c r="K25" t="inlineStr"/>
       <c r="L25" t="inlineStr"/>
-      <c r="M25" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
@@ -3251,10 +3255,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>745249</v>
+        <v>745310</v>
       </c>
       <c r="R25" t="n">
-        <v>7107940</v>
+        <v>7107765</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3289,29 +3293,25 @@
           <t>2025-05-18</t>
         </is>
       </c>
-      <c r="AC25" t="inlineStr">
-        <is>
-          <t>hackat hål i gran</t>
-        </is>
-      </c>
       <c r="AD25" t="b">
         <v>0</v>
       </c>
       <c r="AE25" t="b">
         <v>0</v>
       </c>
+      <c r="AF25" t="inlineStr"/>
       <c r="AG25" t="b">
         <v>0</v>
       </c>
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Patrik Nygren</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Patrik Nygren</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
@@ -3974,10 +3974,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>125232283</v>
+        <v>125223807</v>
       </c>
       <c r="B32" t="n">
-        <v>57883</v>
+        <v>98101</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -3986,31 +3986,35 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>103015</v>
+        <v>220787</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K32" t="inlineStr"/>
       <c r="L32" t="inlineStr"/>
-      <c r="M32" t="inlineStr"/>
       <c r="N32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
@@ -4018,13 +4022,13 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>745254</v>
+        <v>745315</v>
       </c>
       <c r="R32" t="n">
-        <v>7107972</v>
+        <v>7107851</v>
       </c>
       <c r="S32" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -4056,34 +4060,40 @@
           <t>2025-05-18</t>
         </is>
       </c>
+      <c r="AC32" t="inlineStr">
+        <is>
+          <t>Rikligt med bladrosetter!</t>
+        </is>
+      </c>
       <c r="AD32" t="b">
         <v>0</v>
       </c>
       <c r="AE32" t="b">
         <v>0</v>
       </c>
+      <c r="AF32" t="inlineStr"/>
       <c r="AG32" t="b">
         <v>0</v>
       </c>
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Patrik Nygren</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Patrik Nygren</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>125223807</v>
+        <v>125226206</v>
       </c>
       <c r="B33" t="n">
-        <v>98101</v>
+        <v>91012</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4092,35 +4102,34 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
       <c r="J33" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K33" t="inlineStr"/>
-      <c r="L33" t="inlineStr"/>
       <c r="N33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
@@ -4128,10 +4137,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>745315</v>
+        <v>745327</v>
       </c>
       <c r="R33" t="n">
-        <v>7107851</v>
+        <v>7107827</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4164,11 +4173,6 @@
       <c r="AA33" t="inlineStr">
         <is>
           <t>2025-05-18</t>
-        </is>
-      </c>
-      <c r="AC33" t="inlineStr">
-        <is>
-          <t>Rikligt med bladrosetter!</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4196,10 +4200,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>125226206</v>
+        <v>125232283</v>
       </c>
       <c r="B34" t="n">
-        <v>91012</v>
+        <v>57883</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4208,34 +4212,31 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>1202</v>
+        <v>103015</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
-      <c r="J34" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
       <c r="K34" t="inlineStr"/>
+      <c r="L34" t="inlineStr"/>
+      <c r="M34" t="inlineStr"/>
       <c r="N34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
@@ -4243,13 +4244,13 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>745327</v>
+        <v>745254</v>
       </c>
       <c r="R34" t="n">
-        <v>7107827</v>
+        <v>7107972</v>
       </c>
       <c r="S34" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4287,19 +4288,18 @@
       <c r="AE34" t="b">
         <v>0</v>
       </c>
-      <c r="AF34" t="inlineStr"/>
       <c r="AG34" t="b">
         <v>0</v>
       </c>
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Patrik Nygren</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Patrik Nygren</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>

--- a/artfynd/A 53969-2024 artfynd.xlsx
+++ b/artfynd/A 53969-2024 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>125223203</v>
+        <v>125225982</v>
       </c>
       <c r="B2" t="n">
         <v>98101</v>
@@ -723,10 +723,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>745293</v>
+        <v>745327</v>
       </c>
       <c r="R2" t="n">
-        <v>7107855</v>
+        <v>7107834</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -897,10 +897,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>125227847</v>
+        <v>125222055</v>
       </c>
       <c r="B4" t="n">
-        <v>57529</v>
+        <v>91012</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -913,31 +913,30 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100049</v>
+        <v>1202</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -945,10 +944,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>745285</v>
+        <v>745262</v>
       </c>
       <c r="R4" t="n">
-        <v>7107862</v>
+        <v>7107948</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -983,17 +982,13 @@
           <t>2025-05-18</t>
         </is>
       </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>hack i död gran</t>
-        </is>
-      </c>
       <c r="AD4" t="b">
         <v>0</v>
       </c>
       <c r="AE4" t="b">
         <v>0</v>
       </c>
+      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
@@ -1012,10 +1007,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>125227327</v>
+        <v>125232181</v>
       </c>
       <c r="B5" t="n">
-        <v>98101</v>
+        <v>57529</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1024,35 +1019,31 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr"/>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1060,10 +1051,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>745280</v>
+        <v>745227</v>
       </c>
       <c r="R5" t="n">
-        <v>7107795</v>
+        <v>7107774</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1104,29 +1095,28 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
-      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Patrik Nygren</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Patrik Nygren</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>125231105</v>
+        <v>125231618</v>
       </c>
       <c r="B6" t="n">
-        <v>79920</v>
+        <v>79795</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1139,21 +1129,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6462</v>
+        <v>6456</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1166,10 +1156,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>745259</v>
+        <v>745381</v>
       </c>
       <c r="R6" t="n">
-        <v>7107964</v>
+        <v>7107841</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1229,10 +1219,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>125231658</v>
+        <v>125227847</v>
       </c>
       <c r="B7" t="n">
-        <v>90977</v>
+        <v>57529</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1241,30 +1231,35 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>5447</v>
+        <v>100049</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
@@ -1272,10 +1267,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>745405</v>
+        <v>745285</v>
       </c>
       <c r="R7" t="n">
-        <v>7107837</v>
+        <v>7107862</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1310,32 +1305,36 @@
           <t>2025-05-18</t>
         </is>
       </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>hack i död gran</t>
+        </is>
+      </c>
       <c r="AD7" t="b">
         <v>0</v>
       </c>
       <c r="AE7" t="b">
         <v>0</v>
       </c>
-      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Patrik Nygren</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Patrik Nygren</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>125222545</v>
+        <v>125227446</v>
       </c>
       <c r="B8" t="n">
         <v>98101</v>
@@ -1383,10 +1382,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>745294</v>
+        <v>745280</v>
       </c>
       <c r="R8" t="n">
-        <v>7107877</v>
+        <v>7107802</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1446,7 +1445,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>125223425</v>
+        <v>125231838</v>
       </c>
       <c r="B9" t="n">
         <v>98101</v>
@@ -1480,11 +1479,7 @@
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="J9" t="inlineStr"/>
       <c r="K9" t="inlineStr"/>
       <c r="L9" t="inlineStr"/>
       <c r="N9" t="inlineStr"/>
@@ -1494,10 +1489,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>745298</v>
+        <v>745310</v>
       </c>
       <c r="R9" t="n">
-        <v>7107856</v>
+        <v>7107765</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1545,19 +1540,19 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Patrik Nygren</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Patrik Nygren</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>125225490</v>
+        <v>125222083</v>
       </c>
       <c r="B10" t="n">
         <v>91361</v>
@@ -1604,10 +1599,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>745321</v>
+        <v>745262</v>
       </c>
       <c r="R10" t="n">
-        <v>7107841</v>
+        <v>7107946</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1667,7 +1662,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>125222017</v>
+        <v>125231309</v>
       </c>
       <c r="B11" t="n">
         <v>98101</v>
@@ -1701,11 +1696,7 @@
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="J11" t="inlineStr"/>
       <c r="K11" t="inlineStr"/>
       <c r="L11" t="inlineStr"/>
       <c r="N11" t="inlineStr"/>
@@ -1715,10 +1706,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>745243</v>
+        <v>745268</v>
       </c>
       <c r="R11" t="n">
-        <v>7107977</v>
+        <v>7107926</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1766,22 +1757,22 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Patrik Nygren</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Patrik Nygren</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>125222404</v>
+        <v>125226206</v>
       </c>
       <c r="B12" t="n">
-        <v>98101</v>
+        <v>91012</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1790,35 +1781,34 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
       <c r="J12" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K12" t="inlineStr"/>
-      <c r="L12" t="inlineStr"/>
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
@@ -1826,10 +1816,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>745290</v>
+        <v>745327</v>
       </c>
       <c r="R12" t="n">
-        <v>7107886</v>
+        <v>7107827</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1862,11 +1852,6 @@
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-05-18</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>några kvadratmeter med bladrosetter</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1894,7 +1879,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>125227661</v>
+        <v>125223203</v>
       </c>
       <c r="B13" t="n">
         <v>98101</v>
@@ -1942,10 +1927,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>745280</v>
+        <v>745293</v>
       </c>
       <c r="R13" t="n">
-        <v>7107827</v>
+        <v>7107855</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2005,10 +1990,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>125231779</v>
+        <v>125222017</v>
       </c>
       <c r="B14" t="n">
-        <v>79920</v>
+        <v>98101</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2017,30 +2002,35 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6462</v>
+        <v>220787</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
-      <c r="J14" t="inlineStr"/>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
       <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
@@ -2048,10 +2038,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>745323</v>
+        <v>745243</v>
       </c>
       <c r="R14" t="n">
-        <v>7107772</v>
+        <v>7107977</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2099,22 +2089,22 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Patrik Nygren</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Patrik Nygren</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>125231342</v>
+        <v>125228007</v>
       </c>
       <c r="B15" t="n">
-        <v>98101</v>
+        <v>57529</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2123,31 +2113,35 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
-      <c r="J15" t="inlineStr"/>
       <c r="K15" t="inlineStr"/>
       <c r="L15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
@@ -2155,10 +2149,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>745267</v>
+        <v>745249</v>
       </c>
       <c r="R15" t="n">
-        <v>7107907</v>
+        <v>7107940</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2193,35 +2187,39 @@
           <t>2025-05-18</t>
         </is>
       </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>hackat hål i gran</t>
+        </is>
+      </c>
       <c r="AD15" t="b">
         <v>0</v>
       </c>
       <c r="AE15" t="b">
         <v>0</v>
       </c>
-      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
       </c>
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Patrik Nygren</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Patrik Nygren</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>125226783</v>
+        <v>125231658</v>
       </c>
       <c r="B16" t="n">
-        <v>98101</v>
+        <v>90977</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2230,35 +2228,30 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>220787</v>
+        <v>5447</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
-      <c r="J16" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="J16" t="inlineStr"/>
       <c r="K16" t="inlineStr"/>
-      <c r="L16" t="inlineStr"/>
       <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
@@ -2266,10 +2259,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>745294</v>
+        <v>745405</v>
       </c>
       <c r="R16" t="n">
-        <v>7107772</v>
+        <v>7107837</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2317,22 +2310,22 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Patrik Nygren</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Patrik Nygren</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>125228040</v>
+        <v>125232195</v>
       </c>
       <c r="B17" t="n">
-        <v>98101</v>
+        <v>79891</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2341,35 +2334,30 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
-      <c r="J17" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="J17" t="inlineStr"/>
       <c r="K17" t="inlineStr"/>
-      <c r="L17" t="inlineStr"/>
       <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
@@ -2377,10 +2365,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>745249</v>
+        <v>745215</v>
       </c>
       <c r="R17" t="n">
-        <v>7107940</v>
+        <v>7107730</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2415,11 +2403,6 @@
           <t>2025-05-18</t>
         </is>
       </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>rikligt med bladrosetter!</t>
-        </is>
-      </c>
       <c r="AD17" t="b">
         <v>0</v>
       </c>
@@ -2433,19 +2416,19 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Patrik Nygren</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Patrik Nygren</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>125222055</v>
+        <v>125225686</v>
       </c>
       <c r="B18" t="n">
         <v>91012</v>
@@ -2492,10 +2475,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>745262</v>
+        <v>745321</v>
       </c>
       <c r="R18" t="n">
-        <v>7107948</v>
+        <v>7107841</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2555,7 +2538,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>125231249</v>
+        <v>125223590</v>
       </c>
       <c r="B19" t="n">
         <v>98101</v>
@@ -2589,7 +2572,11 @@
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
-      <c r="J19" t="inlineStr"/>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K19" t="inlineStr"/>
       <c r="L19" t="inlineStr"/>
       <c r="N19" t="inlineStr"/>
@@ -2599,10 +2586,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>745260</v>
+        <v>745299</v>
       </c>
       <c r="R19" t="n">
-        <v>7107948</v>
+        <v>7107851</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2650,22 +2637,22 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Patrik Nygren</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Patrik Nygren</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>125232181</v>
+        <v>125230982</v>
       </c>
       <c r="B20" t="n">
-        <v>57529</v>
+        <v>98101</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2674,31 +2661,31 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
+      <c r="J20" t="inlineStr"/>
       <c r="K20" t="inlineStr"/>
       <c r="L20" t="inlineStr"/>
-      <c r="M20" t="inlineStr"/>
       <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
@@ -2706,10 +2693,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>745227</v>
+        <v>745259</v>
       </c>
       <c r="R20" t="n">
-        <v>7107774</v>
+        <v>7107964</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2750,6 +2737,7 @@
       <c r="AE20" t="b">
         <v>0</v>
       </c>
+      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
       </c>
@@ -2768,10 +2756,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>125222083</v>
+        <v>125222288</v>
       </c>
       <c r="B21" t="n">
-        <v>91361</v>
+        <v>98101</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2784,30 +2772,31 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>2062</v>
+        <v>220787</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Ulltickeporing</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Skeletocutis brevispora</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
       <c r="J21" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K21" t="inlineStr"/>
+      <c r="L21" t="inlineStr"/>
       <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
@@ -2815,10 +2804,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>745262</v>
+        <v>745266</v>
       </c>
       <c r="R21" t="n">
-        <v>7107946</v>
+        <v>7107910</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2878,10 +2867,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>125227728</v>
+        <v>125222246</v>
       </c>
       <c r="B22" t="n">
-        <v>98101</v>
+        <v>91012</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2890,35 +2879,34 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
       <c r="J22" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K22" t="inlineStr"/>
-      <c r="L22" t="inlineStr"/>
       <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
@@ -2926,10 +2914,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>745279</v>
+        <v>745262</v>
       </c>
       <c r="R22" t="n">
-        <v>7107831</v>
+        <v>7107944</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2989,10 +2977,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>125228007</v>
+        <v>125232024</v>
       </c>
       <c r="B23" t="n">
-        <v>57529</v>
+        <v>91012</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3005,31 +2993,26 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>100049</v>
+        <v>1202</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
+      <c r="J23" t="inlineStr"/>
       <c r="K23" t="inlineStr"/>
-      <c r="L23" t="inlineStr"/>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
@@ -3037,10 +3020,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>745249</v>
+        <v>745288</v>
       </c>
       <c r="R23" t="n">
-        <v>7107940</v>
+        <v>7107786</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3075,36 +3058,32 @@
           <t>2025-05-18</t>
         </is>
       </c>
-      <c r="AC23" t="inlineStr">
-        <is>
-          <t>hackat hål i gran</t>
-        </is>
-      </c>
       <c r="AD23" t="b">
         <v>0</v>
       </c>
       <c r="AE23" t="b">
         <v>0</v>
       </c>
+      <c r="AF23" t="inlineStr"/>
       <c r="AG23" t="b">
         <v>0</v>
       </c>
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Patrik Nygren</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Patrik Nygren</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>125231983</v>
+        <v>125223425</v>
       </c>
       <c r="B24" t="n">
         <v>98101</v>
@@ -3138,7 +3117,11 @@
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
-      <c r="J24" t="inlineStr"/>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K24" t="inlineStr"/>
       <c r="L24" t="inlineStr"/>
       <c r="N24" t="inlineStr"/>
@@ -3148,10 +3131,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>745279</v>
+        <v>745298</v>
       </c>
       <c r="R24" t="n">
-        <v>7107767</v>
+        <v>7107856</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3199,19 +3182,19 @@
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Patrik Nygren</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Patrik Nygren</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>125231838</v>
+        <v>125231888</v>
       </c>
       <c r="B25" t="n">
         <v>98101</v>
@@ -3255,10 +3238,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>745310</v>
+        <v>745297</v>
       </c>
       <c r="R25" t="n">
-        <v>7107765</v>
+        <v>7107757</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3318,10 +3301,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>125222361</v>
+        <v>125232283</v>
       </c>
       <c r="B26" t="n">
-        <v>98101</v>
+        <v>57883</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3330,35 +3313,31 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>220787</v>
+        <v>103015</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
-      <c r="J26" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
       <c r="K26" t="inlineStr"/>
       <c r="L26" t="inlineStr"/>
+      <c r="M26" t="inlineStr"/>
       <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
@@ -3366,13 +3345,13 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>745280</v>
+        <v>745254</v>
       </c>
       <c r="R26" t="n">
-        <v>7107886</v>
+        <v>7107972</v>
       </c>
       <c r="S26" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3410,26 +3389,25 @@
       <c r="AE26" t="b">
         <v>0</v>
       </c>
-      <c r="AF26" t="inlineStr"/>
       <c r="AG26" t="b">
         <v>0</v>
       </c>
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Patrik Nygren</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Patrik Nygren</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>125222754</v>
+        <v>125231983</v>
       </c>
       <c r="B27" t="n">
         <v>98101</v>
@@ -3463,11 +3441,7 @@
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
-      <c r="J27" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="J27" t="inlineStr"/>
       <c r="K27" t="inlineStr"/>
       <c r="L27" t="inlineStr"/>
       <c r="N27" t="inlineStr"/>
@@ -3477,10 +3451,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>745306</v>
+        <v>745279</v>
       </c>
       <c r="R27" t="n">
-        <v>7107877</v>
+        <v>7107767</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3528,22 +3502,22 @@
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Patrik Nygren</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Patrik Nygren</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>125231464</v>
+        <v>125231948</v>
       </c>
       <c r="B28" t="n">
-        <v>79795</v>
+        <v>98101</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3552,30 +3526,31 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6456</v>
+        <v>220787</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
       <c r="J28" t="inlineStr"/>
       <c r="K28" t="inlineStr"/>
+      <c r="L28" t="inlineStr"/>
       <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
@@ -3583,10 +3558,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>745287</v>
+        <v>745279</v>
       </c>
       <c r="R28" t="n">
-        <v>7107886</v>
+        <v>7107754</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3646,10 +3621,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>125230982</v>
+        <v>125231696</v>
       </c>
       <c r="B29" t="n">
-        <v>98101</v>
+        <v>98122</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3658,25 +3633,25 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>220787</v>
+        <v>221952</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3690,10 +3665,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>745259</v>
+        <v>745356</v>
       </c>
       <c r="R29" t="n">
-        <v>7107964</v>
+        <v>7107793</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3753,7 +3728,7 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>125225982</v>
+        <v>125227901</v>
       </c>
       <c r="B30" t="n">
         <v>98101</v>
@@ -3801,10 +3776,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>745327</v>
+        <v>745280</v>
       </c>
       <c r="R30" t="n">
-        <v>7107834</v>
+        <v>7107886</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3864,10 +3839,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>125225686</v>
+        <v>125222545</v>
       </c>
       <c r="B31" t="n">
-        <v>91012</v>
+        <v>98101</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3876,34 +3851,35 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
       <c r="J31" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K31" t="inlineStr"/>
+      <c r="L31" t="inlineStr"/>
       <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
@@ -3911,10 +3887,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>745321</v>
+        <v>745294</v>
       </c>
       <c r="R31" t="n">
-        <v>7107841</v>
+        <v>7107877</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3974,7 +3950,7 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>125223807</v>
+        <v>125227661</v>
       </c>
       <c r="B32" t="n">
         <v>98101</v>
@@ -4022,10 +3998,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>745315</v>
+        <v>745280</v>
       </c>
       <c r="R32" t="n">
-        <v>7107851</v>
+        <v>7107827</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4058,11 +4034,6 @@
       <c r="AA32" t="inlineStr">
         <is>
           <t>2025-05-18</t>
-        </is>
-      </c>
-      <c r="AC32" t="inlineStr">
-        <is>
-          <t>Rikligt med bladrosetter!</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4090,10 +4061,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>125226206</v>
+        <v>125227728</v>
       </c>
       <c r="B33" t="n">
-        <v>91012</v>
+        <v>98101</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4102,34 +4073,35 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
       <c r="J33" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K33" t="inlineStr"/>
+      <c r="L33" t="inlineStr"/>
       <c r="N33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
@@ -4137,10 +4109,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>745327</v>
+        <v>745279</v>
       </c>
       <c r="R33" t="n">
-        <v>7107827</v>
+        <v>7107831</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4200,10 +4172,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>125232283</v>
+        <v>125225490</v>
       </c>
       <c r="B34" t="n">
-        <v>57883</v>
+        <v>91361</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4212,31 +4184,34 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>103015</v>
+        <v>2062</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Ulltickeporing</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Skeletocutis brevispora</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K34" t="inlineStr"/>
-      <c r="L34" t="inlineStr"/>
-      <c r="M34" t="inlineStr"/>
       <c r="N34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
@@ -4244,13 +4219,13 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>745254</v>
+        <v>745321</v>
       </c>
       <c r="R34" t="n">
-        <v>7107972</v>
+        <v>7107841</v>
       </c>
       <c r="S34" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4288,28 +4263,29 @@
       <c r="AE34" t="b">
         <v>0</v>
       </c>
+      <c r="AF34" t="inlineStr"/>
       <c r="AG34" t="b">
         <v>0</v>
       </c>
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Patrik Nygren</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Patrik Nygren</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>125232195</v>
+        <v>125231545</v>
       </c>
       <c r="B35" t="n">
-        <v>79891</v>
+        <v>79795</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4318,25 +4294,25 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6458</v>
+        <v>6456</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4349,10 +4325,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>745215</v>
+        <v>745310</v>
       </c>
       <c r="R35" t="n">
-        <v>7107730</v>
+        <v>7107876</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4412,7 +4388,7 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>125227446</v>
+        <v>125227327</v>
       </c>
       <c r="B36" t="n">
         <v>98101</v>
@@ -4463,7 +4439,7 @@
         <v>745280</v>
       </c>
       <c r="R36" t="n">
-        <v>7107802</v>
+        <v>7107795</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4523,7 +4499,7 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>125222288</v>
+        <v>125231249</v>
       </c>
       <c r="B37" t="n">
         <v>98101</v>
@@ -4557,11 +4533,7 @@
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
-      <c r="J37" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="J37" t="inlineStr"/>
       <c r="K37" t="inlineStr"/>
       <c r="L37" t="inlineStr"/>
       <c r="N37" t="inlineStr"/>
@@ -4571,10 +4543,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>745266</v>
+        <v>745260</v>
       </c>
       <c r="R37" t="n">
-        <v>7107910</v>
+        <v>7107948</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4622,19 +4594,19 @@
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Patrik Nygren</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Patrik Nygren</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>125231309</v>
+        <v>125223807</v>
       </c>
       <c r="B38" t="n">
         <v>98101</v>
@@ -4668,7 +4640,11 @@
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
-      <c r="J38" t="inlineStr"/>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K38" t="inlineStr"/>
       <c r="L38" t="inlineStr"/>
       <c r="N38" t="inlineStr"/>
@@ -4678,10 +4654,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>745268</v>
+        <v>745315</v>
       </c>
       <c r="R38" t="n">
-        <v>7107926</v>
+        <v>7107851</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4716,6 +4692,11 @@
           <t>2025-05-18</t>
         </is>
       </c>
+      <c r="AC38" t="inlineStr">
+        <is>
+          <t>Rikligt med bladrosetter!</t>
+        </is>
+      </c>
       <c r="AD38" t="b">
         <v>0</v>
       </c>
@@ -4729,19 +4710,19 @@
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Patrik Nygren</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Patrik Nygren</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>125223590</v>
+        <v>125231342</v>
       </c>
       <c r="B39" t="n">
         <v>98101</v>
@@ -4775,11 +4756,7 @@
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
-      <c r="J39" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="J39" t="inlineStr"/>
       <c r="K39" t="inlineStr"/>
       <c r="L39" t="inlineStr"/>
       <c r="N39" t="inlineStr"/>
@@ -4789,10 +4766,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>745299</v>
+        <v>745267</v>
       </c>
       <c r="R39" t="n">
-        <v>7107851</v>
+        <v>7107907</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4840,22 +4817,22 @@
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Patrik Nygren</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Patrik Nygren</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>125231696</v>
+        <v>125222073</v>
       </c>
       <c r="B40" t="n">
-        <v>98122</v>
+        <v>91012</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4864,31 +4841,34 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>221952</v>
+        <v>1202</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
-      <c r="J40" t="inlineStr"/>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K40" t="inlineStr"/>
-      <c r="L40" t="inlineStr"/>
       <c r="N40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
@@ -4896,10 +4876,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>745356</v>
+        <v>745262</v>
       </c>
       <c r="R40" t="n">
-        <v>7107793</v>
+        <v>7107946</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4947,22 +4927,22 @@
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Patrik Nygren</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Patrik Nygren</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>125232024</v>
+        <v>125226783</v>
       </c>
       <c r="B41" t="n">
-        <v>91012</v>
+        <v>98101</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -4971,30 +4951,35 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
-      <c r="J41" t="inlineStr"/>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K41" t="inlineStr"/>
+      <c r="L41" t="inlineStr"/>
       <c r="N41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
@@ -5002,10 +4987,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>745288</v>
+        <v>745294</v>
       </c>
       <c r="R41" t="n">
-        <v>7107786</v>
+        <v>7107772</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5053,22 +5038,22 @@
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Patrik Nygren</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Patrik Nygren</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>125231545</v>
+        <v>125222404</v>
       </c>
       <c r="B42" t="n">
-        <v>79795</v>
+        <v>98101</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -5077,30 +5062,35 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6456</v>
+        <v>220787</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
-      <c r="J42" t="inlineStr"/>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K42" t="inlineStr"/>
+      <c r="L42" t="inlineStr"/>
       <c r="N42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
@@ -5108,10 +5098,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>745310</v>
+        <v>745290</v>
       </c>
       <c r="R42" t="n">
-        <v>7107876</v>
+        <v>7107886</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5146,6 +5136,11 @@
           <t>2025-05-18</t>
         </is>
       </c>
+      <c r="AC42" t="inlineStr">
+        <is>
+          <t>några kvadratmeter med bladrosetter</t>
+        </is>
+      </c>
       <c r="AD42" t="b">
         <v>0</v>
       </c>
@@ -5159,22 +5154,22 @@
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Patrik Nygren</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Patrik Nygren</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>125222073</v>
+        <v>125228040</v>
       </c>
       <c r="B43" t="n">
-        <v>91012</v>
+        <v>98101</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5183,34 +5178,35 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
       <c r="J43" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K43" t="inlineStr"/>
+      <c r="L43" t="inlineStr"/>
       <c r="N43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
@@ -5218,10 +5214,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>745262</v>
+        <v>745249</v>
       </c>
       <c r="R43" t="n">
-        <v>7107946</v>
+        <v>7107940</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5254,6 +5250,11 @@
       <c r="AA43" t="inlineStr">
         <is>
           <t>2025-05-18</t>
+        </is>
+      </c>
+      <c r="AC43" t="inlineStr">
+        <is>
+          <t>rikligt med bladrosetter!</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5281,10 +5282,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>125226477</v>
+        <v>125232212</v>
       </c>
       <c r="B44" t="n">
-        <v>91012</v>
+        <v>98101</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5293,34 +5294,31 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
-      <c r="J44" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+      <c r="J44" t="inlineStr"/>
       <c r="K44" t="inlineStr"/>
+      <c r="L44" t="inlineStr"/>
       <c r="N44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
@@ -5328,10 +5326,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>745445</v>
+        <v>745252</v>
       </c>
       <c r="R44" t="n">
-        <v>7107841</v>
+        <v>7107940</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5379,19 +5377,19 @@
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>Patrik Nygren</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Patrik Nygren</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>125231618</v>
+        <v>125231464</v>
       </c>
       <c r="B45" t="n">
         <v>79795</v>
@@ -5434,10 +5432,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>745381</v>
+        <v>745287</v>
       </c>
       <c r="R45" t="n">
-        <v>7107841</v>
+        <v>7107886</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5497,10 +5495,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>125231948</v>
+        <v>125231779</v>
       </c>
       <c r="B46" t="n">
-        <v>98101</v>
+        <v>79920</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5509,31 +5507,30 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>220787</v>
+        <v>6462</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
       <c r="J46" t="inlineStr"/>
       <c r="K46" t="inlineStr"/>
-      <c r="L46" t="inlineStr"/>
       <c r="N46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
@@ -5541,10 +5538,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>745279</v>
+        <v>745323</v>
       </c>
       <c r="R46" t="n">
-        <v>7107754</v>
+        <v>7107772</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5604,10 +5601,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>125232212</v>
+        <v>125231105</v>
       </c>
       <c r="B47" t="n">
-        <v>98101</v>
+        <v>79920</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5616,31 +5613,30 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>220787</v>
+        <v>6462</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
       <c r="J47" t="inlineStr"/>
       <c r="K47" t="inlineStr"/>
-      <c r="L47" t="inlineStr"/>
       <c r="N47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
@@ -5648,10 +5644,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>745252</v>
+        <v>745259</v>
       </c>
       <c r="R47" t="n">
-        <v>7107940</v>
+        <v>7107964</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5711,7 +5707,7 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>125231888</v>
+        <v>125227797</v>
       </c>
       <c r="B48" t="n">
         <v>98101</v>
@@ -5745,7 +5741,11 @@
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
-      <c r="J48" t="inlineStr"/>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K48" t="inlineStr"/>
       <c r="L48" t="inlineStr"/>
       <c r="N48" t="inlineStr"/>
@@ -5755,10 +5755,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>745297</v>
+        <v>745277</v>
       </c>
       <c r="R48" t="n">
-        <v>7107757</v>
+        <v>7107838</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5806,22 +5806,22 @@
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Patrik Nygren</t>
         </is>
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Patrik Nygren</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>125222246</v>
+        <v>125222754</v>
       </c>
       <c r="B49" t="n">
-        <v>91012</v>
+        <v>98101</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -5830,34 +5830,35 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
       <c r="J49" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K49" t="inlineStr"/>
+      <c r="L49" t="inlineStr"/>
       <c r="N49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
@@ -5865,10 +5866,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>745262</v>
+        <v>745306</v>
       </c>
       <c r="R49" t="n">
-        <v>7107944</v>
+        <v>7107877</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5928,10 +5929,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>125227797</v>
+        <v>125226477</v>
       </c>
       <c r="B50" t="n">
-        <v>98101</v>
+        <v>91012</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -5940,35 +5941,34 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
       <c r="J50" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K50" t="inlineStr"/>
-      <c r="L50" t="inlineStr"/>
       <c r="N50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
@@ -5976,10 +5976,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>745277</v>
+        <v>745445</v>
       </c>
       <c r="R50" t="n">
-        <v>7107838</v>
+        <v>7107841</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>

--- a/artfynd/A 53969-2024 artfynd.xlsx
+++ b/artfynd/A 53969-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>125225982</v>
+        <v>125222083</v>
       </c>
       <c r="B2" t="n">
-        <v>98101</v>
+        <v>91361</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,31 +691,30 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220787</v>
+        <v>2062</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ulltickeporing</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Skeletocutis brevispora</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="J2" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -723,10 +722,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>745327</v>
+        <v>745262</v>
       </c>
       <c r="R2" t="n">
-        <v>7107834</v>
+        <v>7107946</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -786,10 +785,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>125222999</v>
+        <v>125231618</v>
       </c>
       <c r="B3" t="n">
-        <v>98101</v>
+        <v>79795</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -798,35 +797,30 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220787</v>
+        <v>6456</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -834,10 +828,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>745290</v>
+        <v>745381</v>
       </c>
       <c r="R3" t="n">
-        <v>7107864</v>
+        <v>7107841</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -885,22 +879,22 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Patrik Nygren</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Patrik Nygren</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>125222055</v>
+        <v>125226783</v>
       </c>
       <c r="B4" t="n">
-        <v>91012</v>
+        <v>98101</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -909,34 +903,35 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="J4" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -944,10 +939,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>745262</v>
+        <v>745294</v>
       </c>
       <c r="R4" t="n">
-        <v>7107948</v>
+        <v>7107772</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1007,10 +1002,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>125232181</v>
+        <v>125222055</v>
       </c>
       <c r="B5" t="n">
-        <v>57529</v>
+        <v>91012</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1023,27 +1018,30 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100049</v>
+        <v>1202</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr"/>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1051,10 +1049,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>745227</v>
+        <v>745262</v>
       </c>
       <c r="R5" t="n">
-        <v>7107774</v>
+        <v>7107948</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1095,28 +1093,29 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
+      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Patrik Nygren</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Patrik Nygren</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>125231618</v>
+        <v>125222754</v>
       </c>
       <c r="B6" t="n">
-        <v>79795</v>
+        <v>98101</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1125,30 +1124,35 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6456</v>
+        <v>220787</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr"/>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1156,10 +1160,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>745381</v>
+        <v>745306</v>
       </c>
       <c r="R6" t="n">
-        <v>7107841</v>
+        <v>7107877</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1207,22 +1211,22 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Patrik Nygren</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Patrik Nygren</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>125227847</v>
+        <v>125228040</v>
       </c>
       <c r="B7" t="n">
-        <v>57529</v>
+        <v>98101</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1231,35 +1235,35 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
@@ -1267,10 +1271,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>745285</v>
+        <v>745249</v>
       </c>
       <c r="R7" t="n">
-        <v>7107862</v>
+        <v>7107940</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1307,7 +1311,7 @@
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>hack i död gran</t>
+          <t>rikligt med bladrosetter!</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1316,6 +1320,7 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
+      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
@@ -1334,10 +1339,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>125227446</v>
+        <v>125232283</v>
       </c>
       <c r="B8" t="n">
-        <v>98101</v>
+        <v>57883</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1346,35 +1351,31 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>220787</v>
+        <v>103015</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
       <c r="K8" t="inlineStr"/>
       <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr"/>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
@@ -1382,13 +1383,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>745280</v>
+        <v>745254</v>
       </c>
       <c r="R8" t="n">
-        <v>7107802</v>
+        <v>7107972</v>
       </c>
       <c r="S8" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1426,29 +1427,28 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
-      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Patrik Nygren</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Patrik Nygren</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>125231838</v>
+        <v>125231779</v>
       </c>
       <c r="B9" t="n">
-        <v>98101</v>
+        <v>79920</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1457,31 +1457,30 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>220787</v>
+        <v>6462</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="J9" t="inlineStr"/>
       <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr"/>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
@@ -1489,10 +1488,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>745310</v>
+        <v>745323</v>
       </c>
       <c r="R9" t="n">
-        <v>7107765</v>
+        <v>7107772</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1552,10 +1551,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>125222083</v>
+        <v>125227901</v>
       </c>
       <c r="B10" t="n">
-        <v>91361</v>
+        <v>98101</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1568,30 +1567,31 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>2062</v>
+        <v>220787</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Ulltickeporing</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Skeletocutis brevispora</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="J10" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
@@ -1599,10 +1599,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>745262</v>
+        <v>745280</v>
       </c>
       <c r="R10" t="n">
-        <v>7107946</v>
+        <v>7107886</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1662,10 +1662,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>125231309</v>
+        <v>125227847</v>
       </c>
       <c r="B11" t="n">
-        <v>98101</v>
+        <v>57529</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1674,31 +1674,35 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="J11" t="inlineStr"/>
       <c r="K11" t="inlineStr"/>
       <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
@@ -1706,10 +1710,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>745268</v>
+        <v>745285</v>
       </c>
       <c r="R11" t="n">
-        <v>7107926</v>
+        <v>7107862</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1744,35 +1748,39 @@
           <t>2025-05-18</t>
         </is>
       </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>hack i död gran</t>
+        </is>
+      </c>
       <c r="AD11" t="b">
         <v>0</v>
       </c>
       <c r="AE11" t="b">
         <v>0</v>
       </c>
-      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Patrik Nygren</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Patrik Nygren</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>125226206</v>
+        <v>125227327</v>
       </c>
       <c r="B12" t="n">
-        <v>91012</v>
+        <v>98101</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1781,34 +1789,35 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
       <c r="J12" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
@@ -1816,10 +1825,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>745327</v>
+        <v>745280</v>
       </c>
       <c r="R12" t="n">
-        <v>7107827</v>
+        <v>7107795</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1879,7 +1888,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>125223203</v>
+        <v>125223590</v>
       </c>
       <c r="B13" t="n">
         <v>98101</v>
@@ -1927,10 +1936,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>745293</v>
+        <v>745299</v>
       </c>
       <c r="R13" t="n">
-        <v>7107855</v>
+        <v>7107851</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1990,7 +1999,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>125222017</v>
+        <v>125227661</v>
       </c>
       <c r="B14" t="n">
         <v>98101</v>
@@ -2038,10 +2047,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>745243</v>
+        <v>745280</v>
       </c>
       <c r="R14" t="n">
-        <v>7107977</v>
+        <v>7107827</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2101,10 +2110,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>125228007</v>
+        <v>125222073</v>
       </c>
       <c r="B15" t="n">
-        <v>57529</v>
+        <v>91012</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2117,31 +2126,30 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100049</v>
+        <v>1202</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K15" t="inlineStr"/>
-      <c r="L15" t="inlineStr"/>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
@@ -2149,10 +2157,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>745249</v>
+        <v>745262</v>
       </c>
       <c r="R15" t="n">
-        <v>7107940</v>
+        <v>7107946</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2187,17 +2195,13 @@
           <t>2025-05-18</t>
         </is>
       </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>hackat hål i gran</t>
-        </is>
-      </c>
       <c r="AD15" t="b">
         <v>0</v>
       </c>
       <c r="AE15" t="b">
         <v>0</v>
       </c>
+      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
       </c>
@@ -2216,10 +2220,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>125231658</v>
+        <v>125227728</v>
       </c>
       <c r="B16" t="n">
-        <v>90977</v>
+        <v>98101</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2228,30 +2232,35 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>5447</v>
+        <v>220787</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
-      <c r="J16" t="inlineStr"/>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
       <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
@@ -2259,10 +2268,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>745405</v>
+        <v>745279</v>
       </c>
       <c r="R16" t="n">
-        <v>7107837</v>
+        <v>7107831</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2310,22 +2319,22 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Patrik Nygren</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Patrik Nygren</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>125232195</v>
+        <v>125222404</v>
       </c>
       <c r="B17" t="n">
-        <v>79891</v>
+        <v>98101</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2334,30 +2343,35 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
-      <c r="J17" t="inlineStr"/>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr"/>
       <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
@@ -2365,10 +2379,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>745215</v>
+        <v>745290</v>
       </c>
       <c r="R17" t="n">
-        <v>7107730</v>
+        <v>7107886</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2403,6 +2417,11 @@
           <t>2025-05-18</t>
         </is>
       </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>några kvadratmeter med bladrosetter</t>
+        </is>
+      </c>
       <c r="AD17" t="b">
         <v>0</v>
       </c>
@@ -2416,22 +2435,22 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Patrik Nygren</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Patrik Nygren</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>125225686</v>
+        <v>125223425</v>
       </c>
       <c r="B18" t="n">
-        <v>91012</v>
+        <v>98101</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2440,34 +2459,35 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
       <c r="J18" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr"/>
       <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
@@ -2475,10 +2495,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>745321</v>
+        <v>745298</v>
       </c>
       <c r="R18" t="n">
-        <v>7107841</v>
+        <v>7107856</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2538,7 +2558,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>125223590</v>
+        <v>125223807</v>
       </c>
       <c r="B19" t="n">
         <v>98101</v>
@@ -2586,7 +2606,7 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>745299</v>
+        <v>745315</v>
       </c>
       <c r="R19" t="n">
         <v>7107851</v>
@@ -2622,6 +2642,11 @@
       <c r="AA19" t="inlineStr">
         <is>
           <t>2025-05-18</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>Rikligt med bladrosetter!</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2649,7 +2674,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>125230982</v>
+        <v>125223203</v>
       </c>
       <c r="B20" t="n">
         <v>98101</v>
@@ -2683,7 +2708,11 @@
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
-      <c r="J20" t="inlineStr"/>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K20" t="inlineStr"/>
       <c r="L20" t="inlineStr"/>
       <c r="N20" t="inlineStr"/>
@@ -2693,10 +2722,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>745259</v>
+        <v>745293</v>
       </c>
       <c r="R20" t="n">
-        <v>7107964</v>
+        <v>7107855</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2744,19 +2773,19 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Patrik Nygren</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Patrik Nygren</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>125222288</v>
+        <v>125231948</v>
       </c>
       <c r="B21" t="n">
         <v>98101</v>
@@ -2790,11 +2819,7 @@
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
-      <c r="J21" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="J21" t="inlineStr"/>
       <c r="K21" t="inlineStr"/>
       <c r="L21" t="inlineStr"/>
       <c r="N21" t="inlineStr"/>
@@ -2804,10 +2829,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>745266</v>
+        <v>745279</v>
       </c>
       <c r="R21" t="n">
-        <v>7107910</v>
+        <v>7107754</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2855,22 +2880,22 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Patrik Nygren</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Patrik Nygren</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>125222246</v>
+        <v>125231983</v>
       </c>
       <c r="B22" t="n">
-        <v>91012</v>
+        <v>98101</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2879,34 +2904,31 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
-      <c r="J22" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+      <c r="J22" t="inlineStr"/>
       <c r="K22" t="inlineStr"/>
+      <c r="L22" t="inlineStr"/>
       <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
@@ -2914,10 +2936,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>745262</v>
+        <v>745279</v>
       </c>
       <c r="R22" t="n">
-        <v>7107944</v>
+        <v>7107767</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2965,22 +2987,22 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Patrik Nygren</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Patrik Nygren</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>125232024</v>
+        <v>125232212</v>
       </c>
       <c r="B23" t="n">
-        <v>91012</v>
+        <v>98101</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2989,30 +3011,31 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
       <c r="J23" t="inlineStr"/>
       <c r="K23" t="inlineStr"/>
+      <c r="L23" t="inlineStr"/>
       <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
@@ -3020,10 +3043,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>745288</v>
+        <v>745252</v>
       </c>
       <c r="R23" t="n">
-        <v>7107786</v>
+        <v>7107940</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3083,10 +3106,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>125223425</v>
+        <v>125231105</v>
       </c>
       <c r="B24" t="n">
-        <v>98101</v>
+        <v>79920</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3095,35 +3118,30 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>220787</v>
+        <v>6462</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
-      <c r="J24" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="J24" t="inlineStr"/>
       <c r="K24" t="inlineStr"/>
-      <c r="L24" t="inlineStr"/>
       <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
@@ -3131,10 +3149,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>745298</v>
+        <v>745259</v>
       </c>
       <c r="R24" t="n">
-        <v>7107856</v>
+        <v>7107964</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3182,22 +3200,22 @@
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Patrik Nygren</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Patrik Nygren</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>125231888</v>
+        <v>125225490</v>
       </c>
       <c r="B25" t="n">
-        <v>98101</v>
+        <v>91361</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3210,27 +3228,30 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>220787</v>
+        <v>2062</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ulltickeporing</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Skeletocutis brevispora</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
-      <c r="J25" t="inlineStr"/>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K25" t="inlineStr"/>
-      <c r="L25" t="inlineStr"/>
       <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
@@ -3238,10 +3259,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>745297</v>
+        <v>745321</v>
       </c>
       <c r="R25" t="n">
-        <v>7107757</v>
+        <v>7107841</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3289,22 +3310,22 @@
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Patrik Nygren</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Patrik Nygren</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>125232283</v>
+        <v>125231342</v>
       </c>
       <c r="B26" t="n">
-        <v>57883</v>
+        <v>98101</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3313,31 +3334,31 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>103015</v>
+        <v>220787</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
+      <c r="J26" t="inlineStr"/>
       <c r="K26" t="inlineStr"/>
       <c r="L26" t="inlineStr"/>
-      <c r="M26" t="inlineStr"/>
       <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
@@ -3345,13 +3366,13 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>745254</v>
+        <v>745267</v>
       </c>
       <c r="R26" t="n">
-        <v>7107972</v>
+        <v>7107907</v>
       </c>
       <c r="S26" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3389,6 +3410,7 @@
       <c r="AE26" t="b">
         <v>0</v>
       </c>
+      <c r="AF26" t="inlineStr"/>
       <c r="AG26" t="b">
         <v>0</v>
       </c>
@@ -3407,7 +3429,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>125231983</v>
+        <v>125231888</v>
       </c>
       <c r="B27" t="n">
         <v>98101</v>
@@ -3451,10 +3473,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>745279</v>
+        <v>745297</v>
       </c>
       <c r="R27" t="n">
-        <v>7107767</v>
+        <v>7107757</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3514,7 +3536,7 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>125231948</v>
+        <v>125222545</v>
       </c>
       <c r="B28" t="n">
         <v>98101</v>
@@ -3548,7 +3570,11 @@
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
-      <c r="J28" t="inlineStr"/>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K28" t="inlineStr"/>
       <c r="L28" t="inlineStr"/>
       <c r="N28" t="inlineStr"/>
@@ -3558,10 +3584,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>745279</v>
+        <v>745294</v>
       </c>
       <c r="R28" t="n">
-        <v>7107754</v>
+        <v>7107877</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3609,22 +3635,22 @@
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Patrik Nygren</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Patrik Nygren</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>125231696</v>
+        <v>125227446</v>
       </c>
       <c r="B29" t="n">
-        <v>98122</v>
+        <v>98101</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3633,29 +3659,33 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>221952</v>
+        <v>220787</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
-      <c r="J29" t="inlineStr"/>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K29" t="inlineStr"/>
       <c r="L29" t="inlineStr"/>
       <c r="N29" t="inlineStr"/>
@@ -3665,10 +3695,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>745356</v>
+        <v>745280</v>
       </c>
       <c r="R29" t="n">
-        <v>7107793</v>
+        <v>7107802</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3716,19 +3746,19 @@
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Patrik Nygren</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Patrik Nygren</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>125227901</v>
+        <v>125222999</v>
       </c>
       <c r="B30" t="n">
         <v>98101</v>
@@ -3776,10 +3806,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>745280</v>
+        <v>745290</v>
       </c>
       <c r="R30" t="n">
-        <v>7107886</v>
+        <v>7107864</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3839,7 +3869,7 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>125222545</v>
+        <v>125231309</v>
       </c>
       <c r="B31" t="n">
         <v>98101</v>
@@ -3873,11 +3903,7 @@
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
-      <c r="J31" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="J31" t="inlineStr"/>
       <c r="K31" t="inlineStr"/>
       <c r="L31" t="inlineStr"/>
       <c r="N31" t="inlineStr"/>
@@ -3887,10 +3913,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>745294</v>
+        <v>745268</v>
       </c>
       <c r="R31" t="n">
-        <v>7107877</v>
+        <v>7107926</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3938,22 +3964,22 @@
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Patrik Nygren</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Patrik Nygren</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>125227661</v>
+        <v>125231464</v>
       </c>
       <c r="B32" t="n">
-        <v>98101</v>
+        <v>79795</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -3962,35 +3988,30 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>220787</v>
+        <v>6456</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
-      <c r="J32" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="J32" t="inlineStr"/>
       <c r="K32" t="inlineStr"/>
-      <c r="L32" t="inlineStr"/>
       <c r="N32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
@@ -3998,10 +4019,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>745280</v>
+        <v>745287</v>
       </c>
       <c r="R32" t="n">
-        <v>7107827</v>
+        <v>7107886</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4049,22 +4070,22 @@
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Patrik Nygren</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Patrik Nygren</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>125227728</v>
+        <v>125226477</v>
       </c>
       <c r="B33" t="n">
-        <v>98101</v>
+        <v>91012</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4073,35 +4094,34 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
       <c r="J33" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K33" t="inlineStr"/>
-      <c r="L33" t="inlineStr"/>
       <c r="N33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
@@ -4109,10 +4129,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>745279</v>
+        <v>745445</v>
       </c>
       <c r="R33" t="n">
-        <v>7107831</v>
+        <v>7107841</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4172,10 +4192,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>125225490</v>
+        <v>125225686</v>
       </c>
       <c r="B34" t="n">
-        <v>91361</v>
+        <v>91012</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4184,25 +4204,25 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>2062</v>
+        <v>1202</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Ulltickeporing</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Skeletocutis brevispora</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4282,10 +4302,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>125231545</v>
+        <v>125228007</v>
       </c>
       <c r="B35" t="n">
-        <v>79795</v>
+        <v>57529</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4294,30 +4314,35 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6456</v>
+        <v>100049</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
-      <c r="J35" t="inlineStr"/>
       <c r="K35" t="inlineStr"/>
+      <c r="L35" t="inlineStr"/>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
@@ -4325,10 +4350,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>745310</v>
+        <v>745249</v>
       </c>
       <c r="R35" t="n">
-        <v>7107876</v>
+        <v>7107940</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4363,35 +4388,39 @@
           <t>2025-05-18</t>
         </is>
       </c>
+      <c r="AC35" t="inlineStr">
+        <is>
+          <t>hackat hål i gran</t>
+        </is>
+      </c>
       <c r="AD35" t="b">
         <v>0</v>
       </c>
       <c r="AE35" t="b">
         <v>0</v>
       </c>
-      <c r="AF35" t="inlineStr"/>
       <c r="AG35" t="b">
         <v>0</v>
       </c>
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Patrik Nygren</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Patrik Nygren</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>125227327</v>
+        <v>125231545</v>
       </c>
       <c r="B36" t="n">
-        <v>98101</v>
+        <v>79795</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4400,35 +4429,30 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>220787</v>
+        <v>6456</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
-      <c r="J36" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="J36" t="inlineStr"/>
       <c r="K36" t="inlineStr"/>
-      <c r="L36" t="inlineStr"/>
       <c r="N36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
@@ -4436,10 +4460,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>745280</v>
+        <v>745310</v>
       </c>
       <c r="R36" t="n">
-        <v>7107795</v>
+        <v>7107876</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4487,19 +4511,19 @@
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Patrik Nygren</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Patrik Nygren</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>125231249</v>
+        <v>125227797</v>
       </c>
       <c r="B37" t="n">
         <v>98101</v>
@@ -4533,7 +4557,11 @@
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
-      <c r="J37" t="inlineStr"/>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K37" t="inlineStr"/>
       <c r="L37" t="inlineStr"/>
       <c r="N37" t="inlineStr"/>
@@ -4543,10 +4571,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>745260</v>
+        <v>745277</v>
       </c>
       <c r="R37" t="n">
-        <v>7107948</v>
+        <v>7107838</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4594,19 +4622,19 @@
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Patrik Nygren</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Patrik Nygren</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>125223807</v>
+        <v>125230982</v>
       </c>
       <c r="B38" t="n">
         <v>98101</v>
@@ -4640,11 +4668,7 @@
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
-      <c r="J38" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="J38" t="inlineStr"/>
       <c r="K38" t="inlineStr"/>
       <c r="L38" t="inlineStr"/>
       <c r="N38" t="inlineStr"/>
@@ -4654,10 +4678,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>745315</v>
+        <v>745259</v>
       </c>
       <c r="R38" t="n">
-        <v>7107851</v>
+        <v>7107964</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4692,11 +4716,6 @@
           <t>2025-05-18</t>
         </is>
       </c>
-      <c r="AC38" t="inlineStr">
-        <is>
-          <t>Rikligt med bladrosetter!</t>
-        </is>
-      </c>
       <c r="AD38" t="b">
         <v>0</v>
       </c>
@@ -4710,19 +4729,19 @@
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Patrik Nygren</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Patrik Nygren</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>125231342</v>
+        <v>125222017</v>
       </c>
       <c r="B39" t="n">
         <v>98101</v>
@@ -4756,7 +4775,11 @@
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
-      <c r="J39" t="inlineStr"/>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K39" t="inlineStr"/>
       <c r="L39" t="inlineStr"/>
       <c r="N39" t="inlineStr"/>
@@ -4766,10 +4789,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>745267</v>
+        <v>745243</v>
       </c>
       <c r="R39" t="n">
-        <v>7107907</v>
+        <v>7107977</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4817,22 +4840,22 @@
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Patrik Nygren</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Patrik Nygren</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>125222073</v>
+        <v>125231696</v>
       </c>
       <c r="B40" t="n">
-        <v>91012</v>
+        <v>98122</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4841,34 +4864,31 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>1202</v>
+        <v>221952</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
-      <c r="J40" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+      <c r="J40" t="inlineStr"/>
       <c r="K40" t="inlineStr"/>
+      <c r="L40" t="inlineStr"/>
       <c r="N40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
@@ -4876,10 +4896,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>745262</v>
+        <v>745356</v>
       </c>
       <c r="R40" t="n">
-        <v>7107946</v>
+        <v>7107793</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4927,22 +4947,22 @@
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>Patrik Nygren</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Patrik Nygren</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>125226783</v>
+        <v>125231658</v>
       </c>
       <c r="B41" t="n">
-        <v>98101</v>
+        <v>90977</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -4951,35 +4971,30 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>220787</v>
+        <v>5447</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
-      <c r="J41" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="J41" t="inlineStr"/>
       <c r="K41" t="inlineStr"/>
-      <c r="L41" t="inlineStr"/>
       <c r="N41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
@@ -4987,10 +5002,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>745294</v>
+        <v>745405</v>
       </c>
       <c r="R41" t="n">
-        <v>7107772</v>
+        <v>7107837</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5038,22 +5053,22 @@
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Patrik Nygren</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Patrik Nygren</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>125222404</v>
+        <v>125232024</v>
       </c>
       <c r="B42" t="n">
-        <v>98101</v>
+        <v>91012</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -5062,35 +5077,30 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
-      <c r="J42" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="J42" t="inlineStr"/>
       <c r="K42" t="inlineStr"/>
-      <c r="L42" t="inlineStr"/>
       <c r="N42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
@@ -5098,10 +5108,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>745290</v>
+        <v>745288</v>
       </c>
       <c r="R42" t="n">
-        <v>7107886</v>
+        <v>7107786</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5136,11 +5146,6 @@
           <t>2025-05-18</t>
         </is>
       </c>
-      <c r="AC42" t="inlineStr">
-        <is>
-          <t>några kvadratmeter med bladrosetter</t>
-        </is>
-      </c>
       <c r="AD42" t="b">
         <v>0</v>
       </c>
@@ -5154,19 +5159,19 @@
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Patrik Nygren</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Patrik Nygren</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>125228040</v>
+        <v>125225982</v>
       </c>
       <c r="B43" t="n">
         <v>98101</v>
@@ -5214,10 +5219,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>745249</v>
+        <v>745327</v>
       </c>
       <c r="R43" t="n">
-        <v>7107940</v>
+        <v>7107834</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5250,11 +5255,6 @@
       <c r="AA43" t="inlineStr">
         <is>
           <t>2025-05-18</t>
-        </is>
-      </c>
-      <c r="AC43" t="inlineStr">
-        <is>
-          <t>rikligt med bladrosetter!</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5282,7 +5282,7 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>125232212</v>
+        <v>125222288</v>
       </c>
       <c r="B44" t="n">
         <v>98101</v>
@@ -5316,7 +5316,11 @@
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
-      <c r="J44" t="inlineStr"/>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K44" t="inlineStr"/>
       <c r="L44" t="inlineStr"/>
       <c r="N44" t="inlineStr"/>
@@ -5326,10 +5330,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>745252</v>
+        <v>745266</v>
       </c>
       <c r="R44" t="n">
-        <v>7107940</v>
+        <v>7107910</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5377,22 +5381,22 @@
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Patrik Nygren</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Patrik Nygren</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>125231464</v>
+        <v>125232181</v>
       </c>
       <c r="B45" t="n">
-        <v>79795</v>
+        <v>57529</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5401,30 +5405,31 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6456</v>
+        <v>100049</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
-      <c r="J45" t="inlineStr"/>
       <c r="K45" t="inlineStr"/>
+      <c r="L45" t="inlineStr"/>
+      <c r="M45" t="inlineStr"/>
       <c r="N45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
@@ -5432,10 +5437,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>745287</v>
+        <v>745227</v>
       </c>
       <c r="R45" t="n">
-        <v>7107886</v>
+        <v>7107774</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5476,7 +5481,6 @@
       <c r="AE45" t="b">
         <v>0</v>
       </c>
-      <c r="AF45" t="inlineStr"/>
       <c r="AG45" t="b">
         <v>0</v>
       </c>
@@ -5495,10 +5499,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>125231779</v>
+        <v>125232195</v>
       </c>
       <c r="B46" t="n">
-        <v>79920</v>
+        <v>79891</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5507,25 +5511,25 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6462</v>
+        <v>6458</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5538,10 +5542,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>745323</v>
+        <v>745215</v>
       </c>
       <c r="R46" t="n">
-        <v>7107772</v>
+        <v>7107730</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5601,10 +5605,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>125231105</v>
+        <v>125226206</v>
       </c>
       <c r="B47" t="n">
-        <v>79920</v>
+        <v>91012</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5613,29 +5617,33 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6462</v>
+        <v>1202</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
-      <c r="J47" t="inlineStr"/>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K47" t="inlineStr"/>
       <c r="N47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
@@ -5644,10 +5652,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>745259</v>
+        <v>745327</v>
       </c>
       <c r="R47" t="n">
-        <v>7107964</v>
+        <v>7107827</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5695,19 +5703,19 @@
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Patrik Nygren</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Patrik Nygren</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>125227797</v>
+        <v>125231249</v>
       </c>
       <c r="B48" t="n">
         <v>98101</v>
@@ -5741,11 +5749,7 @@
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
-      <c r="J48" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="J48" t="inlineStr"/>
       <c r="K48" t="inlineStr"/>
       <c r="L48" t="inlineStr"/>
       <c r="N48" t="inlineStr"/>
@@ -5755,10 +5759,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>745277</v>
+        <v>745260</v>
       </c>
       <c r="R48" t="n">
-        <v>7107838</v>
+        <v>7107948</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5806,19 +5810,19 @@
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>Patrik Nygren</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>Patrik Nygren</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>125222754</v>
+        <v>125231838</v>
       </c>
       <c r="B49" t="n">
         <v>98101</v>
@@ -5852,11 +5856,7 @@
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
-      <c r="J49" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="J49" t="inlineStr"/>
       <c r="K49" t="inlineStr"/>
       <c r="L49" t="inlineStr"/>
       <c r="N49" t="inlineStr"/>
@@ -5866,10 +5866,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>745306</v>
+        <v>745310</v>
       </c>
       <c r="R49" t="n">
-        <v>7107877</v>
+        <v>7107765</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5917,19 +5917,19 @@
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
         <is>
-          <t>Patrik Nygren</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>Patrik Nygren</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>125226477</v>
+        <v>125222246</v>
       </c>
       <c r="B50" t="n">
         <v>91012</v>
@@ -5976,10 +5976,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>745445</v>
+        <v>745262</v>
       </c>
       <c r="R50" t="n">
-        <v>7107841</v>
+        <v>7107944</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>

--- a/artfynd/A 53969-2024 artfynd.xlsx
+++ b/artfynd/A 53969-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>125222083</v>
+        <v>125225686</v>
       </c>
       <c r="B2" t="n">
-        <v>91361</v>
+        <v>91012</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>2062</v>
+        <v>1202</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Ulltickeporing</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Skeletocutis brevispora</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -722,10 +722,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>745262</v>
+        <v>745321</v>
       </c>
       <c r="R2" t="n">
-        <v>7107946</v>
+        <v>7107841</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -785,10 +785,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>125231618</v>
+        <v>125225982</v>
       </c>
       <c r="B3" t="n">
-        <v>79795</v>
+        <v>98101</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -797,30 +797,35 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6456</v>
+        <v>220787</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -828,10 +833,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>745381</v>
+        <v>745327</v>
       </c>
       <c r="R3" t="n">
-        <v>7107841</v>
+        <v>7107834</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -879,19 +884,19 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Patrik Nygren</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Patrik Nygren</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>125226783</v>
+        <v>125227797</v>
       </c>
       <c r="B4" t="n">
         <v>98101</v>
@@ -939,10 +944,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>745294</v>
+        <v>745277</v>
       </c>
       <c r="R4" t="n">
-        <v>7107772</v>
+        <v>7107838</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1002,10 +1007,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>125222055</v>
+        <v>125231105</v>
       </c>
       <c r="B5" t="n">
-        <v>91012</v>
+        <v>79920</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1014,33 +1019,29 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1202</v>
+        <v>6462</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+      <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
@@ -1049,10 +1050,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>745262</v>
+        <v>745259</v>
       </c>
       <c r="R5" t="n">
-        <v>7107948</v>
+        <v>7107964</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1100,19 +1101,19 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Patrik Nygren</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Patrik Nygren</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>125222754</v>
+        <v>125222404</v>
       </c>
       <c r="B6" t="n">
         <v>98101</v>
@@ -1160,10 +1161,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>745306</v>
+        <v>745290</v>
       </c>
       <c r="R6" t="n">
-        <v>7107877</v>
+        <v>7107886</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1196,6 +1197,11 @@
       <c r="AA6" t="inlineStr">
         <is>
           <t>2025-05-18</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>några kvadratmeter med bladrosetter</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1223,7 +1229,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>125228040</v>
+        <v>125223590</v>
       </c>
       <c r="B7" t="n">
         <v>98101</v>
@@ -1271,10 +1277,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>745249</v>
+        <v>745299</v>
       </c>
       <c r="R7" t="n">
-        <v>7107940</v>
+        <v>7107851</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1307,11 +1313,6 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-05-18</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>rikligt med bladrosetter!</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1339,10 +1340,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>125232283</v>
+        <v>125231309</v>
       </c>
       <c r="B8" t="n">
-        <v>57883</v>
+        <v>98101</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1351,31 +1352,31 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>103015</v>
+        <v>220787</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
       <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr"/>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
@@ -1383,13 +1384,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>745254</v>
+        <v>745268</v>
       </c>
       <c r="R8" t="n">
-        <v>7107972</v>
+        <v>7107926</v>
       </c>
       <c r="S8" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1427,6 +1428,7 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
+      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
@@ -1445,10 +1447,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>125231779</v>
+        <v>125232283</v>
       </c>
       <c r="B9" t="n">
-        <v>79920</v>
+        <v>57883</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1461,26 +1463,27 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6462</v>
+        <v>103015</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="J9" t="inlineStr"/>
       <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr"/>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
@@ -1488,13 +1491,13 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>745323</v>
+        <v>745254</v>
       </c>
       <c r="R9" t="n">
-        <v>7107772</v>
+        <v>7107972</v>
       </c>
       <c r="S9" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1532,7 +1535,6 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
-      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
@@ -1551,10 +1553,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>125227901</v>
+        <v>125222083</v>
       </c>
       <c r="B10" t="n">
-        <v>98101</v>
+        <v>91361</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1567,31 +1569,30 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>220787</v>
+        <v>2062</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ulltickeporing</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Skeletocutis brevispora</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="J10" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr"/>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
@@ -1599,10 +1600,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>745280</v>
+        <v>745262</v>
       </c>
       <c r="R10" t="n">
-        <v>7107886</v>
+        <v>7107946</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1662,10 +1663,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>125227847</v>
+        <v>125226783</v>
       </c>
       <c r="B11" t="n">
-        <v>57529</v>
+        <v>98101</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1674,35 +1675,35 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K11" t="inlineStr"/>
       <c r="L11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
@@ -1710,10 +1711,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>745285</v>
+        <v>745294</v>
       </c>
       <c r="R11" t="n">
-        <v>7107862</v>
+        <v>7107772</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1748,17 +1749,13 @@
           <t>2025-05-18</t>
         </is>
       </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>hack i död gran</t>
-        </is>
-      </c>
       <c r="AD11" t="b">
         <v>0</v>
       </c>
       <c r="AE11" t="b">
         <v>0</v>
       </c>
+      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
@@ -1777,7 +1774,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>125227327</v>
+        <v>125223425</v>
       </c>
       <c r="B12" t="n">
         <v>98101</v>
@@ -1825,10 +1822,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>745280</v>
+        <v>745298</v>
       </c>
       <c r="R12" t="n">
-        <v>7107795</v>
+        <v>7107856</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1888,7 +1885,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>125223590</v>
+        <v>125231342</v>
       </c>
       <c r="B13" t="n">
         <v>98101</v>
@@ -1922,11 +1919,7 @@
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="J13" t="inlineStr"/>
       <c r="K13" t="inlineStr"/>
       <c r="L13" t="inlineStr"/>
       <c r="N13" t="inlineStr"/>
@@ -1936,10 +1929,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>745299</v>
+        <v>745267</v>
       </c>
       <c r="R13" t="n">
-        <v>7107851</v>
+        <v>7107907</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1987,22 +1980,22 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Patrik Nygren</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Patrik Nygren</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>125227661</v>
+        <v>125225490</v>
       </c>
       <c r="B14" t="n">
-        <v>98101</v>
+        <v>91361</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2015,31 +2008,30 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>220787</v>
+        <v>2062</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ulltickeporing</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Skeletocutis brevispora</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
       <c r="J14" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K14" t="inlineStr"/>
-      <c r="L14" t="inlineStr"/>
       <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
@@ -2047,10 +2039,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>745280</v>
+        <v>745321</v>
       </c>
       <c r="R14" t="n">
-        <v>7107827</v>
+        <v>7107841</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2220,7 +2212,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>125227728</v>
+        <v>125222754</v>
       </c>
       <c r="B16" t="n">
         <v>98101</v>
@@ -2268,10 +2260,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>745279</v>
+        <v>745306</v>
       </c>
       <c r="R16" t="n">
-        <v>7107831</v>
+        <v>7107877</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2331,7 +2323,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>125222404</v>
+        <v>125231983</v>
       </c>
       <c r="B17" t="n">
         <v>98101</v>
@@ -2365,11 +2357,7 @@
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
-      <c r="J17" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="J17" t="inlineStr"/>
       <c r="K17" t="inlineStr"/>
       <c r="L17" t="inlineStr"/>
       <c r="N17" t="inlineStr"/>
@@ -2379,10 +2367,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>745290</v>
+        <v>745279</v>
       </c>
       <c r="R17" t="n">
-        <v>7107886</v>
+        <v>7107767</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2417,11 +2405,6 @@
           <t>2025-05-18</t>
         </is>
       </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>några kvadratmeter med bladrosetter</t>
-        </is>
-      </c>
       <c r="AD17" t="b">
         <v>0</v>
       </c>
@@ -2435,19 +2418,19 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Patrik Nygren</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Patrik Nygren</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>125223425</v>
+        <v>125227728</v>
       </c>
       <c r="B18" t="n">
         <v>98101</v>
@@ -2495,10 +2478,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>745298</v>
+        <v>745279</v>
       </c>
       <c r="R18" t="n">
-        <v>7107856</v>
+        <v>7107831</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2674,7 +2657,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>125223203</v>
+        <v>125222017</v>
       </c>
       <c r="B20" t="n">
         <v>98101</v>
@@ -2722,10 +2705,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>745293</v>
+        <v>745243</v>
       </c>
       <c r="R20" t="n">
-        <v>7107855</v>
+        <v>7107977</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2785,10 +2768,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>125231948</v>
+        <v>125232024</v>
       </c>
       <c r="B21" t="n">
-        <v>98101</v>
+        <v>91012</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2797,31 +2780,30 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
       <c r="J21" t="inlineStr"/>
       <c r="K21" t="inlineStr"/>
-      <c r="L21" t="inlineStr"/>
       <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
@@ -2829,10 +2811,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>745279</v>
+        <v>745288</v>
       </c>
       <c r="R21" t="n">
-        <v>7107754</v>
+        <v>7107786</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2892,7 +2874,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>125231983</v>
+        <v>125231249</v>
       </c>
       <c r="B22" t="n">
         <v>98101</v>
@@ -2936,10 +2918,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>745279</v>
+        <v>745260</v>
       </c>
       <c r="R22" t="n">
-        <v>7107767</v>
+        <v>7107948</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2999,7 +2981,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>125232212</v>
+        <v>125228040</v>
       </c>
       <c r="B23" t="n">
         <v>98101</v>
@@ -3033,7 +3015,11 @@
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
-      <c r="J23" t="inlineStr"/>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K23" t="inlineStr"/>
       <c r="L23" t="inlineStr"/>
       <c r="N23" t="inlineStr"/>
@@ -3043,7 +3029,7 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>745252</v>
+        <v>745249</v>
       </c>
       <c r="R23" t="n">
         <v>7107940</v>
@@ -3081,6 +3067,11 @@
           <t>2025-05-18</t>
         </is>
       </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>rikligt med bladrosetter!</t>
+        </is>
+      </c>
       <c r="AD23" t="b">
         <v>0</v>
       </c>
@@ -3094,22 +3085,22 @@
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Patrik Nygren</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Patrik Nygren</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>125231105</v>
+        <v>125227446</v>
       </c>
       <c r="B24" t="n">
-        <v>79920</v>
+        <v>98101</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3118,30 +3109,35 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6462</v>
+        <v>220787</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
-      <c r="J24" t="inlineStr"/>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K24" t="inlineStr"/>
+      <c r="L24" t="inlineStr"/>
       <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
@@ -3149,10 +3145,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>745259</v>
+        <v>745280</v>
       </c>
       <c r="R24" t="n">
-        <v>7107964</v>
+        <v>7107802</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3200,22 +3196,22 @@
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Patrik Nygren</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Patrik Nygren</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>125225490</v>
+        <v>125227661</v>
       </c>
       <c r="B25" t="n">
-        <v>91361</v>
+        <v>98101</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3228,30 +3224,31 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>2062</v>
+        <v>220787</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Ulltickeporing</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Skeletocutis brevispora</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
       <c r="J25" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K25" t="inlineStr"/>
+      <c r="L25" t="inlineStr"/>
       <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
@@ -3259,10 +3256,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>745321</v>
+        <v>745280</v>
       </c>
       <c r="R25" t="n">
-        <v>7107841</v>
+        <v>7107827</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3322,10 +3319,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>125231342</v>
+        <v>125231696</v>
       </c>
       <c r="B26" t="n">
-        <v>98101</v>
+        <v>98122</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3334,25 +3331,25 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>220787</v>
+        <v>221952</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3366,10 +3363,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>745267</v>
+        <v>745356</v>
       </c>
       <c r="R26" t="n">
-        <v>7107907</v>
+        <v>7107793</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3429,7 +3426,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>125231888</v>
+        <v>125231838</v>
       </c>
       <c r="B27" t="n">
         <v>98101</v>
@@ -3473,10 +3470,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>745297</v>
+        <v>745310</v>
       </c>
       <c r="R27" t="n">
-        <v>7107757</v>
+        <v>7107765</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3536,10 +3533,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>125222545</v>
+        <v>125232195</v>
       </c>
       <c r="B28" t="n">
-        <v>98101</v>
+        <v>79891</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3548,35 +3545,30 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
-      <c r="J28" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="J28" t="inlineStr"/>
       <c r="K28" t="inlineStr"/>
-      <c r="L28" t="inlineStr"/>
       <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
@@ -3584,10 +3576,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>745294</v>
+        <v>745215</v>
       </c>
       <c r="R28" t="n">
-        <v>7107877</v>
+        <v>7107730</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3635,22 +3627,22 @@
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Patrik Nygren</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Patrik Nygren</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>125227446</v>
+        <v>125222246</v>
       </c>
       <c r="B29" t="n">
-        <v>98101</v>
+        <v>91012</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3659,35 +3651,34 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
       <c r="J29" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K29" t="inlineStr"/>
-      <c r="L29" t="inlineStr"/>
       <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
@@ -3695,10 +3686,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>745280</v>
+        <v>745262</v>
       </c>
       <c r="R29" t="n">
-        <v>7107802</v>
+        <v>7107944</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3758,7 +3749,7 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>125222999</v>
+        <v>125227327</v>
       </c>
       <c r="B30" t="n">
         <v>98101</v>
@@ -3806,10 +3797,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>745290</v>
+        <v>745280</v>
       </c>
       <c r="R30" t="n">
-        <v>7107864</v>
+        <v>7107795</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3869,7 +3860,7 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>125231309</v>
+        <v>125230982</v>
       </c>
       <c r="B31" t="n">
         <v>98101</v>
@@ -3913,10 +3904,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>745268</v>
+        <v>745259</v>
       </c>
       <c r="R31" t="n">
-        <v>7107926</v>
+        <v>7107964</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3976,10 +3967,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>125231464</v>
+        <v>125222288</v>
       </c>
       <c r="B32" t="n">
-        <v>79795</v>
+        <v>98101</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -3988,30 +3979,35 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6456</v>
+        <v>220787</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
-      <c r="J32" t="inlineStr"/>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K32" t="inlineStr"/>
+      <c r="L32" t="inlineStr"/>
       <c r="N32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
@@ -4019,10 +4015,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>745287</v>
+        <v>745266</v>
       </c>
       <c r="R32" t="n">
-        <v>7107886</v>
+        <v>7107910</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4070,22 +4066,22 @@
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Patrik Nygren</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Patrik Nygren</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>125226477</v>
+        <v>125231545</v>
       </c>
       <c r="B33" t="n">
-        <v>91012</v>
+        <v>79795</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4094,33 +4090,29 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>1202</v>
+        <v>6456</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
-      <c r="J33" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+      <c r="J33" t="inlineStr"/>
       <c r="K33" t="inlineStr"/>
       <c r="N33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
@@ -4129,10 +4121,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>745445</v>
+        <v>745310</v>
       </c>
       <c r="R33" t="n">
-        <v>7107841</v>
+        <v>7107876</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4180,22 +4172,22 @@
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Patrik Nygren</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Patrik Nygren</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>125225686</v>
+        <v>125227901</v>
       </c>
       <c r="B34" t="n">
-        <v>91012</v>
+        <v>98101</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4204,34 +4196,35 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
       <c r="J34" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K34" t="inlineStr"/>
+      <c r="L34" t="inlineStr"/>
       <c r="N34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
@@ -4239,10 +4232,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>745321</v>
+        <v>745280</v>
       </c>
       <c r="R34" t="n">
-        <v>7107841</v>
+        <v>7107886</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4302,10 +4295,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>125228007</v>
+        <v>125231948</v>
       </c>
       <c r="B35" t="n">
-        <v>57529</v>
+        <v>98101</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4314,35 +4307,31 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
+      <c r="J35" t="inlineStr"/>
       <c r="K35" t="inlineStr"/>
       <c r="L35" t="inlineStr"/>
-      <c r="M35" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
@@ -4350,10 +4339,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>745249</v>
+        <v>745279</v>
       </c>
       <c r="R35" t="n">
-        <v>7107940</v>
+        <v>7107754</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4388,36 +4377,32 @@
           <t>2025-05-18</t>
         </is>
       </c>
-      <c r="AC35" t="inlineStr">
-        <is>
-          <t>hackat hål i gran</t>
-        </is>
-      </c>
       <c r="AD35" t="b">
         <v>0</v>
       </c>
       <c r="AE35" t="b">
         <v>0</v>
       </c>
+      <c r="AF35" t="inlineStr"/>
       <c r="AG35" t="b">
         <v>0</v>
       </c>
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Patrik Nygren</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Patrik Nygren</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>125231545</v>
+        <v>125231464</v>
       </c>
       <c r="B36" t="n">
         <v>79795</v>
@@ -4460,10 +4445,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>745310</v>
+        <v>745287</v>
       </c>
       <c r="R36" t="n">
-        <v>7107876</v>
+        <v>7107886</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4523,10 +4508,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>125227797</v>
+        <v>125226206</v>
       </c>
       <c r="B37" t="n">
-        <v>98101</v>
+        <v>91012</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4535,35 +4520,34 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
       <c r="J37" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K37" t="inlineStr"/>
-      <c r="L37" t="inlineStr"/>
       <c r="N37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
@@ -4571,10 +4555,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>745277</v>
+        <v>745327</v>
       </c>
       <c r="R37" t="n">
-        <v>7107838</v>
+        <v>7107827</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4634,7 +4618,7 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>125230982</v>
+        <v>125222545</v>
       </c>
       <c r="B38" t="n">
         <v>98101</v>
@@ -4668,7 +4652,11 @@
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
-      <c r="J38" t="inlineStr"/>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K38" t="inlineStr"/>
       <c r="L38" t="inlineStr"/>
       <c r="N38" t="inlineStr"/>
@@ -4678,10 +4666,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>745259</v>
+        <v>745294</v>
       </c>
       <c r="R38" t="n">
-        <v>7107964</v>
+        <v>7107877</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4729,22 +4717,22 @@
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Patrik Nygren</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Patrik Nygren</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>125222017</v>
+        <v>125232181</v>
       </c>
       <c r="B39" t="n">
-        <v>98101</v>
+        <v>57529</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4753,35 +4741,31 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
-      <c r="J39" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
       <c r="K39" t="inlineStr"/>
       <c r="L39" t="inlineStr"/>
+      <c r="M39" t="inlineStr"/>
       <c r="N39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
@@ -4789,10 +4773,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>745243</v>
+        <v>745227</v>
       </c>
       <c r="R39" t="n">
-        <v>7107977</v>
+        <v>7107774</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4833,29 +4817,28 @@
       <c r="AE39" t="b">
         <v>0</v>
       </c>
-      <c r="AF39" t="inlineStr"/>
       <c r="AG39" t="b">
         <v>0</v>
       </c>
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Patrik Nygren</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Patrik Nygren</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>125231696</v>
+        <v>125231779</v>
       </c>
       <c r="B40" t="n">
-        <v>98122</v>
+        <v>79920</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4868,27 +4851,26 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>221952</v>
+        <v>6462</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
       <c r="J40" t="inlineStr"/>
       <c r="K40" t="inlineStr"/>
-      <c r="L40" t="inlineStr"/>
       <c r="N40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
@@ -4896,10 +4878,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>745356</v>
+        <v>745323</v>
       </c>
       <c r="R40" t="n">
-        <v>7107793</v>
+        <v>7107772</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4959,10 +4941,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>125231658</v>
+        <v>125231888</v>
       </c>
       <c r="B41" t="n">
-        <v>90977</v>
+        <v>98101</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -4971,30 +4953,31 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>5447</v>
+        <v>220787</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
       <c r="J41" t="inlineStr"/>
       <c r="K41" t="inlineStr"/>
+      <c r="L41" t="inlineStr"/>
       <c r="N41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
@@ -5002,10 +4985,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>745405</v>
+        <v>745297</v>
       </c>
       <c r="R41" t="n">
-        <v>7107837</v>
+        <v>7107757</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5065,7 +5048,7 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>125232024</v>
+        <v>125222055</v>
       </c>
       <c r="B42" t="n">
         <v>91012</v>
@@ -5099,7 +5082,11 @@
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
-      <c r="J42" t="inlineStr"/>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K42" t="inlineStr"/>
       <c r="N42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
@@ -5108,10 +5095,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>745288</v>
+        <v>745262</v>
       </c>
       <c r="R42" t="n">
-        <v>7107786</v>
+        <v>7107948</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5159,19 +5146,19 @@
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Patrik Nygren</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Patrik Nygren</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>125225982</v>
+        <v>125232212</v>
       </c>
       <c r="B43" t="n">
         <v>98101</v>
@@ -5205,11 +5192,7 @@
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
-      <c r="J43" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="J43" t="inlineStr"/>
       <c r="K43" t="inlineStr"/>
       <c r="L43" t="inlineStr"/>
       <c r="N43" t="inlineStr"/>
@@ -5219,10 +5202,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>745327</v>
+        <v>745252</v>
       </c>
       <c r="R43" t="n">
-        <v>7107834</v>
+        <v>7107940</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5270,19 +5253,19 @@
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Patrik Nygren</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Patrik Nygren</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>125222288</v>
+        <v>125222999</v>
       </c>
       <c r="B44" t="n">
         <v>98101</v>
@@ -5330,10 +5313,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>745266</v>
+        <v>745290</v>
       </c>
       <c r="R44" t="n">
-        <v>7107910</v>
+        <v>7107864</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5393,10 +5376,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>125232181</v>
+        <v>125231658</v>
       </c>
       <c r="B45" t="n">
-        <v>57529</v>
+        <v>90977</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5405,31 +5388,30 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>100049</v>
+        <v>5447</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
+      <c r="J45" t="inlineStr"/>
       <c r="K45" t="inlineStr"/>
-      <c r="L45" t="inlineStr"/>
-      <c r="M45" t="inlineStr"/>
       <c r="N45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
@@ -5437,10 +5419,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>745227</v>
+        <v>745405</v>
       </c>
       <c r="R45" t="n">
-        <v>7107774</v>
+        <v>7107837</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5481,6 +5463,7 @@
       <c r="AE45" t="b">
         <v>0</v>
       </c>
+      <c r="AF45" t="inlineStr"/>
       <c r="AG45" t="b">
         <v>0</v>
       </c>
@@ -5499,10 +5482,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>125232195</v>
+        <v>125228007</v>
       </c>
       <c r="B46" t="n">
-        <v>79891</v>
+        <v>57529</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5515,26 +5498,31 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6458</v>
+        <v>100049</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
-      <c r="J46" t="inlineStr"/>
       <c r="K46" t="inlineStr"/>
+      <c r="L46" t="inlineStr"/>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
@@ -5542,10 +5530,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>745215</v>
+        <v>745249</v>
       </c>
       <c r="R46" t="n">
-        <v>7107730</v>
+        <v>7107940</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5580,32 +5568,36 @@
           <t>2025-05-18</t>
         </is>
       </c>
+      <c r="AC46" t="inlineStr">
+        <is>
+          <t>hackat hål i gran</t>
+        </is>
+      </c>
       <c r="AD46" t="b">
         <v>0</v>
       </c>
       <c r="AE46" t="b">
         <v>0</v>
       </c>
-      <c r="AF46" t="inlineStr"/>
       <c r="AG46" t="b">
         <v>0</v>
       </c>
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Patrik Nygren</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Patrik Nygren</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>125226206</v>
+        <v>125226477</v>
       </c>
       <c r="B47" t="n">
         <v>91012</v>
@@ -5652,10 +5644,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>745327</v>
+        <v>745445</v>
       </c>
       <c r="R47" t="n">
-        <v>7107827</v>
+        <v>7107841</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5715,10 +5707,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>125231249</v>
+        <v>125227847</v>
       </c>
       <c r="B48" t="n">
-        <v>98101</v>
+        <v>57529</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5727,31 +5719,35 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
-      <c r="J48" t="inlineStr"/>
       <c r="K48" t="inlineStr"/>
       <c r="L48" t="inlineStr"/>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
@@ -5759,10 +5755,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>745260</v>
+        <v>745285</v>
       </c>
       <c r="R48" t="n">
-        <v>7107948</v>
+        <v>7107862</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5797,35 +5793,39 @@
           <t>2025-05-18</t>
         </is>
       </c>
+      <c r="AC48" t="inlineStr">
+        <is>
+          <t>hack i död gran</t>
+        </is>
+      </c>
       <c r="AD48" t="b">
         <v>0</v>
       </c>
       <c r="AE48" t="b">
         <v>0</v>
       </c>
-      <c r="AF48" t="inlineStr"/>
       <c r="AG48" t="b">
         <v>0</v>
       </c>
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Patrik Nygren</t>
         </is>
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Patrik Nygren</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>125231838</v>
+        <v>125231618</v>
       </c>
       <c r="B49" t="n">
-        <v>98101</v>
+        <v>79795</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -5834,31 +5834,30 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>220787</v>
+        <v>6456</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
       <c r="J49" t="inlineStr"/>
       <c r="K49" t="inlineStr"/>
-      <c r="L49" t="inlineStr"/>
       <c r="N49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
@@ -5866,10 +5865,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>745310</v>
+        <v>745381</v>
       </c>
       <c r="R49" t="n">
-        <v>7107765</v>
+        <v>7107841</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5929,10 +5928,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>125222246</v>
+        <v>125223203</v>
       </c>
       <c r="B50" t="n">
-        <v>91012</v>
+        <v>98101</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -5941,34 +5940,35 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
       <c r="J50" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K50" t="inlineStr"/>
+      <c r="L50" t="inlineStr"/>
       <c r="N50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
@@ -5976,10 +5976,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>745262</v>
+        <v>745293</v>
       </c>
       <c r="R50" t="n">
-        <v>7107944</v>
+        <v>7107855</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>

--- a/artfynd/A 53969-2024 artfynd.xlsx
+++ b/artfynd/A 53969-2024 artfynd.xlsx
@@ -1553,10 +1553,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>125222083</v>
+        <v>125226783</v>
       </c>
       <c r="B10" t="n">
-        <v>91361</v>
+        <v>98101</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1569,30 +1569,31 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>2062</v>
+        <v>220787</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Ulltickeporing</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Skeletocutis brevispora</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="J10" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
@@ -1600,10 +1601,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>745262</v>
+        <v>745294</v>
       </c>
       <c r="R10" t="n">
-        <v>7107946</v>
+        <v>7107772</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1663,7 +1664,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>125226783</v>
+        <v>125223425</v>
       </c>
       <c r="B11" t="n">
         <v>98101</v>
@@ -1711,10 +1712,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>745294</v>
+        <v>745298</v>
       </c>
       <c r="R11" t="n">
-        <v>7107772</v>
+        <v>7107856</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1774,7 +1775,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>125223425</v>
+        <v>125231342</v>
       </c>
       <c r="B12" t="n">
         <v>98101</v>
@@ -1808,11 +1809,7 @@
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="J12" t="inlineStr"/>
       <c r="K12" t="inlineStr"/>
       <c r="L12" t="inlineStr"/>
       <c r="N12" t="inlineStr"/>
@@ -1822,10 +1819,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>745298</v>
+        <v>745267</v>
       </c>
       <c r="R12" t="n">
-        <v>7107856</v>
+        <v>7107907</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1873,22 +1870,22 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Patrik Nygren</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Patrik Nygren</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>125231342</v>
+        <v>125222083</v>
       </c>
       <c r="B13" t="n">
-        <v>98101</v>
+        <v>91361</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1901,27 +1898,30 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>220787</v>
+        <v>2062</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ulltickeporing</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Skeletocutis brevispora</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="J13" t="inlineStr"/>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K13" t="inlineStr"/>
-      <c r="L13" t="inlineStr"/>
       <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
@@ -1929,10 +1929,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>745267</v>
+        <v>745262</v>
       </c>
       <c r="R13" t="n">
-        <v>7107907</v>
+        <v>7107946</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1980,12 +1980,12 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Patrik Nygren</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Patrik Nygren</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
@@ -2768,10 +2768,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>125232024</v>
+        <v>125231249</v>
       </c>
       <c r="B21" t="n">
-        <v>91012</v>
+        <v>98101</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2780,30 +2780,31 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
       <c r="J21" t="inlineStr"/>
       <c r="K21" t="inlineStr"/>
+      <c r="L21" t="inlineStr"/>
       <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
@@ -2811,10 +2812,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>745288</v>
+        <v>745260</v>
       </c>
       <c r="R21" t="n">
-        <v>7107786</v>
+        <v>7107948</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2874,7 +2875,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>125231249</v>
+        <v>125228040</v>
       </c>
       <c r="B22" t="n">
         <v>98101</v>
@@ -2908,7 +2909,11 @@
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
-      <c r="J22" t="inlineStr"/>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K22" t="inlineStr"/>
       <c r="L22" t="inlineStr"/>
       <c r="N22" t="inlineStr"/>
@@ -2918,10 +2923,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>745260</v>
+        <v>745249</v>
       </c>
       <c r="R22" t="n">
-        <v>7107948</v>
+        <v>7107940</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2956,6 +2961,11 @@
           <t>2025-05-18</t>
         </is>
       </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>rikligt med bladrosetter!</t>
+        </is>
+      </c>
       <c r="AD22" t="b">
         <v>0</v>
       </c>
@@ -2969,22 +2979,22 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Patrik Nygren</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Patrik Nygren</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>125228040</v>
+        <v>125232024</v>
       </c>
       <c r="B23" t="n">
-        <v>98101</v>
+        <v>91012</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2993,35 +3003,30 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
-      <c r="J23" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="J23" t="inlineStr"/>
       <c r="K23" t="inlineStr"/>
-      <c r="L23" t="inlineStr"/>
       <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
@@ -3029,10 +3034,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>745249</v>
+        <v>745288</v>
       </c>
       <c r="R23" t="n">
-        <v>7107940</v>
+        <v>7107786</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3067,11 +3072,6 @@
           <t>2025-05-18</t>
         </is>
       </c>
-      <c r="AC23" t="inlineStr">
-        <is>
-          <t>rikligt med bladrosetter!</t>
-        </is>
-      </c>
       <c r="AD23" t="b">
         <v>0</v>
       </c>
@@ -3085,12 +3085,12 @@
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Patrik Nygren</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Patrik Nygren</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
@@ -4402,10 +4402,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>125231464</v>
+        <v>125222545</v>
       </c>
       <c r="B36" t="n">
-        <v>79795</v>
+        <v>98101</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4414,30 +4414,35 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6456</v>
+        <v>220787</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
-      <c r="J36" t="inlineStr"/>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K36" t="inlineStr"/>
+      <c r="L36" t="inlineStr"/>
       <c r="N36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
@@ -4445,10 +4450,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>745287</v>
+        <v>745294</v>
       </c>
       <c r="R36" t="n">
-        <v>7107886</v>
+        <v>7107877</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4496,12 +4501,12 @@
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Patrik Nygren</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Patrik Nygren</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
@@ -4618,10 +4623,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>125222545</v>
+        <v>125231464</v>
       </c>
       <c r="B38" t="n">
-        <v>98101</v>
+        <v>79795</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4630,35 +4635,30 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>220787</v>
+        <v>6456</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
-      <c r="J38" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="J38" t="inlineStr"/>
       <c r="K38" t="inlineStr"/>
-      <c r="L38" t="inlineStr"/>
       <c r="N38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
@@ -4666,10 +4666,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>745294</v>
+        <v>745287</v>
       </c>
       <c r="R38" t="n">
-        <v>7107877</v>
+        <v>7107886</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4717,12 +4717,12 @@
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Patrik Nygren</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Patrik Nygren</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
@@ -5707,10 +5707,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>125227847</v>
+        <v>125231618</v>
       </c>
       <c r="B48" t="n">
-        <v>57529</v>
+        <v>79795</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5719,35 +5719,30 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>100049</v>
+        <v>6456</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
+      <c r="J48" t="inlineStr"/>
       <c r="K48" t="inlineStr"/>
-      <c r="L48" t="inlineStr"/>
-      <c r="M48" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
@@ -5755,10 +5750,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>745285</v>
+        <v>745381</v>
       </c>
       <c r="R48" t="n">
-        <v>7107862</v>
+        <v>7107841</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5793,39 +5788,35 @@
           <t>2025-05-18</t>
         </is>
       </c>
-      <c r="AC48" t="inlineStr">
-        <is>
-          <t>hack i död gran</t>
-        </is>
-      </c>
       <c r="AD48" t="b">
         <v>0</v>
       </c>
       <c r="AE48" t="b">
         <v>0</v>
       </c>
+      <c r="AF48" t="inlineStr"/>
       <c r="AG48" t="b">
         <v>0</v>
       </c>
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>Patrik Nygren</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>Patrik Nygren</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>125231618</v>
+        <v>125223203</v>
       </c>
       <c r="B49" t="n">
-        <v>79795</v>
+        <v>98101</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -5834,30 +5825,35 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6456</v>
+        <v>220787</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
-      <c r="J49" t="inlineStr"/>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K49" t="inlineStr"/>
+      <c r="L49" t="inlineStr"/>
       <c r="N49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
@@ -5865,10 +5861,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>745381</v>
+        <v>745293</v>
       </c>
       <c r="R49" t="n">
-        <v>7107841</v>
+        <v>7107855</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5916,22 +5912,22 @@
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Patrik Nygren</t>
         </is>
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Patrik Nygren</t>
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>125223203</v>
+        <v>125227847</v>
       </c>
       <c r="B50" t="n">
-        <v>98101</v>
+        <v>57529</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -5940,35 +5936,35 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
-      <c r="J50" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
       <c r="K50" t="inlineStr"/>
       <c r="L50" t="inlineStr"/>
+      <c r="M50" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
@@ -5976,10 +5972,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>745293</v>
+        <v>745285</v>
       </c>
       <c r="R50" t="n">
-        <v>7107855</v>
+        <v>7107862</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -6014,13 +6010,17 @@
           <t>2025-05-18</t>
         </is>
       </c>
+      <c r="AC50" t="inlineStr">
+        <is>
+          <t>hack i död gran</t>
+        </is>
+      </c>
       <c r="AD50" t="b">
         <v>0</v>
       </c>
       <c r="AE50" t="b">
         <v>0</v>
       </c>
-      <c r="AF50" t="inlineStr"/>
       <c r="AG50" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 53969-2024 artfynd.xlsx
+++ b/artfynd/A 53969-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>125225686</v>
+        <v>125223590</v>
       </c>
       <c r="B2" t="n">
-        <v>91012</v>
+        <v>98101</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,34 +687,35 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="J2" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -722,10 +723,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>745321</v>
+        <v>745299</v>
       </c>
       <c r="R2" t="n">
-        <v>7107841</v>
+        <v>7107851</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -785,10 +786,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>125225982</v>
+        <v>125225686</v>
       </c>
       <c r="B3" t="n">
-        <v>98101</v>
+        <v>91012</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -797,35 +798,34 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="J3" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -833,10 +833,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>745327</v>
+        <v>745321</v>
       </c>
       <c r="R3" t="n">
-        <v>7107834</v>
+        <v>7107841</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -896,7 +896,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>125227797</v>
+        <v>125231983</v>
       </c>
       <c r="B4" t="n">
         <v>98101</v>
@@ -930,11 +930,7 @@
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
@@ -944,10 +940,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>745277</v>
+        <v>745279</v>
       </c>
       <c r="R4" t="n">
-        <v>7107838</v>
+        <v>7107767</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -995,22 +991,22 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Patrik Nygren</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Patrik Nygren</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>125231105</v>
+        <v>125227446</v>
       </c>
       <c r="B5" t="n">
-        <v>79920</v>
+        <v>98101</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1019,30 +1015,35 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6462</v>
+        <v>220787</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1050,10 +1051,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>745259</v>
+        <v>745280</v>
       </c>
       <c r="R5" t="n">
-        <v>7107964</v>
+        <v>7107802</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1101,22 +1102,22 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Patrik Nygren</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Patrik Nygren</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>125222404</v>
+        <v>125222055</v>
       </c>
       <c r="B6" t="n">
-        <v>98101</v>
+        <v>91012</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1125,35 +1126,34 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="J6" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1161,10 +1161,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>745290</v>
+        <v>745262</v>
       </c>
       <c r="R6" t="n">
-        <v>7107886</v>
+        <v>7107948</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1197,11 +1197,6 @@
       <c r="AA6" t="inlineStr">
         <is>
           <t>2025-05-18</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>några kvadratmeter med bladrosetter</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1229,10 +1224,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>125223590</v>
+        <v>125232024</v>
       </c>
       <c r="B7" t="n">
-        <v>98101</v>
+        <v>91012</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1241,35 +1236,30 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
@@ -1277,10 +1267,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>745299</v>
+        <v>745288</v>
       </c>
       <c r="R7" t="n">
-        <v>7107851</v>
+        <v>7107786</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1328,19 +1318,19 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Patrik Nygren</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Patrik Nygren</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>125231309</v>
+        <v>125228040</v>
       </c>
       <c r="B8" t="n">
         <v>98101</v>
@@ -1374,7 +1364,11 @@
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr"/>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K8" t="inlineStr"/>
       <c r="L8" t="inlineStr"/>
       <c r="N8" t="inlineStr"/>
@@ -1384,10 +1378,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>745268</v>
+        <v>745249</v>
       </c>
       <c r="R8" t="n">
-        <v>7107926</v>
+        <v>7107940</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1422,6 +1416,11 @@
           <t>2025-05-18</t>
         </is>
       </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>rikligt med bladrosetter!</t>
+        </is>
+      </c>
       <c r="AD8" t="b">
         <v>0</v>
       </c>
@@ -1435,22 +1434,22 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Patrik Nygren</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Patrik Nygren</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>125232283</v>
+        <v>125225490</v>
       </c>
       <c r="B9" t="n">
-        <v>57883</v>
+        <v>91361</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1459,31 +1458,34 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>103015</v>
+        <v>2062</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Ulltickeporing</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Skeletocutis brevispora</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr"/>
-      <c r="M9" t="inlineStr"/>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
@@ -1491,13 +1493,13 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>745254</v>
+        <v>745321</v>
       </c>
       <c r="R9" t="n">
-        <v>7107972</v>
+        <v>7107841</v>
       </c>
       <c r="S9" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1535,25 +1537,26 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
+      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Patrik Nygren</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Patrik Nygren</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>125226783</v>
+        <v>125232212</v>
       </c>
       <c r="B10" t="n">
         <v>98101</v>
@@ -1587,11 +1590,7 @@
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="J10" t="inlineStr"/>
       <c r="K10" t="inlineStr"/>
       <c r="L10" t="inlineStr"/>
       <c r="N10" t="inlineStr"/>
@@ -1601,10 +1600,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>745294</v>
+        <v>745252</v>
       </c>
       <c r="R10" t="n">
-        <v>7107772</v>
+        <v>7107940</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1652,19 +1651,19 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Patrik Nygren</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Patrik Nygren</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>125223425</v>
+        <v>125223203</v>
       </c>
       <c r="B11" t="n">
         <v>98101</v>
@@ -1712,10 +1711,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>745298</v>
+        <v>745293</v>
       </c>
       <c r="R11" t="n">
-        <v>7107856</v>
+        <v>7107855</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1775,10 +1774,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>125231342</v>
+        <v>125231545</v>
       </c>
       <c r="B12" t="n">
-        <v>98101</v>
+        <v>79795</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1787,31 +1786,30 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>220787</v>
+        <v>6456</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
       <c r="J12" t="inlineStr"/>
       <c r="K12" t="inlineStr"/>
-      <c r="L12" t="inlineStr"/>
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
@@ -1819,10 +1817,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>745267</v>
+        <v>745310</v>
       </c>
       <c r="R12" t="n">
-        <v>7107907</v>
+        <v>7107876</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1882,10 +1880,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>125222083</v>
+        <v>125222017</v>
       </c>
       <c r="B13" t="n">
-        <v>91361</v>
+        <v>98101</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1898,30 +1896,31 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>2062</v>
+        <v>220787</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Ulltickeporing</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Skeletocutis brevispora</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
       <c r="J13" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
       <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
@@ -1929,10 +1928,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>745262</v>
+        <v>745243</v>
       </c>
       <c r="R13" t="n">
-        <v>7107946</v>
+        <v>7107977</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1992,10 +1991,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>125225490</v>
+        <v>125222999</v>
       </c>
       <c r="B14" t="n">
-        <v>91361</v>
+        <v>98101</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2008,30 +2007,31 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>2062</v>
+        <v>220787</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Ulltickeporing</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Skeletocutis brevispora</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
       <c r="J14" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
       <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
@@ -2039,10 +2039,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>745321</v>
+        <v>745290</v>
       </c>
       <c r="R14" t="n">
-        <v>7107841</v>
+        <v>7107864</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2102,10 +2102,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>125222073</v>
+        <v>125232195</v>
       </c>
       <c r="B15" t="n">
-        <v>91012</v>
+        <v>79891</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2118,29 +2118,25 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+      <c r="J15" t="inlineStr"/>
       <c r="K15" t="inlineStr"/>
       <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
@@ -2149,10 +2145,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>745262</v>
+        <v>745215</v>
       </c>
       <c r="R15" t="n">
-        <v>7107946</v>
+        <v>7107730</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2200,22 +2196,22 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Patrik Nygren</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Patrik Nygren</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>125222754</v>
+        <v>125227847</v>
       </c>
       <c r="B16" t="n">
-        <v>98101</v>
+        <v>57529</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2224,35 +2220,35 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
-      <c r="J16" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
       <c r="K16" t="inlineStr"/>
       <c r="L16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
@@ -2260,10 +2256,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>745306</v>
+        <v>745285</v>
       </c>
       <c r="R16" t="n">
-        <v>7107877</v>
+        <v>7107862</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2298,13 +2294,17 @@
           <t>2025-05-18</t>
         </is>
       </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>hack i död gran</t>
+        </is>
+      </c>
       <c r="AD16" t="b">
         <v>0</v>
       </c>
       <c r="AE16" t="b">
         <v>0</v>
       </c>
-      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>
@@ -2323,7 +2323,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>125231983</v>
+        <v>125225982</v>
       </c>
       <c r="B17" t="n">
         <v>98101</v>
@@ -2357,7 +2357,11 @@
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
-      <c r="J17" t="inlineStr"/>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K17" t="inlineStr"/>
       <c r="L17" t="inlineStr"/>
       <c r="N17" t="inlineStr"/>
@@ -2367,10 +2371,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>745279</v>
+        <v>745327</v>
       </c>
       <c r="R17" t="n">
-        <v>7107767</v>
+        <v>7107834</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2418,19 +2422,19 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Patrik Nygren</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Patrik Nygren</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>125227728</v>
+        <v>125231309</v>
       </c>
       <c r="B18" t="n">
         <v>98101</v>
@@ -2464,11 +2468,7 @@
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
-      <c r="J18" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="J18" t="inlineStr"/>
       <c r="K18" t="inlineStr"/>
       <c r="L18" t="inlineStr"/>
       <c r="N18" t="inlineStr"/>
@@ -2478,10 +2478,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>745279</v>
+        <v>745268</v>
       </c>
       <c r="R18" t="n">
-        <v>7107831</v>
+        <v>7107926</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2529,22 +2529,22 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Patrik Nygren</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Patrik Nygren</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>125223807</v>
+        <v>125231658</v>
       </c>
       <c r="B19" t="n">
-        <v>98101</v>
+        <v>90977</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2553,35 +2553,30 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>220787</v>
+        <v>5447</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
-      <c r="J19" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="J19" t="inlineStr"/>
       <c r="K19" t="inlineStr"/>
-      <c r="L19" t="inlineStr"/>
       <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
@@ -2589,10 +2584,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>745315</v>
+        <v>745405</v>
       </c>
       <c r="R19" t="n">
-        <v>7107851</v>
+        <v>7107837</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2627,11 +2622,6 @@
           <t>2025-05-18</t>
         </is>
       </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>Rikligt med bladrosetter!</t>
-        </is>
-      </c>
       <c r="AD19" t="b">
         <v>0</v>
       </c>
@@ -2645,22 +2635,22 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Patrik Nygren</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Patrik Nygren</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>125222017</v>
+        <v>125231696</v>
       </c>
       <c r="B20" t="n">
-        <v>98101</v>
+        <v>98122</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2669,33 +2659,29 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>220787</v>
+        <v>221952</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
-      <c r="J20" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="J20" t="inlineStr"/>
       <c r="K20" t="inlineStr"/>
       <c r="L20" t="inlineStr"/>
       <c r="N20" t="inlineStr"/>
@@ -2705,10 +2691,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>745243</v>
+        <v>745356</v>
       </c>
       <c r="R20" t="n">
-        <v>7107977</v>
+        <v>7107793</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2756,19 +2742,19 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Patrik Nygren</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Patrik Nygren</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>125231249</v>
+        <v>125231948</v>
       </c>
       <c r="B21" t="n">
         <v>98101</v>
@@ -2812,10 +2798,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>745260</v>
+        <v>745279</v>
       </c>
       <c r="R21" t="n">
-        <v>7107948</v>
+        <v>7107754</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2875,10 +2861,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>125228040</v>
+        <v>125231779</v>
       </c>
       <c r="B22" t="n">
-        <v>98101</v>
+        <v>79920</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2887,35 +2873,30 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>220787</v>
+        <v>6462</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
-      <c r="J22" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="J22" t="inlineStr"/>
       <c r="K22" t="inlineStr"/>
-      <c r="L22" t="inlineStr"/>
       <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
@@ -2923,10 +2904,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>745249</v>
+        <v>745323</v>
       </c>
       <c r="R22" t="n">
-        <v>7107940</v>
+        <v>7107772</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2961,11 +2942,6 @@
           <t>2025-05-18</t>
         </is>
       </c>
-      <c r="AC22" t="inlineStr">
-        <is>
-          <t>rikligt med bladrosetter!</t>
-        </is>
-      </c>
       <c r="AD22" t="b">
         <v>0</v>
       </c>
@@ -2979,22 +2955,22 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Patrik Nygren</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Patrik Nygren</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>125232024</v>
+        <v>125231105</v>
       </c>
       <c r="B23" t="n">
-        <v>91012</v>
+        <v>79920</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3003,25 +2979,25 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>1202</v>
+        <v>6462</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -3034,10 +3010,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>745288</v>
+        <v>745259</v>
       </c>
       <c r="R23" t="n">
-        <v>7107786</v>
+        <v>7107964</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3097,10 +3073,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>125227446</v>
+        <v>125231464</v>
       </c>
       <c r="B24" t="n">
-        <v>98101</v>
+        <v>79795</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3109,35 +3085,30 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>220787</v>
+        <v>6456</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
-      <c r="J24" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="J24" t="inlineStr"/>
       <c r="K24" t="inlineStr"/>
-      <c r="L24" t="inlineStr"/>
       <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
@@ -3145,10 +3116,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>745280</v>
+        <v>745287</v>
       </c>
       <c r="R24" t="n">
-        <v>7107802</v>
+        <v>7107886</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3196,19 +3167,19 @@
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Patrik Nygren</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Patrik Nygren</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>125227661</v>
+        <v>125227797</v>
       </c>
       <c r="B25" t="n">
         <v>98101</v>
@@ -3256,10 +3227,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>745280</v>
+        <v>745277</v>
       </c>
       <c r="R25" t="n">
-        <v>7107827</v>
+        <v>7107838</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3319,10 +3290,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>125231696</v>
+        <v>125228007</v>
       </c>
       <c r="B26" t="n">
-        <v>98122</v>
+        <v>57529</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3331,31 +3302,35 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>221952</v>
+        <v>100049</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
-      <c r="J26" t="inlineStr"/>
       <c r="K26" t="inlineStr"/>
       <c r="L26" t="inlineStr"/>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
@@ -3363,10 +3338,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>745356</v>
+        <v>745249</v>
       </c>
       <c r="R26" t="n">
-        <v>7107793</v>
+        <v>7107940</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3401,32 +3376,36 @@
           <t>2025-05-18</t>
         </is>
       </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>hackat hål i gran</t>
+        </is>
+      </c>
       <c r="AD26" t="b">
         <v>0</v>
       </c>
       <c r="AE26" t="b">
         <v>0</v>
       </c>
-      <c r="AF26" t="inlineStr"/>
       <c r="AG26" t="b">
         <v>0</v>
       </c>
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Patrik Nygren</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Patrik Nygren</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>125231838</v>
+        <v>125222361</v>
       </c>
       <c r="B27" t="n">
         <v>98101</v>
@@ -3460,7 +3439,11 @@
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
-      <c r="J27" t="inlineStr"/>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K27" t="inlineStr"/>
       <c r="L27" t="inlineStr"/>
       <c r="N27" t="inlineStr"/>
@@ -3470,10 +3453,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>745310</v>
+        <v>745280</v>
       </c>
       <c r="R27" t="n">
-        <v>7107765</v>
+        <v>7107886</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3521,22 +3504,22 @@
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Patrik Nygren</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Patrik Nygren</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>125232195</v>
+        <v>125222545</v>
       </c>
       <c r="B28" t="n">
-        <v>79891</v>
+        <v>98101</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3545,30 +3528,35 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
-      <c r="J28" t="inlineStr"/>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K28" t="inlineStr"/>
+      <c r="L28" t="inlineStr"/>
       <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
@@ -3576,10 +3564,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>745215</v>
+        <v>745294</v>
       </c>
       <c r="R28" t="n">
-        <v>7107730</v>
+        <v>7107877</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3627,22 +3615,22 @@
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Patrik Nygren</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Patrik Nygren</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>125222246</v>
+        <v>125223425</v>
       </c>
       <c r="B29" t="n">
-        <v>91012</v>
+        <v>98101</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3651,34 +3639,35 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
       <c r="J29" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K29" t="inlineStr"/>
+      <c r="L29" t="inlineStr"/>
       <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
@@ -3686,10 +3675,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>745262</v>
+        <v>745298</v>
       </c>
       <c r="R29" t="n">
-        <v>7107944</v>
+        <v>7107856</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3749,7 +3738,7 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>125227327</v>
+        <v>125223807</v>
       </c>
       <c r="B30" t="n">
         <v>98101</v>
@@ -3797,10 +3786,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>745280</v>
+        <v>745315</v>
       </c>
       <c r="R30" t="n">
-        <v>7107795</v>
+        <v>7107851</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3833,6 +3822,11 @@
       <c r="AA30" t="inlineStr">
         <is>
           <t>2025-05-18</t>
+        </is>
+      </c>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>Rikligt med bladrosetter!</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3860,10 +3854,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>125230982</v>
+        <v>125222083</v>
       </c>
       <c r="B31" t="n">
-        <v>98101</v>
+        <v>91361</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3876,27 +3870,30 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>220787</v>
+        <v>2062</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ulltickeporing</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Skeletocutis brevispora</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
-      <c r="J31" t="inlineStr"/>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K31" t="inlineStr"/>
-      <c r="L31" t="inlineStr"/>
       <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
@@ -3904,10 +3901,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>745259</v>
+        <v>745262</v>
       </c>
       <c r="R31" t="n">
-        <v>7107964</v>
+        <v>7107946</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3955,22 +3952,22 @@
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Patrik Nygren</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Patrik Nygren</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>125222288</v>
+        <v>125226477</v>
       </c>
       <c r="B32" t="n">
-        <v>98101</v>
+        <v>91012</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -3979,35 +3976,34 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
       <c r="J32" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K32" t="inlineStr"/>
-      <c r="L32" t="inlineStr"/>
       <c r="N32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
@@ -4015,10 +4011,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>745266</v>
+        <v>745445</v>
       </c>
       <c r="R32" t="n">
-        <v>7107910</v>
+        <v>7107841</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4078,10 +4074,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>125231545</v>
+        <v>125227728</v>
       </c>
       <c r="B33" t="n">
-        <v>79795</v>
+        <v>98101</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4090,30 +4086,35 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6456</v>
+        <v>220787</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
-      <c r="J33" t="inlineStr"/>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K33" t="inlineStr"/>
+      <c r="L33" t="inlineStr"/>
       <c r="N33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
@@ -4121,10 +4122,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>745310</v>
+        <v>745279</v>
       </c>
       <c r="R33" t="n">
-        <v>7107876</v>
+        <v>7107831</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4172,19 +4173,19 @@
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Patrik Nygren</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Patrik Nygren</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>125227901</v>
+        <v>125227327</v>
       </c>
       <c r="B34" t="n">
         <v>98101</v>
@@ -4235,7 +4236,7 @@
         <v>745280</v>
       </c>
       <c r="R34" t="n">
-        <v>7107886</v>
+        <v>7107795</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4295,7 +4296,7 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>125231948</v>
+        <v>125222404</v>
       </c>
       <c r="B35" t="n">
         <v>98101</v>
@@ -4329,7 +4330,11 @@
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
-      <c r="J35" t="inlineStr"/>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K35" t="inlineStr"/>
       <c r="L35" t="inlineStr"/>
       <c r="N35" t="inlineStr"/>
@@ -4339,10 +4344,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>745279</v>
+        <v>745290</v>
       </c>
       <c r="R35" t="n">
-        <v>7107754</v>
+        <v>7107886</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4377,6 +4382,11 @@
           <t>2025-05-18</t>
         </is>
       </c>
+      <c r="AC35" t="inlineStr">
+        <is>
+          <t>några kvadratmeter med bladrosetter</t>
+        </is>
+      </c>
       <c r="AD35" t="b">
         <v>0</v>
       </c>
@@ -4390,19 +4400,19 @@
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Patrik Nygren</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Patrik Nygren</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>125222545</v>
+        <v>125222754</v>
       </c>
       <c r="B36" t="n">
         <v>98101</v>
@@ -4450,7 +4460,7 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>745294</v>
+        <v>745306</v>
       </c>
       <c r="R36" t="n">
         <v>7107877</v>
@@ -4513,10 +4523,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>125226206</v>
+        <v>125231342</v>
       </c>
       <c r="B37" t="n">
-        <v>91012</v>
+        <v>98101</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4525,34 +4535,31 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
-      <c r="J37" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+      <c r="J37" t="inlineStr"/>
       <c r="K37" t="inlineStr"/>
+      <c r="L37" t="inlineStr"/>
       <c r="N37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
@@ -4560,10 +4567,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>745327</v>
+        <v>745267</v>
       </c>
       <c r="R37" t="n">
-        <v>7107827</v>
+        <v>7107907</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4611,22 +4618,22 @@
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Patrik Nygren</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Patrik Nygren</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>125231464</v>
+        <v>125226206</v>
       </c>
       <c r="B38" t="n">
-        <v>79795</v>
+        <v>91012</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4635,29 +4642,33 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6456</v>
+        <v>1202</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
-      <c r="J38" t="inlineStr"/>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K38" t="inlineStr"/>
       <c r="N38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
@@ -4666,10 +4677,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>745287</v>
+        <v>745327</v>
       </c>
       <c r="R38" t="n">
-        <v>7107886</v>
+        <v>7107827</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4717,22 +4728,22 @@
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Patrik Nygren</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Patrik Nygren</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>125232181</v>
+        <v>125222073</v>
       </c>
       <c r="B39" t="n">
-        <v>57529</v>
+        <v>91012</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4745,27 +4756,30 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>100049</v>
+        <v>1202</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K39" t="inlineStr"/>
-      <c r="L39" t="inlineStr"/>
-      <c r="M39" t="inlineStr"/>
       <c r="N39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
@@ -4773,10 +4787,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>745227</v>
+        <v>745262</v>
       </c>
       <c r="R39" t="n">
-        <v>7107774</v>
+        <v>7107946</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4817,28 +4831,29 @@
       <c r="AE39" t="b">
         <v>0</v>
       </c>
+      <c r="AF39" t="inlineStr"/>
       <c r="AG39" t="b">
         <v>0</v>
       </c>
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Patrik Nygren</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Patrik Nygren</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>125231779</v>
+        <v>125231888</v>
       </c>
       <c r="B40" t="n">
-        <v>79920</v>
+        <v>98101</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4847,30 +4862,31 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6462</v>
+        <v>220787</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
       <c r="J40" t="inlineStr"/>
       <c r="K40" t="inlineStr"/>
+      <c r="L40" t="inlineStr"/>
       <c r="N40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
@@ -4878,10 +4894,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>745323</v>
+        <v>745297</v>
       </c>
       <c r="R40" t="n">
-        <v>7107772</v>
+        <v>7107757</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4941,7 +4957,7 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>125231888</v>
+        <v>125226783</v>
       </c>
       <c r="B41" t="n">
         <v>98101</v>
@@ -4975,7 +4991,11 @@
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
-      <c r="J41" t="inlineStr"/>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K41" t="inlineStr"/>
       <c r="L41" t="inlineStr"/>
       <c r="N41" t="inlineStr"/>
@@ -4985,10 +5005,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>745297</v>
+        <v>745294</v>
       </c>
       <c r="R41" t="n">
-        <v>7107757</v>
+        <v>7107772</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5036,22 +5056,22 @@
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Patrik Nygren</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Patrik Nygren</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>125222055</v>
+        <v>125232181</v>
       </c>
       <c r="B42" t="n">
-        <v>91012</v>
+        <v>57529</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -5064,30 +5084,27 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>1202</v>
+        <v>100049</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
-      <c r="J42" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
       <c r="K42" t="inlineStr"/>
+      <c r="L42" t="inlineStr"/>
+      <c r="M42" t="inlineStr"/>
       <c r="N42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
@@ -5095,10 +5112,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>745262</v>
+        <v>745227</v>
       </c>
       <c r="R42" t="n">
-        <v>7107948</v>
+        <v>7107774</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5139,26 +5156,25 @@
       <c r="AE42" t="b">
         <v>0</v>
       </c>
-      <c r="AF42" t="inlineStr"/>
       <c r="AG42" t="b">
         <v>0</v>
       </c>
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Patrik Nygren</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Patrik Nygren</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>125232212</v>
+        <v>125227661</v>
       </c>
       <c r="B43" t="n">
         <v>98101</v>
@@ -5192,7 +5208,11 @@
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
-      <c r="J43" t="inlineStr"/>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K43" t="inlineStr"/>
       <c r="L43" t="inlineStr"/>
       <c r="N43" t="inlineStr"/>
@@ -5202,10 +5222,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>745252</v>
+        <v>745280</v>
       </c>
       <c r="R43" t="n">
-        <v>7107940</v>
+        <v>7107827</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5253,22 +5273,22 @@
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Patrik Nygren</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Patrik Nygren</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>125222999</v>
+        <v>125231618</v>
       </c>
       <c r="B44" t="n">
-        <v>98101</v>
+        <v>79795</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5277,35 +5297,30 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>220787</v>
+        <v>6456</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
-      <c r="J44" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="J44" t="inlineStr"/>
       <c r="K44" t="inlineStr"/>
-      <c r="L44" t="inlineStr"/>
       <c r="N44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
@@ -5313,10 +5328,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>745290</v>
+        <v>745381</v>
       </c>
       <c r="R44" t="n">
-        <v>7107864</v>
+        <v>7107841</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5364,22 +5379,22 @@
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>Patrik Nygren</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Patrik Nygren</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>125231658</v>
+        <v>125222246</v>
       </c>
       <c r="B45" t="n">
-        <v>90977</v>
+        <v>91012</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5388,29 +5403,33 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>5447</v>
+        <v>1202</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
-      <c r="J45" t="inlineStr"/>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K45" t="inlineStr"/>
       <c r="N45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
@@ -5419,10 +5438,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>745405</v>
+        <v>745262</v>
       </c>
       <c r="R45" t="n">
-        <v>7107837</v>
+        <v>7107944</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5470,22 +5489,22 @@
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Patrik Nygren</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Patrik Nygren</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>125228007</v>
+        <v>125232283</v>
       </c>
       <c r="B46" t="n">
-        <v>57529</v>
+        <v>57883</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5494,20 +5513,20 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>100049</v>
+        <v>103015</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
@@ -5518,11 +5537,7 @@
       <c r="I46" t="inlineStr"/>
       <c r="K46" t="inlineStr"/>
       <c r="L46" t="inlineStr"/>
-      <c r="M46" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
+      <c r="M46" t="inlineStr"/>
       <c r="N46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
@@ -5530,13 +5545,13 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>745249</v>
+        <v>745254</v>
       </c>
       <c r="R46" t="n">
-        <v>7107940</v>
+        <v>7107972</v>
       </c>
       <c r="S46" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -5566,11 +5581,6 @@
       <c r="AA46" t="inlineStr">
         <is>
           <t>2025-05-18</t>
-        </is>
-      </c>
-      <c r="AC46" t="inlineStr">
-        <is>
-          <t>hackat hål i gran</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5585,22 +5595,22 @@
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>Patrik Nygren</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Patrik Nygren</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>125226477</v>
+        <v>125222288</v>
       </c>
       <c r="B47" t="n">
-        <v>91012</v>
+        <v>98101</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5609,34 +5619,35 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
       <c r="J47" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K47" t="inlineStr"/>
+      <c r="L47" t="inlineStr"/>
       <c r="N47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
@@ -5644,10 +5655,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>745445</v>
+        <v>745266</v>
       </c>
       <c r="R47" t="n">
-        <v>7107841</v>
+        <v>7107910</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5707,10 +5718,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>125231618</v>
+        <v>125230982</v>
       </c>
       <c r="B48" t="n">
-        <v>79795</v>
+        <v>98101</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5719,30 +5730,31 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6456</v>
+        <v>220787</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
       <c r="J48" t="inlineStr"/>
       <c r="K48" t="inlineStr"/>
+      <c r="L48" t="inlineStr"/>
       <c r="N48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
@@ -5750,10 +5762,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>745381</v>
+        <v>745259</v>
       </c>
       <c r="R48" t="n">
-        <v>7107841</v>
+        <v>7107964</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5813,7 +5825,7 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>125223203</v>
+        <v>125231249</v>
       </c>
       <c r="B49" t="n">
         <v>98101</v>
@@ -5847,11 +5859,7 @@
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
-      <c r="J49" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="J49" t="inlineStr"/>
       <c r="K49" t="inlineStr"/>
       <c r="L49" t="inlineStr"/>
       <c r="N49" t="inlineStr"/>
@@ -5861,10 +5869,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>745293</v>
+        <v>745260</v>
       </c>
       <c r="R49" t="n">
-        <v>7107855</v>
+        <v>7107948</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5912,22 +5920,22 @@
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
         <is>
-          <t>Patrik Nygren</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>Patrik Nygren</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>125227847</v>
+        <v>125231838</v>
       </c>
       <c r="B50" t="n">
-        <v>57529</v>
+        <v>98101</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -5936,35 +5944,31 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
+      <c r="J50" t="inlineStr"/>
       <c r="K50" t="inlineStr"/>
       <c r="L50" t="inlineStr"/>
-      <c r="M50" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
@@ -5972,10 +5976,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>745285</v>
+        <v>745310</v>
       </c>
       <c r="R50" t="n">
-        <v>7107862</v>
+        <v>7107765</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -6010,29 +6014,25 @@
           <t>2025-05-18</t>
         </is>
       </c>
-      <c r="AC50" t="inlineStr">
-        <is>
-          <t>hack i död gran</t>
-        </is>
-      </c>
       <c r="AD50" t="b">
         <v>0</v>
       </c>
       <c r="AE50" t="b">
         <v>0</v>
       </c>
+      <c r="AF50" t="inlineStr"/>
       <c r="AG50" t="b">
         <v>0</v>
       </c>
       <c r="AT50" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
         <is>
-          <t>Patrik Nygren</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX50" t="inlineStr">
         <is>
-          <t>Patrik Nygren</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>

--- a/artfynd/A 53969-2024 artfynd.xlsx
+++ b/artfynd/A 53969-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>125223590</v>
+        <v>125227847</v>
       </c>
       <c r="B2" t="n">
-        <v>98101</v>
+        <v>57529</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,35 +687,35 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -723,10 +723,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>745299</v>
+        <v>745285</v>
       </c>
       <c r="R2" t="n">
-        <v>7107851</v>
+        <v>7107862</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -761,13 +761,17 @@
           <t>2025-05-18</t>
         </is>
       </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>hack i död gran</t>
+        </is>
+      </c>
       <c r="AD2" t="b">
         <v>0</v>
       </c>
       <c r="AE2" t="b">
         <v>0</v>
       </c>
-      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
@@ -786,10 +790,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>125225686</v>
+        <v>125231838</v>
       </c>
       <c r="B3" t="n">
-        <v>91012</v>
+        <v>98101</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -798,34 +802,31 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+      <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -833,10 +834,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>745321</v>
+        <v>745310</v>
       </c>
       <c r="R3" t="n">
-        <v>7107841</v>
+        <v>7107765</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -884,19 +885,19 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Patrik Nygren</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Patrik Nygren</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>125231983</v>
+        <v>125223590</v>
       </c>
       <c r="B4" t="n">
         <v>98101</v>
@@ -930,7 +931,11 @@
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
@@ -940,10 +945,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>745279</v>
+        <v>745299</v>
       </c>
       <c r="R4" t="n">
-        <v>7107767</v>
+        <v>7107851</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -991,19 +996,19 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Patrik Nygren</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Patrik Nygren</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>125227446</v>
+        <v>125231888</v>
       </c>
       <c r="B5" t="n">
         <v>98101</v>
@@ -1037,11 +1042,7 @@
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr"/>
       <c r="N5" t="inlineStr"/>
@@ -1051,10 +1052,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>745280</v>
+        <v>745297</v>
       </c>
       <c r="R5" t="n">
-        <v>7107802</v>
+        <v>7107757</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1102,22 +1103,22 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Patrik Nygren</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Patrik Nygren</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>125222055</v>
+        <v>125231983</v>
       </c>
       <c r="B6" t="n">
-        <v>91012</v>
+        <v>98101</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1126,34 +1127,31 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+      <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1161,10 +1159,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>745262</v>
+        <v>745279</v>
       </c>
       <c r="R6" t="n">
-        <v>7107948</v>
+        <v>7107767</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1212,19 +1210,19 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Patrik Nygren</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Patrik Nygren</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>125232024</v>
+        <v>125222073</v>
       </c>
       <c r="B7" t="n">
         <v>91012</v>
@@ -1258,7 +1256,11 @@
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr"/>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K7" t="inlineStr"/>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
@@ -1267,10 +1269,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>745288</v>
+        <v>745262</v>
       </c>
       <c r="R7" t="n">
-        <v>7107786</v>
+        <v>7107946</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1318,19 +1320,19 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Patrik Nygren</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Patrik Nygren</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>125228040</v>
+        <v>125231249</v>
       </c>
       <c r="B8" t="n">
         <v>98101</v>
@@ -1364,11 +1366,7 @@
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
       <c r="L8" t="inlineStr"/>
       <c r="N8" t="inlineStr"/>
@@ -1378,10 +1376,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>745249</v>
+        <v>745260</v>
       </c>
       <c r="R8" t="n">
-        <v>7107940</v>
+        <v>7107948</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1416,11 +1414,6 @@
           <t>2025-05-18</t>
         </is>
       </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>rikligt med bladrosetter!</t>
-        </is>
-      </c>
       <c r="AD8" t="b">
         <v>0</v>
       </c>
@@ -1434,22 +1427,22 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Patrik Nygren</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Patrik Nygren</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>125225490</v>
+        <v>125231309</v>
       </c>
       <c r="B9" t="n">
-        <v>91361</v>
+        <v>98101</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1462,30 +1455,27 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>2062</v>
+        <v>220787</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Ulltickeporing</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Skeletocutis brevispora</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+      <c r="J9" t="inlineStr"/>
       <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
@@ -1493,10 +1483,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>745321</v>
+        <v>745268</v>
       </c>
       <c r="R9" t="n">
-        <v>7107841</v>
+        <v>7107926</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1544,19 +1534,19 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Patrik Nygren</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Patrik Nygren</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>125232212</v>
+        <v>125228040</v>
       </c>
       <c r="B10" t="n">
         <v>98101</v>
@@ -1590,7 +1580,11 @@
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="J10" t="inlineStr"/>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K10" t="inlineStr"/>
       <c r="L10" t="inlineStr"/>
       <c r="N10" t="inlineStr"/>
@@ -1600,7 +1594,7 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>745252</v>
+        <v>745249</v>
       </c>
       <c r="R10" t="n">
         <v>7107940</v>
@@ -1638,6 +1632,11 @@
           <t>2025-05-18</t>
         </is>
       </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>rikligt med bladrosetter!</t>
+        </is>
+      </c>
       <c r="AD10" t="b">
         <v>0</v>
       </c>
@@ -1651,19 +1650,19 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Patrik Nygren</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Patrik Nygren</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>125223203</v>
+        <v>125223807</v>
       </c>
       <c r="B11" t="n">
         <v>98101</v>
@@ -1711,10 +1710,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>745293</v>
+        <v>745315</v>
       </c>
       <c r="R11" t="n">
-        <v>7107855</v>
+        <v>7107851</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1747,6 +1746,11 @@
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-05-18</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Rikligt med bladrosetter!</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1774,10 +1778,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>125231545</v>
+        <v>125222246</v>
       </c>
       <c r="B12" t="n">
-        <v>79795</v>
+        <v>91012</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1786,29 +1790,33 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6456</v>
+        <v>1202</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="J12" t="inlineStr"/>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K12" t="inlineStr"/>
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
@@ -1817,10 +1825,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>745310</v>
+        <v>745262</v>
       </c>
       <c r="R12" t="n">
-        <v>7107876</v>
+        <v>7107944</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1868,22 +1876,22 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Patrik Nygren</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Patrik Nygren</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>125222017</v>
+        <v>125232024</v>
       </c>
       <c r="B13" t="n">
-        <v>98101</v>
+        <v>91012</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1892,35 +1900,30 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="J13" t="inlineStr"/>
       <c r="K13" t="inlineStr"/>
-      <c r="L13" t="inlineStr"/>
       <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
@@ -1928,10 +1931,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>745243</v>
+        <v>745288</v>
       </c>
       <c r="R13" t="n">
-        <v>7107977</v>
+        <v>7107786</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1979,19 +1982,19 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Patrik Nygren</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Patrik Nygren</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>125222999</v>
+        <v>125226783</v>
       </c>
       <c r="B14" t="n">
         <v>98101</v>
@@ -2039,10 +2042,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>745290</v>
+        <v>745294</v>
       </c>
       <c r="R14" t="n">
-        <v>7107864</v>
+        <v>7107772</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2102,10 +2105,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>125232195</v>
+        <v>125222545</v>
       </c>
       <c r="B15" t="n">
-        <v>79891</v>
+        <v>98101</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2114,30 +2117,35 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
-      <c r="J15" t="inlineStr"/>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
       <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
@@ -2145,10 +2153,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>745215</v>
+        <v>745294</v>
       </c>
       <c r="R15" t="n">
-        <v>7107730</v>
+        <v>7107877</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2196,22 +2204,22 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Patrik Nygren</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Patrik Nygren</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>125227847</v>
+        <v>125222288</v>
       </c>
       <c r="B16" t="n">
-        <v>57529</v>
+        <v>98101</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2220,35 +2228,35 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K16" t="inlineStr"/>
       <c r="L16" t="inlineStr"/>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
@@ -2256,10 +2264,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>745285</v>
+        <v>745266</v>
       </c>
       <c r="R16" t="n">
-        <v>7107862</v>
+        <v>7107910</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2294,17 +2302,13 @@
           <t>2025-05-18</t>
         </is>
       </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>hack i död gran</t>
-        </is>
-      </c>
       <c r="AD16" t="b">
         <v>0</v>
       </c>
       <c r="AE16" t="b">
         <v>0</v>
       </c>
+      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>
@@ -2323,10 +2327,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>125225982</v>
+        <v>125225686</v>
       </c>
       <c r="B17" t="n">
-        <v>98101</v>
+        <v>91012</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2335,35 +2339,34 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
       <c r="J17" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K17" t="inlineStr"/>
-      <c r="L17" t="inlineStr"/>
       <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
@@ -2371,10 +2374,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>745327</v>
+        <v>745321</v>
       </c>
       <c r="R17" t="n">
-        <v>7107834</v>
+        <v>7107841</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2434,7 +2437,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>125231309</v>
+        <v>125222999</v>
       </c>
       <c r="B18" t="n">
         <v>98101</v>
@@ -2468,7 +2471,11 @@
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
-      <c r="J18" t="inlineStr"/>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K18" t="inlineStr"/>
       <c r="L18" t="inlineStr"/>
       <c r="N18" t="inlineStr"/>
@@ -2478,10 +2485,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>745268</v>
+        <v>745290</v>
       </c>
       <c r="R18" t="n">
-        <v>7107926</v>
+        <v>7107864</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2529,22 +2536,22 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Patrik Nygren</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Patrik Nygren</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>125231658</v>
+        <v>125222404</v>
       </c>
       <c r="B19" t="n">
-        <v>90977</v>
+        <v>98101</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2553,30 +2560,35 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>5447</v>
+        <v>220787</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
-      <c r="J19" t="inlineStr"/>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr"/>
       <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
@@ -2584,10 +2596,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>745405</v>
+        <v>745290</v>
       </c>
       <c r="R19" t="n">
-        <v>7107837</v>
+        <v>7107886</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2622,6 +2634,11 @@
           <t>2025-05-18</t>
         </is>
       </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>några kvadratmeter med bladrosetter</t>
+        </is>
+      </c>
       <c r="AD19" t="b">
         <v>0</v>
       </c>
@@ -2635,22 +2652,22 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Patrik Nygren</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Patrik Nygren</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>125231696</v>
+        <v>125226206</v>
       </c>
       <c r="B20" t="n">
-        <v>98122</v>
+        <v>91012</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2659,31 +2676,34 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>221952</v>
+        <v>1202</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
-      <c r="J20" t="inlineStr"/>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K20" t="inlineStr"/>
-      <c r="L20" t="inlineStr"/>
       <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
@@ -2691,10 +2711,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>745356</v>
+        <v>745327</v>
       </c>
       <c r="R20" t="n">
-        <v>7107793</v>
+        <v>7107827</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2742,22 +2762,22 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Patrik Nygren</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Patrik Nygren</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>125231948</v>
+        <v>125232195</v>
       </c>
       <c r="B21" t="n">
-        <v>98101</v>
+        <v>79891</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2766,31 +2786,30 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
       <c r="J21" t="inlineStr"/>
       <c r="K21" t="inlineStr"/>
-      <c r="L21" t="inlineStr"/>
       <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
@@ -2798,10 +2817,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>745279</v>
+        <v>745215</v>
       </c>
       <c r="R21" t="n">
-        <v>7107754</v>
+        <v>7107730</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2861,10 +2880,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>125231779</v>
+        <v>125231948</v>
       </c>
       <c r="B22" t="n">
-        <v>79920</v>
+        <v>98101</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2873,30 +2892,31 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6462</v>
+        <v>220787</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
       <c r="J22" t="inlineStr"/>
       <c r="K22" t="inlineStr"/>
+      <c r="L22" t="inlineStr"/>
       <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
@@ -2904,10 +2924,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>745323</v>
+        <v>745279</v>
       </c>
       <c r="R22" t="n">
-        <v>7107772</v>
+        <v>7107754</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2967,10 +2987,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>125231105</v>
+        <v>125227728</v>
       </c>
       <c r="B23" t="n">
-        <v>79920</v>
+        <v>98101</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2979,30 +2999,35 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6462</v>
+        <v>220787</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
-      <c r="J23" t="inlineStr"/>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K23" t="inlineStr"/>
+      <c r="L23" t="inlineStr"/>
       <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
@@ -3010,10 +3035,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>745259</v>
+        <v>745279</v>
       </c>
       <c r="R23" t="n">
-        <v>7107964</v>
+        <v>7107831</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3061,22 +3086,22 @@
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Patrik Nygren</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Patrik Nygren</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>125231464</v>
+        <v>125232212</v>
       </c>
       <c r="B24" t="n">
-        <v>79795</v>
+        <v>98101</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3085,30 +3110,31 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6456</v>
+        <v>220787</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
       <c r="J24" t="inlineStr"/>
       <c r="K24" t="inlineStr"/>
+      <c r="L24" t="inlineStr"/>
       <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
@@ -3116,10 +3142,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>745287</v>
+        <v>745252</v>
       </c>
       <c r="R24" t="n">
-        <v>7107886</v>
+        <v>7107940</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3179,7 +3205,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>125227797</v>
+        <v>125227901</v>
       </c>
       <c r="B25" t="n">
         <v>98101</v>
@@ -3227,10 +3253,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>745277</v>
+        <v>745280</v>
       </c>
       <c r="R25" t="n">
-        <v>7107838</v>
+        <v>7107886</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3290,10 +3316,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>125228007</v>
+        <v>125227327</v>
       </c>
       <c r="B26" t="n">
-        <v>57529</v>
+        <v>98101</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3302,35 +3328,35 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K26" t="inlineStr"/>
       <c r="L26" t="inlineStr"/>
-      <c r="M26" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
@@ -3338,10 +3364,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>745249</v>
+        <v>745280</v>
       </c>
       <c r="R26" t="n">
-        <v>7107940</v>
+        <v>7107795</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3376,17 +3402,13 @@
           <t>2025-05-18</t>
         </is>
       </c>
-      <c r="AC26" t="inlineStr">
-        <is>
-          <t>hackat hål i gran</t>
-        </is>
-      </c>
       <c r="AD26" t="b">
         <v>0</v>
       </c>
       <c r="AE26" t="b">
         <v>0</v>
       </c>
+      <c r="AF26" t="inlineStr"/>
       <c r="AG26" t="b">
         <v>0</v>
       </c>
@@ -3405,7 +3427,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>125222361</v>
+        <v>125223425</v>
       </c>
       <c r="B27" t="n">
         <v>98101</v>
@@ -3453,10 +3475,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>745280</v>
+        <v>745298</v>
       </c>
       <c r="R27" t="n">
-        <v>7107886</v>
+        <v>7107856</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3516,7 +3538,7 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>125222545</v>
+        <v>125222754</v>
       </c>
       <c r="B28" t="n">
         <v>98101</v>
@@ -3564,7 +3586,7 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>745294</v>
+        <v>745306</v>
       </c>
       <c r="R28" t="n">
         <v>7107877</v>
@@ -3627,7 +3649,7 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>125223425</v>
+        <v>125227446</v>
       </c>
       <c r="B29" t="n">
         <v>98101</v>
@@ -3675,10 +3697,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>745298</v>
+        <v>745280</v>
       </c>
       <c r="R29" t="n">
-        <v>7107856</v>
+        <v>7107802</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3738,7 +3760,7 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>125223807</v>
+        <v>125227797</v>
       </c>
       <c r="B30" t="n">
         <v>98101</v>
@@ -3786,10 +3808,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>745315</v>
+        <v>745277</v>
       </c>
       <c r="R30" t="n">
-        <v>7107851</v>
+        <v>7107838</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3822,11 +3844,6 @@
       <c r="AA30" t="inlineStr">
         <is>
           <t>2025-05-18</t>
-        </is>
-      </c>
-      <c r="AC30" t="inlineStr">
-        <is>
-          <t>Rikligt med bladrosetter!</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3854,7 +3871,7 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>125222083</v>
+        <v>125225490</v>
       </c>
       <c r="B31" t="n">
         <v>91361</v>
@@ -3901,10 +3918,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>745262</v>
+        <v>745321</v>
       </c>
       <c r="R31" t="n">
-        <v>7107946</v>
+        <v>7107841</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3964,10 +3981,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>125226477</v>
+        <v>125222083</v>
       </c>
       <c r="B32" t="n">
-        <v>91012</v>
+        <v>91361</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -3976,25 +3993,25 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>1202</v>
+        <v>2062</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Ulltickeporing</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Skeletocutis brevispora</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -4011,10 +4028,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>745445</v>
+        <v>745262</v>
       </c>
       <c r="R32" t="n">
-        <v>7107841</v>
+        <v>7107946</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4074,10 +4091,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>125227728</v>
+        <v>125222055</v>
       </c>
       <c r="B33" t="n">
-        <v>98101</v>
+        <v>91012</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4086,35 +4103,34 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
       <c r="J33" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K33" t="inlineStr"/>
-      <c r="L33" t="inlineStr"/>
       <c r="N33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
@@ -4122,10 +4138,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>745279</v>
+        <v>745262</v>
       </c>
       <c r="R33" t="n">
-        <v>7107831</v>
+        <v>7107948</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4185,10 +4201,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>125227327</v>
+        <v>125231658</v>
       </c>
       <c r="B34" t="n">
-        <v>98101</v>
+        <v>90977</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4197,35 +4213,30 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>220787</v>
+        <v>5447</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
-      <c r="J34" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="J34" t="inlineStr"/>
       <c r="K34" t="inlineStr"/>
-      <c r="L34" t="inlineStr"/>
       <c r="N34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
@@ -4233,10 +4244,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>745280</v>
+        <v>745405</v>
       </c>
       <c r="R34" t="n">
-        <v>7107795</v>
+        <v>7107837</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4284,22 +4295,22 @@
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Patrik Nygren</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Patrik Nygren</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>125222404</v>
+        <v>125228007</v>
       </c>
       <c r="B35" t="n">
-        <v>98101</v>
+        <v>57529</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4308,35 +4319,35 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
-      <c r="J35" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
       <c r="K35" t="inlineStr"/>
       <c r="L35" t="inlineStr"/>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
@@ -4344,10 +4355,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>745290</v>
+        <v>745249</v>
       </c>
       <c r="R35" t="n">
-        <v>7107886</v>
+        <v>7107940</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4384,7 +4395,7 @@
       </c>
       <c r="AC35" t="inlineStr">
         <is>
-          <t>några kvadratmeter med bladrosetter</t>
+          <t>hackat hål i gran</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4393,7 +4404,6 @@
       <c r="AE35" t="b">
         <v>0</v>
       </c>
-      <c r="AF35" t="inlineStr"/>
       <c r="AG35" t="b">
         <v>0</v>
       </c>
@@ -4412,10 +4422,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>125222754</v>
+        <v>125232283</v>
       </c>
       <c r="B36" t="n">
-        <v>98101</v>
+        <v>57883</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4424,35 +4434,31 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>220787</v>
+        <v>103015</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
-      <c r="J36" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
       <c r="K36" t="inlineStr"/>
       <c r="L36" t="inlineStr"/>
+      <c r="M36" t="inlineStr"/>
       <c r="N36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
@@ -4460,13 +4466,13 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>745306</v>
+        <v>745254</v>
       </c>
       <c r="R36" t="n">
-        <v>7107877</v>
+        <v>7107972</v>
       </c>
       <c r="S36" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -4504,29 +4510,28 @@
       <c r="AE36" t="b">
         <v>0</v>
       </c>
-      <c r="AF36" t="inlineStr"/>
       <c r="AG36" t="b">
         <v>0</v>
       </c>
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Patrik Nygren</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Patrik Nygren</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>125231342</v>
+        <v>125231464</v>
       </c>
       <c r="B37" t="n">
-        <v>98101</v>
+        <v>79795</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4535,31 +4540,30 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>220787</v>
+        <v>6456</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
       <c r="J37" t="inlineStr"/>
       <c r="K37" t="inlineStr"/>
-      <c r="L37" t="inlineStr"/>
       <c r="N37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
@@ -4567,10 +4571,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>745267</v>
+        <v>745287</v>
       </c>
       <c r="R37" t="n">
-        <v>7107907</v>
+        <v>7107886</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4630,10 +4634,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>125226206</v>
+        <v>125230982</v>
       </c>
       <c r="B38" t="n">
-        <v>91012</v>
+        <v>98101</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4642,34 +4646,31 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
-      <c r="J38" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+      <c r="J38" t="inlineStr"/>
       <c r="K38" t="inlineStr"/>
+      <c r="L38" t="inlineStr"/>
       <c r="N38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
@@ -4677,10 +4678,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>745327</v>
+        <v>745259</v>
       </c>
       <c r="R38" t="n">
-        <v>7107827</v>
+        <v>7107964</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4728,22 +4729,22 @@
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Patrik Nygren</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Patrik Nygren</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>125222073</v>
+        <v>125227661</v>
       </c>
       <c r="B39" t="n">
-        <v>91012</v>
+        <v>98101</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4752,34 +4753,35 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
       <c r="J39" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K39" t="inlineStr"/>
+      <c r="L39" t="inlineStr"/>
       <c r="N39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
@@ -4787,10 +4789,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>745262</v>
+        <v>745280</v>
       </c>
       <c r="R39" t="n">
-        <v>7107946</v>
+        <v>7107827</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4850,10 +4852,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>125231888</v>
+        <v>125232181</v>
       </c>
       <c r="B40" t="n">
-        <v>98101</v>
+        <v>57529</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4862,31 +4864,31 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
-      <c r="J40" t="inlineStr"/>
       <c r="K40" t="inlineStr"/>
       <c r="L40" t="inlineStr"/>
+      <c r="M40" t="inlineStr"/>
       <c r="N40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
@@ -4894,10 +4896,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>745297</v>
+        <v>745227</v>
       </c>
       <c r="R40" t="n">
-        <v>7107757</v>
+        <v>7107774</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4938,7 +4940,6 @@
       <c r="AE40" t="b">
         <v>0</v>
       </c>
-      <c r="AF40" t="inlineStr"/>
       <c r="AG40" t="b">
         <v>0</v>
       </c>
@@ -4957,10 +4958,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>125226783</v>
+        <v>125231105</v>
       </c>
       <c r="B41" t="n">
-        <v>98101</v>
+        <v>79920</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -4969,35 +4970,30 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>220787</v>
+        <v>6462</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
-      <c r="J41" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="J41" t="inlineStr"/>
       <c r="K41" t="inlineStr"/>
-      <c r="L41" t="inlineStr"/>
       <c r="N41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
@@ -5005,10 +5001,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>745294</v>
+        <v>745259</v>
       </c>
       <c r="R41" t="n">
-        <v>7107772</v>
+        <v>7107964</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5056,22 +5052,22 @@
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Patrik Nygren</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Patrik Nygren</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>125232181</v>
+        <v>125223203</v>
       </c>
       <c r="B42" t="n">
-        <v>57529</v>
+        <v>98101</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -5080,31 +5076,35 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K42" t="inlineStr"/>
       <c r="L42" t="inlineStr"/>
-      <c r="M42" t="inlineStr"/>
       <c r="N42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
@@ -5112,10 +5112,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>745227</v>
+        <v>745293</v>
       </c>
       <c r="R42" t="n">
-        <v>7107774</v>
+        <v>7107855</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5156,28 +5156,29 @@
       <c r="AE42" t="b">
         <v>0</v>
       </c>
+      <c r="AF42" t="inlineStr"/>
       <c r="AG42" t="b">
         <v>0</v>
       </c>
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Patrik Nygren</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Patrik Nygren</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>125227661</v>
+        <v>125231696</v>
       </c>
       <c r="B43" t="n">
-        <v>98101</v>
+        <v>98122</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5186,33 +5187,29 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>220787</v>
+        <v>221952</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
-      <c r="J43" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="J43" t="inlineStr"/>
       <c r="K43" t="inlineStr"/>
       <c r="L43" t="inlineStr"/>
       <c r="N43" t="inlineStr"/>
@@ -5222,10 +5219,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>745280</v>
+        <v>745356</v>
       </c>
       <c r="R43" t="n">
-        <v>7107827</v>
+        <v>7107793</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5273,22 +5270,22 @@
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Patrik Nygren</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Patrik Nygren</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>125231618</v>
+        <v>125231779</v>
       </c>
       <c r="B44" t="n">
-        <v>79795</v>
+        <v>79920</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5301,21 +5298,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6456</v>
+        <v>6462</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5328,10 +5325,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>745381</v>
+        <v>745323</v>
       </c>
       <c r="R44" t="n">
-        <v>7107841</v>
+        <v>7107772</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5391,10 +5388,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>125222246</v>
+        <v>125231618</v>
       </c>
       <c r="B45" t="n">
-        <v>91012</v>
+        <v>79795</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5403,33 +5400,29 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>1202</v>
+        <v>6456</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
-      <c r="J45" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+      <c r="J45" t="inlineStr"/>
       <c r="K45" t="inlineStr"/>
       <c r="N45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
@@ -5438,10 +5431,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>745262</v>
+        <v>745381</v>
       </c>
       <c r="R45" t="n">
-        <v>7107944</v>
+        <v>7107841</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5489,22 +5482,22 @@
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>Patrik Nygren</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Patrik Nygren</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>125232283</v>
+        <v>125231545</v>
       </c>
       <c r="B46" t="n">
-        <v>57883</v>
+        <v>79795</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5517,27 +5510,26 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>103015</v>
+        <v>6456</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
+      <c r="J46" t="inlineStr"/>
       <c r="K46" t="inlineStr"/>
-      <c r="L46" t="inlineStr"/>
-      <c r="M46" t="inlineStr"/>
       <c r="N46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
@@ -5545,13 +5537,13 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>745254</v>
+        <v>745310</v>
       </c>
       <c r="R46" t="n">
-        <v>7107972</v>
+        <v>7107876</v>
       </c>
       <c r="S46" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -5589,6 +5581,7 @@
       <c r="AE46" t="b">
         <v>0</v>
       </c>
+      <c r="AF46" t="inlineStr"/>
       <c r="AG46" t="b">
         <v>0</v>
       </c>
@@ -5607,7 +5600,7 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>125222288</v>
+        <v>125225982</v>
       </c>
       <c r="B47" t="n">
         <v>98101</v>
@@ -5655,10 +5648,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>745266</v>
+        <v>745327</v>
       </c>
       <c r="R47" t="n">
-        <v>7107910</v>
+        <v>7107834</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5718,7 +5711,7 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>125230982</v>
+        <v>125222017</v>
       </c>
       <c r="B48" t="n">
         <v>98101</v>
@@ -5752,7 +5745,11 @@
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
-      <c r="J48" t="inlineStr"/>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K48" t="inlineStr"/>
       <c r="L48" t="inlineStr"/>
       <c r="N48" t="inlineStr"/>
@@ -5762,10 +5759,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>745259</v>
+        <v>745243</v>
       </c>
       <c r="R48" t="n">
-        <v>7107964</v>
+        <v>7107977</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5813,22 +5810,22 @@
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Patrik Nygren</t>
         </is>
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Patrik Nygren</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>125231249</v>
+        <v>125226477</v>
       </c>
       <c r="B49" t="n">
-        <v>98101</v>
+        <v>91012</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -5837,31 +5834,34 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
-      <c r="J49" t="inlineStr"/>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K49" t="inlineStr"/>
-      <c r="L49" t="inlineStr"/>
       <c r="N49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
@@ -5869,10 +5869,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>745260</v>
+        <v>745445</v>
       </c>
       <c r="R49" t="n">
-        <v>7107948</v>
+        <v>7107841</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5920,19 +5920,19 @@
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Patrik Nygren</t>
         </is>
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Patrik Nygren</t>
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>125231838</v>
+        <v>125231342</v>
       </c>
       <c r="B50" t="n">
         <v>98101</v>
@@ -5976,10 +5976,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>745310</v>
+        <v>745267</v>
       </c>
       <c r="R50" t="n">
-        <v>7107765</v>
+        <v>7107907</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>

--- a/artfynd/A 53969-2024 artfynd.xlsx
+++ b/artfynd/A 53969-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>125227847</v>
+        <v>125231779</v>
       </c>
       <c r="B2" t="n">
-        <v>57529</v>
+        <v>80057</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,35 +687,30 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100049</v>
+        <v>6462</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -723,10 +718,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>745285</v>
+        <v>745323</v>
       </c>
       <c r="R2" t="n">
-        <v>7107862</v>
+        <v>7107772</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -761,39 +756,35 @@
           <t>2025-05-18</t>
         </is>
       </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>hack i död gran</t>
-        </is>
-      </c>
       <c r="AD2" t="b">
         <v>0</v>
       </c>
       <c r="AE2" t="b">
         <v>0</v>
       </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Patrik Nygren</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Patrik Nygren</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>125231838</v>
+        <v>125227847</v>
       </c>
       <c r="B3" t="n">
-        <v>98101</v>
+        <v>57632</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -802,31 +793,35 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -834,10 +829,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>745310</v>
+        <v>745285</v>
       </c>
       <c r="R3" t="n">
-        <v>7107765</v>
+        <v>7107862</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -872,35 +867,39 @@
           <t>2025-05-18</t>
         </is>
       </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>hack i död gran</t>
+        </is>
+      </c>
       <c r="AD3" t="b">
         <v>0</v>
       </c>
       <c r="AE3" t="b">
         <v>0</v>
       </c>
-      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Patrik Nygren</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Patrik Nygren</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>125223590</v>
+        <v>125223425</v>
       </c>
       <c r="B4" t="n">
-        <v>98101</v>
+        <v>98269</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -945,10 +944,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>745299</v>
+        <v>745298</v>
       </c>
       <c r="R4" t="n">
-        <v>7107851</v>
+        <v>7107856</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1008,10 +1007,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>125231888</v>
+        <v>125222404</v>
       </c>
       <c r="B5" t="n">
-        <v>98101</v>
+        <v>98269</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1042,7 +1041,11 @@
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr"/>
       <c r="N5" t="inlineStr"/>
@@ -1052,10 +1055,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>745297</v>
+        <v>745290</v>
       </c>
       <c r="R5" t="n">
-        <v>7107757</v>
+        <v>7107886</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1090,6 +1093,11 @@
           <t>2025-05-18</t>
         </is>
       </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>några kvadratmeter med bladrosetter</t>
+        </is>
+      </c>
       <c r="AD5" t="b">
         <v>0</v>
       </c>
@@ -1103,22 +1111,22 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Patrik Nygren</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Patrik Nygren</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>125231983</v>
+        <v>125222754</v>
       </c>
       <c r="B6" t="n">
-        <v>98101</v>
+        <v>98269</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1149,7 +1157,11 @@
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr"/>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr"/>
       <c r="N6" t="inlineStr"/>
@@ -1159,10 +1171,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>745279</v>
+        <v>745306</v>
       </c>
       <c r="R6" t="n">
-        <v>7107767</v>
+        <v>7107877</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1210,22 +1222,22 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Patrik Nygren</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Patrik Nygren</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>125222073</v>
+        <v>125227327</v>
       </c>
       <c r="B7" t="n">
-        <v>91012</v>
+        <v>98269</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1234,34 +1246,35 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="J7" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
@@ -1269,10 +1282,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>745262</v>
+        <v>745280</v>
       </c>
       <c r="R7" t="n">
-        <v>7107946</v>
+        <v>7107795</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1332,10 +1345,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>125231249</v>
+        <v>125231888</v>
       </c>
       <c r="B8" t="n">
-        <v>98101</v>
+        <v>98269</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1376,10 +1389,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>745260</v>
+        <v>745297</v>
       </c>
       <c r="R8" t="n">
-        <v>7107948</v>
+        <v>7107757</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1439,10 +1452,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>125231309</v>
+        <v>125231105</v>
       </c>
       <c r="B9" t="n">
-        <v>98101</v>
+        <v>80057</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1451,31 +1464,30 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>220787</v>
+        <v>6462</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="J9" t="inlineStr"/>
       <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr"/>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
@@ -1483,10 +1495,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>745268</v>
+        <v>745259</v>
       </c>
       <c r="R9" t="n">
-        <v>7107926</v>
+        <v>7107964</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1546,10 +1558,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>125228040</v>
+        <v>125232195</v>
       </c>
       <c r="B10" t="n">
-        <v>98101</v>
+        <v>80028</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1558,35 +1570,30 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="J10" t="inlineStr"/>
       <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr"/>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
@@ -1594,10 +1601,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>745249</v>
+        <v>745215</v>
       </c>
       <c r="R10" t="n">
-        <v>7107940</v>
+        <v>7107730</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1632,11 +1639,6 @@
           <t>2025-05-18</t>
         </is>
       </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>rikligt med bladrosetter!</t>
-        </is>
-      </c>
       <c r="AD10" t="b">
         <v>0</v>
       </c>
@@ -1650,22 +1652,22 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Patrik Nygren</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Patrik Nygren</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>125223807</v>
+        <v>125225982</v>
       </c>
       <c r="B11" t="n">
-        <v>98101</v>
+        <v>98269</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1710,10 +1712,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>745315</v>
+        <v>745327</v>
       </c>
       <c r="R11" t="n">
-        <v>7107851</v>
+        <v>7107834</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1746,11 +1748,6 @@
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-05-18</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>Rikligt med bladrosetter!</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1778,10 +1775,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>125222246</v>
+        <v>125223203</v>
       </c>
       <c r="B12" t="n">
-        <v>91012</v>
+        <v>98269</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1790,34 +1787,35 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
       <c r="J12" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
@@ -1825,10 +1823,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>745262</v>
+        <v>745293</v>
       </c>
       <c r="R12" t="n">
-        <v>7107944</v>
+        <v>7107855</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1888,10 +1886,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>125232024</v>
+        <v>125222017</v>
       </c>
       <c r="B13" t="n">
-        <v>91012</v>
+        <v>98269</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1900,30 +1898,35 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="J13" t="inlineStr"/>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
       <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
@@ -1931,10 +1934,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>745288</v>
+        <v>745243</v>
       </c>
       <c r="R13" t="n">
-        <v>7107786</v>
+        <v>7107977</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1982,22 +1985,22 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Patrik Nygren</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Patrik Nygren</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>125226783</v>
+        <v>125222361</v>
       </c>
       <c r="B14" t="n">
-        <v>98101</v>
+        <v>98269</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2042,10 +2045,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>745294</v>
+        <v>745280</v>
       </c>
       <c r="R14" t="n">
-        <v>7107772</v>
+        <v>7107886</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2105,10 +2108,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>125222545</v>
+        <v>125223590</v>
       </c>
       <c r="B15" t="n">
-        <v>98101</v>
+        <v>98269</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2153,10 +2156,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>745294</v>
+        <v>745299</v>
       </c>
       <c r="R15" t="n">
-        <v>7107877</v>
+        <v>7107851</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2216,10 +2219,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>125222288</v>
+        <v>125231464</v>
       </c>
       <c r="B16" t="n">
-        <v>98101</v>
+        <v>79932</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2228,35 +2231,30 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>220787</v>
+        <v>6456</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
-      <c r="J16" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="J16" t="inlineStr"/>
       <c r="K16" t="inlineStr"/>
-      <c r="L16" t="inlineStr"/>
       <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
@@ -2264,10 +2262,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>745266</v>
+        <v>745287</v>
       </c>
       <c r="R16" t="n">
-        <v>7107910</v>
+        <v>7107886</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2315,22 +2313,22 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Patrik Nygren</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Patrik Nygren</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>125225686</v>
+        <v>125231948</v>
       </c>
       <c r="B17" t="n">
-        <v>91012</v>
+        <v>98269</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2339,34 +2337,31 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
-      <c r="J17" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+      <c r="J17" t="inlineStr"/>
       <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr"/>
       <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
@@ -2374,10 +2369,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>745321</v>
+        <v>745279</v>
       </c>
       <c r="R17" t="n">
-        <v>7107841</v>
+        <v>7107754</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2425,22 +2420,22 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Patrik Nygren</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Patrik Nygren</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>125222999</v>
+        <v>125222288</v>
       </c>
       <c r="B18" t="n">
-        <v>98101</v>
+        <v>98269</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2485,10 +2480,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>745290</v>
+        <v>745266</v>
       </c>
       <c r="R18" t="n">
-        <v>7107864</v>
+        <v>7107910</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2548,10 +2543,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>125222404</v>
+        <v>125231249</v>
       </c>
       <c r="B19" t="n">
-        <v>98101</v>
+        <v>98269</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2582,11 +2577,7 @@
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
-      <c r="J19" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="J19" t="inlineStr"/>
       <c r="K19" t="inlineStr"/>
       <c r="L19" t="inlineStr"/>
       <c r="N19" t="inlineStr"/>
@@ -2596,10 +2587,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>745290</v>
+        <v>745260</v>
       </c>
       <c r="R19" t="n">
-        <v>7107886</v>
+        <v>7107948</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2634,11 +2625,6 @@
           <t>2025-05-18</t>
         </is>
       </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>några kvadratmeter med bladrosetter</t>
-        </is>
-      </c>
       <c r="AD19" t="b">
         <v>0</v>
       </c>
@@ -2652,22 +2638,22 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Patrik Nygren</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Patrik Nygren</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>125226206</v>
+        <v>125222083</v>
       </c>
       <c r="B20" t="n">
-        <v>91012</v>
+        <v>91521</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2676,25 +2662,25 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>1202</v>
+        <v>2062</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Ulltickeporing</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Skeletocutis brevispora</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2711,10 +2697,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>745327</v>
+        <v>745262</v>
       </c>
       <c r="R20" t="n">
-        <v>7107827</v>
+        <v>7107946</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2774,10 +2760,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>125232195</v>
+        <v>125222073</v>
       </c>
       <c r="B21" t="n">
-        <v>79891</v>
+        <v>91166</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2790,25 +2776,29 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
-      <c r="J21" t="inlineStr"/>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K21" t="inlineStr"/>
       <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
@@ -2817,10 +2807,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>745215</v>
+        <v>745262</v>
       </c>
       <c r="R21" t="n">
-        <v>7107730</v>
+        <v>7107946</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2868,22 +2858,22 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Patrik Nygren</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Patrik Nygren</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>125231948</v>
+        <v>125228007</v>
       </c>
       <c r="B22" t="n">
-        <v>98101</v>
+        <v>57632</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2892,31 +2882,35 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
-      <c r="J22" t="inlineStr"/>
       <c r="K22" t="inlineStr"/>
       <c r="L22" t="inlineStr"/>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
@@ -2924,10 +2918,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>745279</v>
+        <v>745249</v>
       </c>
       <c r="R22" t="n">
-        <v>7107754</v>
+        <v>7107940</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2962,35 +2956,39 @@
           <t>2025-05-18</t>
         </is>
       </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>hackat hål i gran</t>
+        </is>
+      </c>
       <c r="AD22" t="b">
         <v>0</v>
       </c>
       <c r="AE22" t="b">
         <v>0</v>
       </c>
-      <c r="AF22" t="inlineStr"/>
       <c r="AG22" t="b">
         <v>0</v>
       </c>
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Patrik Nygren</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Patrik Nygren</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>125227728</v>
+        <v>125232181</v>
       </c>
       <c r="B23" t="n">
-        <v>98101</v>
+        <v>57632</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2999,35 +2997,31 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
-      <c r="J23" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
       <c r="K23" t="inlineStr"/>
       <c r="L23" t="inlineStr"/>
+      <c r="M23" t="inlineStr"/>
       <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
@@ -3035,10 +3029,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>745279</v>
+        <v>745227</v>
       </c>
       <c r="R23" t="n">
-        <v>7107831</v>
+        <v>7107774</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3079,29 +3073,28 @@
       <c r="AE23" t="b">
         <v>0</v>
       </c>
-      <c r="AF23" t="inlineStr"/>
       <c r="AG23" t="b">
         <v>0</v>
       </c>
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Patrik Nygren</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Patrik Nygren</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>125232212</v>
+        <v>125222246</v>
       </c>
       <c r="B24" t="n">
-        <v>98101</v>
+        <v>91166</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3110,31 +3103,34 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
-      <c r="J24" t="inlineStr"/>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K24" t="inlineStr"/>
-      <c r="L24" t="inlineStr"/>
       <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
@@ -3142,10 +3138,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>745252</v>
+        <v>745262</v>
       </c>
       <c r="R24" t="n">
-        <v>7107940</v>
+        <v>7107944</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3193,22 +3189,22 @@
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Patrik Nygren</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Patrik Nygren</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>125227901</v>
+        <v>125227728</v>
       </c>
       <c r="B25" t="n">
-        <v>98101</v>
+        <v>98269</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3253,10 +3249,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>745280</v>
+        <v>745279</v>
       </c>
       <c r="R25" t="n">
-        <v>7107886</v>
+        <v>7107831</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3316,10 +3312,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>125227327</v>
+        <v>125222545</v>
       </c>
       <c r="B26" t="n">
-        <v>98101</v>
+        <v>98269</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3364,10 +3360,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>745280</v>
+        <v>745294</v>
       </c>
       <c r="R26" t="n">
-        <v>7107795</v>
+        <v>7107877</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3427,10 +3423,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>125223425</v>
+        <v>125231618</v>
       </c>
       <c r="B27" t="n">
-        <v>98101</v>
+        <v>79932</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3439,35 +3435,30 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>220787</v>
+        <v>6456</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
-      <c r="J27" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="J27" t="inlineStr"/>
       <c r="K27" t="inlineStr"/>
-      <c r="L27" t="inlineStr"/>
       <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
@@ -3475,10 +3466,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>745298</v>
+        <v>745381</v>
       </c>
       <c r="R27" t="n">
-        <v>7107856</v>
+        <v>7107841</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3526,22 +3517,22 @@
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Patrik Nygren</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Patrik Nygren</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>125222754</v>
+        <v>125232024</v>
       </c>
       <c r="B28" t="n">
-        <v>98101</v>
+        <v>91166</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3550,35 +3541,30 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
-      <c r="J28" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="J28" t="inlineStr"/>
       <c r="K28" t="inlineStr"/>
-      <c r="L28" t="inlineStr"/>
       <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
@@ -3586,10 +3572,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>745306</v>
+        <v>745288</v>
       </c>
       <c r="R28" t="n">
-        <v>7107877</v>
+        <v>7107786</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3637,22 +3623,22 @@
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Patrik Nygren</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Patrik Nygren</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>125227446</v>
+        <v>125231696</v>
       </c>
       <c r="B29" t="n">
-        <v>98101</v>
+        <v>98290</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3661,33 +3647,29 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>220787</v>
+        <v>221952</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
-      <c r="J29" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="J29" t="inlineStr"/>
       <c r="K29" t="inlineStr"/>
       <c r="L29" t="inlineStr"/>
       <c r="N29" t="inlineStr"/>
@@ -3697,10 +3679,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>745280</v>
+        <v>745356</v>
       </c>
       <c r="R29" t="n">
-        <v>7107802</v>
+        <v>7107793</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3748,22 +3730,22 @@
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Patrik Nygren</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Patrik Nygren</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>125227797</v>
+        <v>125226783</v>
       </c>
       <c r="B30" t="n">
-        <v>98101</v>
+        <v>98269</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3808,10 +3790,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>745277</v>
+        <v>745294</v>
       </c>
       <c r="R30" t="n">
-        <v>7107838</v>
+        <v>7107772</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3871,10 +3853,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>125225490</v>
+        <v>125225686</v>
       </c>
       <c r="B31" t="n">
-        <v>91361</v>
+        <v>91166</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3883,25 +3865,25 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>2062</v>
+        <v>1202</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Ulltickeporing</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Skeletocutis brevispora</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3981,10 +3963,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>125222083</v>
+        <v>125231983</v>
       </c>
       <c r="B32" t="n">
-        <v>91361</v>
+        <v>98269</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -3997,30 +3979,27 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>2062</v>
+        <v>220787</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Ulltickeporing</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Skeletocutis brevispora</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
-      <c r="J32" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+      <c r="J32" t="inlineStr"/>
       <c r="K32" t="inlineStr"/>
+      <c r="L32" t="inlineStr"/>
       <c r="N32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
@@ -4028,10 +4007,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>745262</v>
+        <v>745279</v>
       </c>
       <c r="R32" t="n">
-        <v>7107946</v>
+        <v>7107767</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4079,22 +4058,22 @@
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Patrik Nygren</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Patrik Nygren</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>125222055</v>
+        <v>125232212</v>
       </c>
       <c r="B33" t="n">
-        <v>91012</v>
+        <v>98269</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4103,34 +4082,31 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
-      <c r="J33" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+      <c r="J33" t="inlineStr"/>
       <c r="K33" t="inlineStr"/>
+      <c r="L33" t="inlineStr"/>
       <c r="N33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
@@ -4138,10 +4114,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>745262</v>
+        <v>745252</v>
       </c>
       <c r="R33" t="n">
-        <v>7107948</v>
+        <v>7107940</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4189,22 +4165,22 @@
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Patrik Nygren</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Patrik Nygren</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>125231658</v>
+        <v>125222999</v>
       </c>
       <c r="B34" t="n">
-        <v>90977</v>
+        <v>98269</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4213,30 +4189,35 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>5447</v>
+        <v>220787</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
-      <c r="J34" t="inlineStr"/>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K34" t="inlineStr"/>
+      <c r="L34" t="inlineStr"/>
       <c r="N34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
@@ -4244,10 +4225,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>745405</v>
+        <v>745290</v>
       </c>
       <c r="R34" t="n">
-        <v>7107837</v>
+        <v>7107864</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4295,22 +4276,22 @@
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Patrik Nygren</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Patrik Nygren</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>125228007</v>
+        <v>125230982</v>
       </c>
       <c r="B35" t="n">
-        <v>57529</v>
+        <v>98269</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4319,35 +4300,31 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
+      <c r="J35" t="inlineStr"/>
       <c r="K35" t="inlineStr"/>
       <c r="L35" t="inlineStr"/>
-      <c r="M35" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
@@ -4355,10 +4332,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>745249</v>
+        <v>745259</v>
       </c>
       <c r="R35" t="n">
-        <v>7107940</v>
+        <v>7107964</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4393,39 +4370,35 @@
           <t>2025-05-18</t>
         </is>
       </c>
-      <c r="AC35" t="inlineStr">
-        <is>
-          <t>hackat hål i gran</t>
-        </is>
-      </c>
       <c r="AD35" t="b">
         <v>0</v>
       </c>
       <c r="AE35" t="b">
         <v>0</v>
       </c>
+      <c r="AF35" t="inlineStr"/>
       <c r="AG35" t="b">
         <v>0</v>
       </c>
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Patrik Nygren</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Patrik Nygren</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>125232283</v>
+        <v>125231838</v>
       </c>
       <c r="B36" t="n">
-        <v>57883</v>
+        <v>98269</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4434,31 +4407,31 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>103015</v>
+        <v>220787</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
+      <c r="J36" t="inlineStr"/>
       <c r="K36" t="inlineStr"/>
       <c r="L36" t="inlineStr"/>
-      <c r="M36" t="inlineStr"/>
       <c r="N36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
@@ -4466,13 +4439,13 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>745254</v>
+        <v>745310</v>
       </c>
       <c r="R36" t="n">
-        <v>7107972</v>
+        <v>7107765</v>
       </c>
       <c r="S36" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -4510,6 +4483,7 @@
       <c r="AE36" t="b">
         <v>0</v>
       </c>
+      <c r="AF36" t="inlineStr"/>
       <c r="AG36" t="b">
         <v>0</v>
       </c>
@@ -4528,10 +4502,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>125231464</v>
+        <v>125227446</v>
       </c>
       <c r="B37" t="n">
-        <v>79795</v>
+        <v>98269</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4540,30 +4514,35 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6456</v>
+        <v>220787</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
-      <c r="J37" t="inlineStr"/>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K37" t="inlineStr"/>
+      <c r="L37" t="inlineStr"/>
       <c r="N37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
@@ -4571,10 +4550,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>745287</v>
+        <v>745280</v>
       </c>
       <c r="R37" t="n">
-        <v>7107886</v>
+        <v>7107802</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4622,22 +4601,22 @@
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Patrik Nygren</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Patrik Nygren</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>125230982</v>
+        <v>125231658</v>
       </c>
       <c r="B38" t="n">
-        <v>98101</v>
+        <v>91131</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4646,31 +4625,30 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>220787</v>
+        <v>5447</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
       <c r="J38" t="inlineStr"/>
       <c r="K38" t="inlineStr"/>
-      <c r="L38" t="inlineStr"/>
       <c r="N38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
@@ -4678,10 +4656,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>745259</v>
+        <v>745405</v>
       </c>
       <c r="R38" t="n">
-        <v>7107964</v>
+        <v>7107837</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4741,10 +4719,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>125227661</v>
+        <v>125227797</v>
       </c>
       <c r="B39" t="n">
-        <v>98101</v>
+        <v>98269</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4789,10 +4767,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>745280</v>
+        <v>745277</v>
       </c>
       <c r="R39" t="n">
-        <v>7107827</v>
+        <v>7107838</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4852,10 +4830,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>125232181</v>
+        <v>125228040</v>
       </c>
       <c r="B40" t="n">
-        <v>57529</v>
+        <v>98269</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4864,31 +4842,35 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K40" t="inlineStr"/>
       <c r="L40" t="inlineStr"/>
-      <c r="M40" t="inlineStr"/>
       <c r="N40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
@@ -4896,10 +4878,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>745227</v>
+        <v>745249</v>
       </c>
       <c r="R40" t="n">
-        <v>7107774</v>
+        <v>7107940</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4934,34 +4916,40 @@
           <t>2025-05-18</t>
         </is>
       </c>
+      <c r="AC40" t="inlineStr">
+        <is>
+          <t>rikligt med bladrosetter!</t>
+        </is>
+      </c>
       <c r="AD40" t="b">
         <v>0</v>
       </c>
       <c r="AE40" t="b">
         <v>0</v>
       </c>
+      <c r="AF40" t="inlineStr"/>
       <c r="AG40" t="b">
         <v>0</v>
       </c>
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Patrik Nygren</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Patrik Nygren</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>125231105</v>
+        <v>125226206</v>
       </c>
       <c r="B41" t="n">
-        <v>79920</v>
+        <v>91166</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -4970,29 +4958,33 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6462</v>
+        <v>1202</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
-      <c r="J41" t="inlineStr"/>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K41" t="inlineStr"/>
       <c r="N41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
@@ -5001,10 +4993,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>745259</v>
+        <v>745327</v>
       </c>
       <c r="R41" t="n">
-        <v>7107964</v>
+        <v>7107827</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5052,22 +5044,22 @@
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Patrik Nygren</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Patrik Nygren</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>125223203</v>
+        <v>125231309</v>
       </c>
       <c r="B42" t="n">
-        <v>98101</v>
+        <v>98269</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -5098,11 +5090,7 @@
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
-      <c r="J42" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="J42" t="inlineStr"/>
       <c r="K42" t="inlineStr"/>
       <c r="L42" t="inlineStr"/>
       <c r="N42" t="inlineStr"/>
@@ -5112,10 +5100,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>745293</v>
+        <v>745268</v>
       </c>
       <c r="R42" t="n">
-        <v>7107855</v>
+        <v>7107926</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5163,22 +5151,22 @@
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Patrik Nygren</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Patrik Nygren</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>125231696</v>
+        <v>125225490</v>
       </c>
       <c r="B43" t="n">
-        <v>98122</v>
+        <v>91521</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5187,31 +5175,34 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>221952</v>
+        <v>2062</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Ulltickeporing</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Skeletocutis brevispora</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
-      <c r="J43" t="inlineStr"/>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K43" t="inlineStr"/>
-      <c r="L43" t="inlineStr"/>
       <c r="N43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
@@ -5219,10 +5210,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>745356</v>
+        <v>745321</v>
       </c>
       <c r="R43" t="n">
-        <v>7107793</v>
+        <v>7107841</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5270,22 +5261,22 @@
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Patrik Nygren</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Patrik Nygren</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>125231779</v>
+        <v>125227661</v>
       </c>
       <c r="B44" t="n">
-        <v>79920</v>
+        <v>98269</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5294,30 +5285,35 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6462</v>
+        <v>220787</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
-      <c r="J44" t="inlineStr"/>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K44" t="inlineStr"/>
+      <c r="L44" t="inlineStr"/>
       <c r="N44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
@@ -5325,10 +5321,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>745323</v>
+        <v>745280</v>
       </c>
       <c r="R44" t="n">
-        <v>7107772</v>
+        <v>7107827</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5376,22 +5372,22 @@
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Patrik Nygren</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Patrik Nygren</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>125231618</v>
+        <v>125232283</v>
       </c>
       <c r="B45" t="n">
-        <v>79795</v>
+        <v>58001</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5404,26 +5400,27 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6456</v>
+        <v>103015</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
-      <c r="J45" t="inlineStr"/>
       <c r="K45" t="inlineStr"/>
+      <c r="L45" t="inlineStr"/>
+      <c r="M45" t="inlineStr"/>
       <c r="N45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
@@ -5431,13 +5428,13 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>745381</v>
+        <v>745254</v>
       </c>
       <c r="R45" t="n">
-        <v>7107841</v>
+        <v>7107972</v>
       </c>
       <c r="S45" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -5475,7 +5472,6 @@
       <c r="AE45" t="b">
         <v>0</v>
       </c>
-      <c r="AF45" t="inlineStr"/>
       <c r="AG45" t="b">
         <v>0</v>
       </c>
@@ -5494,10 +5490,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>125231545</v>
+        <v>125223807</v>
       </c>
       <c r="B46" t="n">
-        <v>79795</v>
+        <v>98269</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5506,30 +5502,35 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6456</v>
+        <v>220787</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
-      <c r="J46" t="inlineStr"/>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K46" t="inlineStr"/>
+      <c r="L46" t="inlineStr"/>
       <c r="N46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
@@ -5537,10 +5538,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>745310</v>
+        <v>745315</v>
       </c>
       <c r="R46" t="n">
-        <v>7107876</v>
+        <v>7107851</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5575,6 +5576,11 @@
           <t>2025-05-18</t>
         </is>
       </c>
+      <c r="AC46" t="inlineStr">
+        <is>
+          <t>Rikligt med bladrosetter!</t>
+        </is>
+      </c>
       <c r="AD46" t="b">
         <v>0</v>
       </c>
@@ -5588,22 +5594,22 @@
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Patrik Nygren</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Patrik Nygren</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>125225982</v>
+        <v>125231342</v>
       </c>
       <c r="B47" t="n">
-        <v>98101</v>
+        <v>98269</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5634,11 +5640,7 @@
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
-      <c r="J47" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="J47" t="inlineStr"/>
       <c r="K47" t="inlineStr"/>
       <c r="L47" t="inlineStr"/>
       <c r="N47" t="inlineStr"/>
@@ -5648,10 +5650,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>745327</v>
+        <v>745267</v>
       </c>
       <c r="R47" t="n">
-        <v>7107834</v>
+        <v>7107907</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5699,22 +5701,22 @@
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>Patrik Nygren</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Patrik Nygren</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>125222017</v>
+        <v>125231545</v>
       </c>
       <c r="B48" t="n">
-        <v>98101</v>
+        <v>79932</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5723,35 +5725,30 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>220787</v>
+        <v>6456</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
-      <c r="J48" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="J48" t="inlineStr"/>
       <c r="K48" t="inlineStr"/>
-      <c r="L48" t="inlineStr"/>
       <c r="N48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
@@ -5759,10 +5756,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>745243</v>
+        <v>745310</v>
       </c>
       <c r="R48" t="n">
-        <v>7107977</v>
+        <v>7107876</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5810,22 +5807,22 @@
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>Patrik Nygren</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>Patrik Nygren</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>125226477</v>
+        <v>125222055</v>
       </c>
       <c r="B49" t="n">
-        <v>91012</v>
+        <v>91166</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -5869,10 +5866,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>745445</v>
+        <v>745262</v>
       </c>
       <c r="R49" t="n">
-        <v>7107841</v>
+        <v>7107948</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5932,10 +5929,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>125231342</v>
+        <v>125226477</v>
       </c>
       <c r="B50" t="n">
-        <v>98101</v>
+        <v>91166</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -5944,31 +5941,34 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
-      <c r="J50" t="inlineStr"/>
+      <c r="J50" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K50" t="inlineStr"/>
-      <c r="L50" t="inlineStr"/>
       <c r="N50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
@@ -5976,10 +5976,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>745267</v>
+        <v>745445</v>
       </c>
       <c r="R50" t="n">
-        <v>7107907</v>
+        <v>7107841</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -6027,12 +6027,12 @@
       <c r="AT50" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Patrik Nygren</t>
         </is>
       </c>
       <c r="AX50" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Patrik Nygren</t>
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>

--- a/artfynd/A 53969-2024 artfynd.xlsx
+++ b/artfynd/A 53969-2024 artfynd.xlsx
@@ -781,10 +781,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>125227847</v>
+        <v>125223590</v>
       </c>
       <c r="B3" t="n">
-        <v>57632</v>
+        <v>98269</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,35 +793,35 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -829,10 +829,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>745285</v>
+        <v>745299</v>
       </c>
       <c r="R3" t="n">
-        <v>7107862</v>
+        <v>7107851</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -867,17 +867,13 @@
           <t>2025-05-18</t>
         </is>
       </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>hack i död gran</t>
-        </is>
-      </c>
       <c r="AD3" t="b">
         <v>0</v>
       </c>
       <c r="AE3" t="b">
         <v>0</v>
       </c>
+      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -896,7 +892,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>125223425</v>
+        <v>125231249</v>
       </c>
       <c r="B4" t="n">
         <v>98269</v>
@@ -930,11 +926,7 @@
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
@@ -944,10 +936,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>745298</v>
+        <v>745260</v>
       </c>
       <c r="R4" t="n">
-        <v>7107856</v>
+        <v>7107948</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -995,19 +987,19 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Patrik Nygren</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Patrik Nygren</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>125222404</v>
+        <v>125231838</v>
       </c>
       <c r="B5" t="n">
         <v>98269</v>
@@ -1041,11 +1033,7 @@
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr"/>
       <c r="N5" t="inlineStr"/>
@@ -1055,10 +1043,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>745290</v>
+        <v>745310</v>
       </c>
       <c r="R5" t="n">
-        <v>7107886</v>
+        <v>7107765</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1093,11 +1081,6 @@
           <t>2025-05-18</t>
         </is>
       </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>några kvadratmeter med bladrosetter</t>
-        </is>
-      </c>
       <c r="AD5" t="b">
         <v>0</v>
       </c>
@@ -1111,19 +1094,19 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Patrik Nygren</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Patrik Nygren</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>125222754</v>
+        <v>125227901</v>
       </c>
       <c r="B6" t="n">
         <v>98269</v>
@@ -1171,10 +1154,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>745306</v>
+        <v>745280</v>
       </c>
       <c r="R6" t="n">
-        <v>7107877</v>
+        <v>7107886</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1234,10 +1217,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>125227327</v>
+        <v>125225490</v>
       </c>
       <c r="B7" t="n">
-        <v>98269</v>
+        <v>91521</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1250,31 +1233,30 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>220787</v>
+        <v>2062</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ulltickeporing</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Skeletocutis brevispora</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="J7" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
@@ -1282,10 +1264,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>745280</v>
+        <v>745321</v>
       </c>
       <c r="R7" t="n">
-        <v>7107795</v>
+        <v>7107841</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1345,10 +1327,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>125231888</v>
+        <v>125232181</v>
       </c>
       <c r="B8" t="n">
-        <v>98269</v>
+        <v>57632</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1357,31 +1339,31 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
       <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr"/>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
@@ -1389,10 +1371,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>745297</v>
+        <v>745227</v>
       </c>
       <c r="R8" t="n">
-        <v>7107757</v>
+        <v>7107774</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1433,7 +1415,6 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
-      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
@@ -1452,10 +1433,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>125231105</v>
+        <v>125231948</v>
       </c>
       <c r="B9" t="n">
-        <v>80057</v>
+        <v>98269</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1464,30 +1445,31 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6462</v>
+        <v>220787</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="J9" t="inlineStr"/>
       <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
@@ -1495,10 +1477,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>745259</v>
+        <v>745279</v>
       </c>
       <c r="R9" t="n">
-        <v>7107964</v>
+        <v>7107754</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1558,10 +1540,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>125232195</v>
+        <v>125231309</v>
       </c>
       <c r="B10" t="n">
-        <v>80028</v>
+        <v>98269</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1570,30 +1552,31 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="J10" t="inlineStr"/>
       <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
@@ -1601,10 +1584,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>745215</v>
+        <v>745268</v>
       </c>
       <c r="R10" t="n">
-        <v>7107730</v>
+        <v>7107926</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1664,10 +1647,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>125225982</v>
+        <v>125222073</v>
       </c>
       <c r="B11" t="n">
-        <v>98269</v>
+        <v>91166</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1676,35 +1659,34 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="J11" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K11" t="inlineStr"/>
-      <c r="L11" t="inlineStr"/>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
@@ -1712,10 +1694,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>745327</v>
+        <v>745262</v>
       </c>
       <c r="R11" t="n">
-        <v>7107834</v>
+        <v>7107946</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1775,7 +1757,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>125223203</v>
+        <v>125231888</v>
       </c>
       <c r="B12" t="n">
         <v>98269</v>
@@ -1809,11 +1791,7 @@
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="J12" t="inlineStr"/>
       <c r="K12" t="inlineStr"/>
       <c r="L12" t="inlineStr"/>
       <c r="N12" t="inlineStr"/>
@@ -1823,10 +1801,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>745293</v>
+        <v>745297</v>
       </c>
       <c r="R12" t="n">
-        <v>7107855</v>
+        <v>7107757</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1874,19 +1852,19 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Patrik Nygren</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Patrik Nygren</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>125222017</v>
+        <v>125227728</v>
       </c>
       <c r="B13" t="n">
         <v>98269</v>
@@ -1934,10 +1912,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>745243</v>
+        <v>745279</v>
       </c>
       <c r="R13" t="n">
-        <v>7107977</v>
+        <v>7107831</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1997,7 +1975,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>125222361</v>
+        <v>125232212</v>
       </c>
       <c r="B14" t="n">
         <v>98269</v>
@@ -2031,11 +2009,7 @@
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="J14" t="inlineStr"/>
       <c r="K14" t="inlineStr"/>
       <c r="L14" t="inlineStr"/>
       <c r="N14" t="inlineStr"/>
@@ -2045,10 +2019,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>745280</v>
+        <v>745252</v>
       </c>
       <c r="R14" t="n">
-        <v>7107886</v>
+        <v>7107940</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2096,19 +2070,19 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Patrik Nygren</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Patrik Nygren</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>125223590</v>
+        <v>125222017</v>
       </c>
       <c r="B15" t="n">
         <v>98269</v>
@@ -2156,10 +2130,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>745299</v>
+        <v>745243</v>
       </c>
       <c r="R15" t="n">
-        <v>7107851</v>
+        <v>7107977</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2219,10 +2193,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>125231464</v>
+        <v>125222055</v>
       </c>
       <c r="B16" t="n">
-        <v>79932</v>
+        <v>91166</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2231,29 +2205,33 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6456</v>
+        <v>1202</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
-      <c r="J16" t="inlineStr"/>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K16" t="inlineStr"/>
       <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
@@ -2262,10 +2240,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>745287</v>
+        <v>745262</v>
       </c>
       <c r="R16" t="n">
-        <v>7107886</v>
+        <v>7107948</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2313,22 +2291,22 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Patrik Nygren</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Patrik Nygren</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>125231948</v>
+        <v>125228007</v>
       </c>
       <c r="B17" t="n">
-        <v>98269</v>
+        <v>57632</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2337,31 +2315,35 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
-      <c r="J17" t="inlineStr"/>
       <c r="K17" t="inlineStr"/>
       <c r="L17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
@@ -2369,10 +2351,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>745279</v>
+        <v>745249</v>
       </c>
       <c r="R17" t="n">
-        <v>7107754</v>
+        <v>7107940</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2407,32 +2389,36 @@
           <t>2025-05-18</t>
         </is>
       </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>hackat hål i gran</t>
+        </is>
+      </c>
       <c r="AD17" t="b">
         <v>0</v>
       </c>
       <c r="AE17" t="b">
         <v>0</v>
       </c>
-      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
       </c>
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Patrik Nygren</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Patrik Nygren</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>125222288</v>
+        <v>125223425</v>
       </c>
       <c r="B18" t="n">
         <v>98269</v>
@@ -2480,10 +2466,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>745266</v>
+        <v>745298</v>
       </c>
       <c r="R18" t="n">
-        <v>7107910</v>
+        <v>7107856</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2543,7 +2529,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>125231249</v>
+        <v>125222754</v>
       </c>
       <c r="B19" t="n">
         <v>98269</v>
@@ -2577,7 +2563,11 @@
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
-      <c r="J19" t="inlineStr"/>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K19" t="inlineStr"/>
       <c r="L19" t="inlineStr"/>
       <c r="N19" t="inlineStr"/>
@@ -2587,10 +2577,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>745260</v>
+        <v>745306</v>
       </c>
       <c r="R19" t="n">
-        <v>7107948</v>
+        <v>7107877</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2638,22 +2628,22 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Patrik Nygren</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Patrik Nygren</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>125222083</v>
+        <v>125232283</v>
       </c>
       <c r="B20" t="n">
-        <v>91521</v>
+        <v>58001</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2662,34 +2652,31 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>2062</v>
+        <v>103015</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Ulltickeporing</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Skeletocutis brevispora</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
-      <c r="J20" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
       <c r="K20" t="inlineStr"/>
+      <c r="L20" t="inlineStr"/>
+      <c r="M20" t="inlineStr"/>
       <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
@@ -2697,13 +2684,13 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>745262</v>
+        <v>745254</v>
       </c>
       <c r="R20" t="n">
-        <v>7107946</v>
+        <v>7107972</v>
       </c>
       <c r="S20" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2741,29 +2728,28 @@
       <c r="AE20" t="b">
         <v>0</v>
       </c>
-      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
       </c>
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Patrik Nygren</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Patrik Nygren</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>125222073</v>
+        <v>125231545</v>
       </c>
       <c r="B21" t="n">
-        <v>91166</v>
+        <v>79932</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2772,33 +2758,29 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>1202</v>
+        <v>6456</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
-      <c r="J21" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+      <c r="J21" t="inlineStr"/>
       <c r="K21" t="inlineStr"/>
       <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
@@ -2807,10 +2789,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>745262</v>
+        <v>745310</v>
       </c>
       <c r="R21" t="n">
-        <v>7107946</v>
+        <v>7107876</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2858,19 +2840,19 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Patrik Nygren</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Patrik Nygren</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>125228007</v>
+        <v>125227847</v>
       </c>
       <c r="B22" t="n">
         <v>57632</v>
@@ -2908,7 +2890,7 @@
       <c r="L22" t="inlineStr"/>
       <c r="M22" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N22" t="inlineStr"/>
@@ -2918,10 +2900,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>745249</v>
+        <v>745285</v>
       </c>
       <c r="R22" t="n">
-        <v>7107940</v>
+        <v>7107862</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2958,7 +2940,7 @@
       </c>
       <c r="AC22" t="inlineStr">
         <is>
-          <t>hackat hål i gran</t>
+          <t>hack i död gran</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2985,10 +2967,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>125232181</v>
+        <v>125223807</v>
       </c>
       <c r="B23" t="n">
-        <v>57632</v>
+        <v>98269</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2997,31 +2979,35 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K23" t="inlineStr"/>
       <c r="L23" t="inlineStr"/>
-      <c r="M23" t="inlineStr"/>
       <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
@@ -3029,10 +3015,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>745227</v>
+        <v>745315</v>
       </c>
       <c r="R23" t="n">
-        <v>7107774</v>
+        <v>7107851</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3067,34 +3053,40 @@
           <t>2025-05-18</t>
         </is>
       </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>Rikligt med bladrosetter!</t>
+        </is>
+      </c>
       <c r="AD23" t="b">
         <v>0</v>
       </c>
       <c r="AE23" t="b">
         <v>0</v>
       </c>
+      <c r="AF23" t="inlineStr"/>
       <c r="AG23" t="b">
         <v>0</v>
       </c>
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Patrik Nygren</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Patrik Nygren</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>125222246</v>
+        <v>125230982</v>
       </c>
       <c r="B24" t="n">
-        <v>91166</v>
+        <v>98269</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3103,34 +3095,31 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
-      <c r="J24" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+      <c r="J24" t="inlineStr"/>
       <c r="K24" t="inlineStr"/>
+      <c r="L24" t="inlineStr"/>
       <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
@@ -3138,10 +3127,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>745262</v>
+        <v>745259</v>
       </c>
       <c r="R24" t="n">
-        <v>7107944</v>
+        <v>7107964</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3189,19 +3178,19 @@
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Patrik Nygren</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Patrik Nygren</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>125227728</v>
+        <v>125227327</v>
       </c>
       <c r="B25" t="n">
         <v>98269</v>
@@ -3249,10 +3238,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>745279</v>
+        <v>745280</v>
       </c>
       <c r="R25" t="n">
-        <v>7107831</v>
+        <v>7107795</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3312,7 +3301,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>125222545</v>
+        <v>125228040</v>
       </c>
       <c r="B26" t="n">
         <v>98269</v>
@@ -3360,10 +3349,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>745294</v>
+        <v>745249</v>
       </c>
       <c r="R26" t="n">
-        <v>7107877</v>
+        <v>7107940</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3396,6 +3385,11 @@
       <c r="AA26" t="inlineStr">
         <is>
           <t>2025-05-18</t>
+        </is>
+      </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>rikligt med bladrosetter!</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3423,10 +3417,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>125231618</v>
+        <v>125232195</v>
       </c>
       <c r="B27" t="n">
-        <v>79932</v>
+        <v>80028</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3435,25 +3429,25 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6456</v>
+        <v>6458</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3466,10 +3460,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>745381</v>
+        <v>745215</v>
       </c>
       <c r="R27" t="n">
-        <v>7107841</v>
+        <v>7107730</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3529,7 +3523,7 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>125232024</v>
+        <v>125226477</v>
       </c>
       <c r="B28" t="n">
         <v>91166</v>
@@ -3563,7 +3557,11 @@
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
-      <c r="J28" t="inlineStr"/>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K28" t="inlineStr"/>
       <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
@@ -3572,10 +3570,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>745288</v>
+        <v>745445</v>
       </c>
       <c r="R28" t="n">
-        <v>7107786</v>
+        <v>7107841</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3623,22 +3621,22 @@
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Patrik Nygren</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Patrik Nygren</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>125231696</v>
+        <v>125231105</v>
       </c>
       <c r="B29" t="n">
-        <v>98290</v>
+        <v>80057</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3651,27 +3649,26 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>221952</v>
+        <v>6462</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
       <c r="J29" t="inlineStr"/>
       <c r="K29" t="inlineStr"/>
-      <c r="L29" t="inlineStr"/>
       <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
@@ -3679,10 +3676,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>745356</v>
+        <v>745259</v>
       </c>
       <c r="R29" t="n">
-        <v>7107793</v>
+        <v>7107964</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3742,7 +3739,7 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>125226783</v>
+        <v>125222404</v>
       </c>
       <c r="B30" t="n">
         <v>98269</v>
@@ -3790,10 +3787,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>745294</v>
+        <v>745290</v>
       </c>
       <c r="R30" t="n">
-        <v>7107772</v>
+        <v>7107886</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3826,6 +3823,11 @@
       <c r="AA30" t="inlineStr">
         <is>
           <t>2025-05-18</t>
+        </is>
+      </c>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>några kvadratmeter med bladrosetter</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3853,10 +3855,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>125225686</v>
+        <v>125231342</v>
       </c>
       <c r="B31" t="n">
-        <v>91166</v>
+        <v>98269</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3865,34 +3867,31 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
-      <c r="J31" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+      <c r="J31" t="inlineStr"/>
       <c r="K31" t="inlineStr"/>
+      <c r="L31" t="inlineStr"/>
       <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
@@ -3900,10 +3899,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>745321</v>
+        <v>745267</v>
       </c>
       <c r="R31" t="n">
-        <v>7107841</v>
+        <v>7107907</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3951,22 +3950,22 @@
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Patrik Nygren</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Patrik Nygren</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>125231983</v>
+        <v>125222083</v>
       </c>
       <c r="B32" t="n">
-        <v>98269</v>
+        <v>91521</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -3979,27 +3978,30 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>220787</v>
+        <v>2062</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ulltickeporing</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Skeletocutis brevispora</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
-      <c r="J32" t="inlineStr"/>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K32" t="inlineStr"/>
-      <c r="L32" t="inlineStr"/>
       <c r="N32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
@@ -4007,10 +4009,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>745279</v>
+        <v>745262</v>
       </c>
       <c r="R32" t="n">
-        <v>7107767</v>
+        <v>7107946</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4058,19 +4060,19 @@
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Patrik Nygren</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Patrik Nygren</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>125232212</v>
+        <v>125231983</v>
       </c>
       <c r="B33" t="n">
         <v>98269</v>
@@ -4114,10 +4116,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>745252</v>
+        <v>745279</v>
       </c>
       <c r="R33" t="n">
-        <v>7107940</v>
+        <v>7107767</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4177,10 +4179,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>125222999</v>
+        <v>125231464</v>
       </c>
       <c r="B34" t="n">
-        <v>98269</v>
+        <v>79932</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4189,35 +4191,30 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>220787</v>
+        <v>6456</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
-      <c r="J34" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="J34" t="inlineStr"/>
       <c r="K34" t="inlineStr"/>
-      <c r="L34" t="inlineStr"/>
       <c r="N34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
@@ -4225,10 +4222,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>745290</v>
+        <v>745287</v>
       </c>
       <c r="R34" t="n">
-        <v>7107864</v>
+        <v>7107886</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4276,19 +4273,19 @@
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Patrik Nygren</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Patrik Nygren</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>125230982</v>
+        <v>125226783</v>
       </c>
       <c r="B35" t="n">
         <v>98269</v>
@@ -4322,7 +4319,11 @@
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
-      <c r="J35" t="inlineStr"/>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K35" t="inlineStr"/>
       <c r="L35" t="inlineStr"/>
       <c r="N35" t="inlineStr"/>
@@ -4332,10 +4333,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>745259</v>
+        <v>745294</v>
       </c>
       <c r="R35" t="n">
-        <v>7107964</v>
+        <v>7107772</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4383,19 +4384,19 @@
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Patrik Nygren</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Patrik Nygren</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>125231838</v>
+        <v>125227446</v>
       </c>
       <c r="B36" t="n">
         <v>98269</v>
@@ -4429,7 +4430,11 @@
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
-      <c r="J36" t="inlineStr"/>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K36" t="inlineStr"/>
       <c r="L36" t="inlineStr"/>
       <c r="N36" t="inlineStr"/>
@@ -4439,10 +4444,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>745310</v>
+        <v>745280</v>
       </c>
       <c r="R36" t="n">
-        <v>7107765</v>
+        <v>7107802</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4490,19 +4495,19 @@
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Patrik Nygren</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Patrik Nygren</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>125227446</v>
+        <v>125223203</v>
       </c>
       <c r="B37" t="n">
         <v>98269</v>
@@ -4550,10 +4555,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>745280</v>
+        <v>745293</v>
       </c>
       <c r="R37" t="n">
-        <v>7107802</v>
+        <v>7107855</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4613,10 +4618,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>125231658</v>
+        <v>125231696</v>
       </c>
       <c r="B38" t="n">
-        <v>91131</v>
+        <v>98290</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4629,26 +4634,27 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>5447</v>
+        <v>221952</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
       <c r="J38" t="inlineStr"/>
       <c r="K38" t="inlineStr"/>
+      <c r="L38" t="inlineStr"/>
       <c r="N38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
@@ -4656,10 +4662,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>745405</v>
+        <v>745356</v>
       </c>
       <c r="R38" t="n">
-        <v>7107837</v>
+        <v>7107793</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4719,7 +4725,7 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>125227797</v>
+        <v>125222545</v>
       </c>
       <c r="B39" t="n">
         <v>98269</v>
@@ -4767,10 +4773,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>745277</v>
+        <v>745294</v>
       </c>
       <c r="R39" t="n">
-        <v>7107838</v>
+        <v>7107877</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4830,7 +4836,7 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>125228040</v>
+        <v>125227797</v>
       </c>
       <c r="B40" t="n">
         <v>98269</v>
@@ -4878,10 +4884,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>745249</v>
+        <v>745277</v>
       </c>
       <c r="R40" t="n">
-        <v>7107940</v>
+        <v>7107838</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4914,11 +4920,6 @@
       <c r="AA40" t="inlineStr">
         <is>
           <t>2025-05-18</t>
-        </is>
-      </c>
-      <c r="AC40" t="inlineStr">
-        <is>
-          <t>rikligt med bladrosetter!</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4946,10 +4947,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>125226206</v>
+        <v>125231618</v>
       </c>
       <c r="B41" t="n">
-        <v>91166</v>
+        <v>79932</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -4958,33 +4959,29 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>1202</v>
+        <v>6456</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
-      <c r="J41" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+      <c r="J41" t="inlineStr"/>
       <c r="K41" t="inlineStr"/>
       <c r="N41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
@@ -4993,10 +4990,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>745327</v>
+        <v>745381</v>
       </c>
       <c r="R41" t="n">
-        <v>7107827</v>
+        <v>7107841</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5044,22 +5041,22 @@
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Patrik Nygren</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Patrik Nygren</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>125231309</v>
+        <v>125226206</v>
       </c>
       <c r="B42" t="n">
-        <v>98269</v>
+        <v>91166</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -5068,31 +5065,34 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
-      <c r="J42" t="inlineStr"/>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K42" t="inlineStr"/>
-      <c r="L42" t="inlineStr"/>
       <c r="N42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
@@ -5100,10 +5100,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>745268</v>
+        <v>745327</v>
       </c>
       <c r="R42" t="n">
-        <v>7107926</v>
+        <v>7107827</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5151,22 +5151,22 @@
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Patrik Nygren</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Patrik Nygren</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>125225490</v>
+        <v>125225686</v>
       </c>
       <c r="B43" t="n">
-        <v>91521</v>
+        <v>91166</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5175,25 +5175,25 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>2062</v>
+        <v>1202</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Ulltickeporing</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Skeletocutis brevispora</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -5273,10 +5273,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>125227661</v>
+        <v>125232024</v>
       </c>
       <c r="B44" t="n">
-        <v>98269</v>
+        <v>91166</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5285,35 +5285,30 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
-      <c r="J44" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="J44" t="inlineStr"/>
       <c r="K44" t="inlineStr"/>
-      <c r="L44" t="inlineStr"/>
       <c r="N44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
@@ -5321,10 +5316,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>745280</v>
+        <v>745288</v>
       </c>
       <c r="R44" t="n">
-        <v>7107827</v>
+        <v>7107786</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5372,22 +5367,22 @@
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>Patrik Nygren</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Patrik Nygren</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>125232283</v>
+        <v>125222246</v>
       </c>
       <c r="B45" t="n">
-        <v>58001</v>
+        <v>91166</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5396,31 +5391,34 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>103015</v>
+        <v>1202</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K45" t="inlineStr"/>
-      <c r="L45" t="inlineStr"/>
-      <c r="M45" t="inlineStr"/>
       <c r="N45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
@@ -5428,13 +5426,13 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>745254</v>
+        <v>745262</v>
       </c>
       <c r="R45" t="n">
-        <v>7107972</v>
+        <v>7107944</v>
       </c>
       <c r="S45" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -5472,25 +5470,26 @@
       <c r="AE45" t="b">
         <v>0</v>
       </c>
+      <c r="AF45" t="inlineStr"/>
       <c r="AG45" t="b">
         <v>0</v>
       </c>
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Patrik Nygren</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Patrik Nygren</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>125223807</v>
+        <v>125225982</v>
       </c>
       <c r="B46" t="n">
         <v>98269</v>
@@ -5538,10 +5537,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>745315</v>
+        <v>745327</v>
       </c>
       <c r="R46" t="n">
-        <v>7107851</v>
+        <v>7107834</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5574,11 +5573,6 @@
       <c r="AA46" t="inlineStr">
         <is>
           <t>2025-05-18</t>
-        </is>
-      </c>
-      <c r="AC46" t="inlineStr">
-        <is>
-          <t>Rikligt med bladrosetter!</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5606,7 +5600,7 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>125231342</v>
+        <v>125222288</v>
       </c>
       <c r="B47" t="n">
         <v>98269</v>
@@ -5640,7 +5634,11 @@
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
-      <c r="J47" t="inlineStr"/>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K47" t="inlineStr"/>
       <c r="L47" t="inlineStr"/>
       <c r="N47" t="inlineStr"/>
@@ -5650,10 +5648,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>745267</v>
+        <v>745266</v>
       </c>
       <c r="R47" t="n">
-        <v>7107907</v>
+        <v>7107910</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5701,22 +5699,22 @@
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Patrik Nygren</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Patrik Nygren</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>125231545</v>
+        <v>125227661</v>
       </c>
       <c r="B48" t="n">
-        <v>79932</v>
+        <v>98269</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5725,30 +5723,35 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6456</v>
+        <v>220787</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
-      <c r="J48" t="inlineStr"/>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K48" t="inlineStr"/>
+      <c r="L48" t="inlineStr"/>
       <c r="N48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
@@ -5756,10 +5759,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>745310</v>
+        <v>745280</v>
       </c>
       <c r="R48" t="n">
-        <v>7107876</v>
+        <v>7107827</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5807,22 +5810,22 @@
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Patrik Nygren</t>
         </is>
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Patrik Nygren</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>125222055</v>
+        <v>125231658</v>
       </c>
       <c r="B49" t="n">
-        <v>91166</v>
+        <v>91131</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -5831,33 +5834,29 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>1202</v>
+        <v>5447</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
-      <c r="J49" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+      <c r="J49" t="inlineStr"/>
       <c r="K49" t="inlineStr"/>
       <c r="N49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
@@ -5866,10 +5865,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>745262</v>
+        <v>745405</v>
       </c>
       <c r="R49" t="n">
-        <v>7107948</v>
+        <v>7107837</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5917,22 +5916,22 @@
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
         <is>
-          <t>Patrik Nygren</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>Patrik Nygren</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>125226477</v>
+        <v>125222999</v>
       </c>
       <c r="B50" t="n">
-        <v>91166</v>
+        <v>98269</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -5941,34 +5940,35 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
       <c r="J50" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K50" t="inlineStr"/>
+      <c r="L50" t="inlineStr"/>
       <c r="N50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
@@ -5976,10 +5976,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>745445</v>
+        <v>745290</v>
       </c>
       <c r="R50" t="n">
-        <v>7107841</v>
+        <v>7107864</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>

--- a/artfynd/A 53969-2024 artfynd.xlsx
+++ b/artfynd/A 53969-2024 artfynd.xlsx
@@ -1106,10 +1106,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>125227901</v>
+        <v>125225490</v>
       </c>
       <c r="B6" t="n">
-        <v>98269</v>
+        <v>91521</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1122,31 +1122,30 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>220787</v>
+        <v>2062</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ulltickeporing</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Skeletocutis brevispora</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="J6" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1154,10 +1153,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>745280</v>
+        <v>745321</v>
       </c>
       <c r="R6" t="n">
-        <v>7107886</v>
+        <v>7107841</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1217,10 +1216,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>125225490</v>
+        <v>125227901</v>
       </c>
       <c r="B7" t="n">
-        <v>91521</v>
+        <v>98269</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1233,30 +1232,31 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>2062</v>
+        <v>220787</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Ulltickeporing</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Skeletocutis brevispora</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="J7" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
@@ -1264,10 +1264,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>745321</v>
+        <v>745280</v>
       </c>
       <c r="R7" t="n">
-        <v>7107841</v>
+        <v>7107886</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -4179,10 +4179,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>125231464</v>
+        <v>125226783</v>
       </c>
       <c r="B34" t="n">
-        <v>79932</v>
+        <v>98269</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4191,30 +4191,35 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6456</v>
+        <v>220787</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
-      <c r="J34" t="inlineStr"/>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K34" t="inlineStr"/>
+      <c r="L34" t="inlineStr"/>
       <c r="N34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
@@ -4222,10 +4227,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>745287</v>
+        <v>745294</v>
       </c>
       <c r="R34" t="n">
-        <v>7107886</v>
+        <v>7107772</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4273,19 +4278,19 @@
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Patrik Nygren</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Patrik Nygren</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>125226783</v>
+        <v>125227446</v>
       </c>
       <c r="B35" t="n">
         <v>98269</v>
@@ -4333,10 +4338,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>745294</v>
+        <v>745280</v>
       </c>
       <c r="R35" t="n">
-        <v>7107772</v>
+        <v>7107802</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4396,7 +4401,7 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>125227446</v>
+        <v>125223203</v>
       </c>
       <c r="B36" t="n">
         <v>98269</v>
@@ -4444,10 +4449,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>745280</v>
+        <v>745293</v>
       </c>
       <c r="R36" t="n">
-        <v>7107802</v>
+        <v>7107855</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4507,10 +4512,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>125223203</v>
+        <v>125231696</v>
       </c>
       <c r="B37" t="n">
-        <v>98269</v>
+        <v>98290</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4519,33 +4524,29 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>220787</v>
+        <v>221952</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
-      <c r="J37" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="J37" t="inlineStr"/>
       <c r="K37" t="inlineStr"/>
       <c r="L37" t="inlineStr"/>
       <c r="N37" t="inlineStr"/>
@@ -4555,10 +4556,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>745293</v>
+        <v>745356</v>
       </c>
       <c r="R37" t="n">
-        <v>7107855</v>
+        <v>7107793</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4606,22 +4607,22 @@
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Patrik Nygren</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Patrik Nygren</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>125231696</v>
+        <v>125231464</v>
       </c>
       <c r="B38" t="n">
-        <v>98290</v>
+        <v>79932</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4634,27 +4635,26 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>221952</v>
+        <v>6456</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
       <c r="J38" t="inlineStr"/>
       <c r="K38" t="inlineStr"/>
-      <c r="L38" t="inlineStr"/>
       <c r="N38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
@@ -4662,10 +4662,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>745356</v>
+        <v>745287</v>
       </c>
       <c r="R38" t="n">
-        <v>7107793</v>
+        <v>7107886</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>

--- a/artfynd/A 53969-2024 artfynd.xlsx
+++ b/artfynd/A 53969-2024 artfynd.xlsx
@@ -1433,10 +1433,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>125231948</v>
+        <v>125222073</v>
       </c>
       <c r="B9" t="n">
-        <v>98269</v>
+        <v>91166</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1445,31 +1445,34 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="J9" t="inlineStr"/>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr"/>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
@@ -1477,10 +1480,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>745279</v>
+        <v>745262</v>
       </c>
       <c r="R9" t="n">
-        <v>7107754</v>
+        <v>7107946</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1528,19 +1531,19 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Patrik Nygren</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Patrik Nygren</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>125231309</v>
+        <v>125231948</v>
       </c>
       <c r="B10" t="n">
         <v>98269</v>
@@ -1584,10 +1587,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>745268</v>
+        <v>745279</v>
       </c>
       <c r="R10" t="n">
-        <v>7107926</v>
+        <v>7107754</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1647,10 +1650,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>125222073</v>
+        <v>125231309</v>
       </c>
       <c r="B11" t="n">
-        <v>91166</v>
+        <v>98269</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1659,34 +1662,31 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+      <c r="J11" t="inlineStr"/>
       <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
@@ -1694,10 +1694,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>745262</v>
+        <v>745268</v>
       </c>
       <c r="R11" t="n">
-        <v>7107946</v>
+        <v>7107926</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1745,12 +1745,12 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Patrik Nygren</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Patrik Nygren</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
@@ -2418,10 +2418,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>125223425</v>
+        <v>125232283</v>
       </c>
       <c r="B18" t="n">
-        <v>98269</v>
+        <v>58001</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2430,35 +2430,31 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>220787</v>
+        <v>103015</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
-      <c r="J18" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
       <c r="K18" t="inlineStr"/>
       <c r="L18" t="inlineStr"/>
+      <c r="M18" t="inlineStr"/>
       <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
@@ -2466,13 +2462,13 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>745298</v>
+        <v>745254</v>
       </c>
       <c r="R18" t="n">
-        <v>7107856</v>
+        <v>7107972</v>
       </c>
       <c r="S18" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2510,26 +2506,25 @@
       <c r="AE18" t="b">
         <v>0</v>
       </c>
-      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
       </c>
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Patrik Nygren</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Patrik Nygren</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>125222754</v>
+        <v>125223425</v>
       </c>
       <c r="B19" t="n">
         <v>98269</v>
@@ -2577,10 +2572,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>745306</v>
+        <v>745298</v>
       </c>
       <c r="R19" t="n">
-        <v>7107877</v>
+        <v>7107856</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2640,10 +2635,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>125232283</v>
+        <v>125222754</v>
       </c>
       <c r="B20" t="n">
-        <v>58001</v>
+        <v>98269</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2652,31 +2647,35 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>103015</v>
+        <v>220787</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K20" t="inlineStr"/>
       <c r="L20" t="inlineStr"/>
-      <c r="M20" t="inlineStr"/>
       <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
@@ -2684,13 +2683,13 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>745254</v>
+        <v>745306</v>
       </c>
       <c r="R20" t="n">
-        <v>7107972</v>
+        <v>7107877</v>
       </c>
       <c r="S20" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2728,18 +2727,19 @@
       <c r="AE20" t="b">
         <v>0</v>
       </c>
+      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
       </c>
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Patrik Nygren</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Patrik Nygren</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
@@ -3962,10 +3962,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>125222083</v>
+        <v>125231983</v>
       </c>
       <c r="B32" t="n">
-        <v>91521</v>
+        <v>98269</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -3978,30 +3978,27 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>2062</v>
+        <v>220787</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Ulltickeporing</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Skeletocutis brevispora</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
-      <c r="J32" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+      <c r="J32" t="inlineStr"/>
       <c r="K32" t="inlineStr"/>
+      <c r="L32" t="inlineStr"/>
       <c r="N32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
@@ -4009,10 +4006,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>745262</v>
+        <v>745279</v>
       </c>
       <c r="R32" t="n">
-        <v>7107946</v>
+        <v>7107767</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4060,22 +4057,22 @@
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Patrik Nygren</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Patrik Nygren</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>125231983</v>
+        <v>125222083</v>
       </c>
       <c r="B33" t="n">
-        <v>98269</v>
+        <v>91521</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4088,27 +4085,30 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>220787</v>
+        <v>2062</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ulltickeporing</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Skeletocutis brevispora</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
-      <c r="J33" t="inlineStr"/>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K33" t="inlineStr"/>
-      <c r="L33" t="inlineStr"/>
       <c r="N33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
@@ -4116,10 +4116,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>745279</v>
+        <v>745262</v>
       </c>
       <c r="R33" t="n">
-        <v>7107767</v>
+        <v>7107946</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4167,22 +4167,22 @@
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Patrik Nygren</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Patrik Nygren</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>125226783</v>
+        <v>125231464</v>
       </c>
       <c r="B34" t="n">
-        <v>98269</v>
+        <v>79932</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4191,35 +4191,30 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>220787</v>
+        <v>6456</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
-      <c r="J34" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="J34" t="inlineStr"/>
       <c r="K34" t="inlineStr"/>
-      <c r="L34" t="inlineStr"/>
       <c r="N34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
@@ -4227,10 +4222,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>745294</v>
+        <v>745287</v>
       </c>
       <c r="R34" t="n">
-        <v>7107772</v>
+        <v>7107886</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4278,19 +4273,19 @@
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Patrik Nygren</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Patrik Nygren</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>125227446</v>
+        <v>125226783</v>
       </c>
       <c r="B35" t="n">
         <v>98269</v>
@@ -4338,10 +4333,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>745280</v>
+        <v>745294</v>
       </c>
       <c r="R35" t="n">
-        <v>7107802</v>
+        <v>7107772</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4401,7 +4396,7 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>125223203</v>
+        <v>125227446</v>
       </c>
       <c r="B36" t="n">
         <v>98269</v>
@@ -4449,10 +4444,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>745293</v>
+        <v>745280</v>
       </c>
       <c r="R36" t="n">
-        <v>7107855</v>
+        <v>7107802</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4512,10 +4507,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>125231696</v>
+        <v>125223203</v>
       </c>
       <c r="B37" t="n">
-        <v>98290</v>
+        <v>98269</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4524,29 +4519,33 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>221952</v>
+        <v>220787</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
-      <c r="J37" t="inlineStr"/>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K37" t="inlineStr"/>
       <c r="L37" t="inlineStr"/>
       <c r="N37" t="inlineStr"/>
@@ -4556,10 +4555,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>745356</v>
+        <v>745293</v>
       </c>
       <c r="R37" t="n">
-        <v>7107793</v>
+        <v>7107855</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4607,22 +4606,22 @@
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Patrik Nygren</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Patrik Nygren</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>125231464</v>
+        <v>125231696</v>
       </c>
       <c r="B38" t="n">
-        <v>79932</v>
+        <v>98290</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4635,26 +4634,27 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6456</v>
+        <v>221952</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
       <c r="J38" t="inlineStr"/>
       <c r="K38" t="inlineStr"/>
+      <c r="L38" t="inlineStr"/>
       <c r="N38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
@@ -4662,10 +4662,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>745287</v>
+        <v>745356</v>
       </c>
       <c r="R38" t="n">
-        <v>7107886</v>
+        <v>7107793</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>

--- a/artfynd/A 53969-2024 artfynd.xlsx
+++ b/artfynd/A 53969-2024 artfynd.xlsx
@@ -675,42 +675,42 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>125231779</v>
+        <v>125227847</v>
       </c>
       <c r="B2" t="n">
-        <v>80057</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57648</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6462</v>
+        <v>100049</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -718,10 +718,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>745323</v>
+        <v>745285</v>
       </c>
       <c r="R2" t="n">
-        <v>7107772</v>
+        <v>7107862</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -756,40 +756,39 @@
           <t>2025-05-18</t>
         </is>
       </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>hack i död gran</t>
+        </is>
+      </c>
       <c r="AD2" t="b">
         <v>0</v>
       </c>
       <c r="AE2" t="b">
         <v>0</v>
       </c>
-      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Patrik Nygren</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Patrik Nygren</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>125223590</v>
+        <v>125227327</v>
       </c>
       <c r="B3" t="n">
-        <v>98269</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>98324</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -829,10 +828,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>745299</v>
+        <v>745280</v>
       </c>
       <c r="R3" t="n">
-        <v>7107851</v>
+        <v>7107795</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -892,43 +891,41 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>125231249</v>
+        <v>125226206</v>
       </c>
       <c r="B4" t="n">
-        <v>98269</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91220</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -936,10 +933,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>745260</v>
+        <v>745327</v>
       </c>
       <c r="R4" t="n">
-        <v>7107948</v>
+        <v>7107827</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -987,55 +984,53 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Patrik Nygren</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Patrik Nygren</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>125231838</v>
+        <v>125222055</v>
       </c>
       <c r="B5" t="n">
-        <v>98269</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91220</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1043,10 +1038,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>745310</v>
+        <v>745262</v>
       </c>
       <c r="R5" t="n">
-        <v>7107765</v>
+        <v>7107948</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1094,49 +1089,44 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Patrik Nygren</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Patrik Nygren</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>125225490</v>
+        <v>125226477</v>
       </c>
       <c r="B6" t="n">
-        <v>91521</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91220</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>2062</v>
+        <v>1202</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Ulltickeporing</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Skeletocutis brevispora</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1153,7 +1143,7 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>745321</v>
+        <v>745445</v>
       </c>
       <c r="R6" t="n">
         <v>7107841</v>
@@ -1216,47 +1206,37 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>125227901</v>
+        <v>125231105</v>
       </c>
       <c r="B7" t="n">
-        <v>98269</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80099</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>220787</v>
+        <v>6462</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
@@ -1264,10 +1244,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>745280</v>
+        <v>745259</v>
       </c>
       <c r="R7" t="n">
-        <v>7107886</v>
+        <v>7107964</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1315,55 +1295,50 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Patrik Nygren</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Patrik Nygren</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>125232181</v>
+        <v>125231249</v>
       </c>
       <c r="B8" t="n">
-        <v>57632</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>98324</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
       <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr"/>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
@@ -1371,10 +1346,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>745227</v>
+        <v>745260</v>
       </c>
       <c r="R8" t="n">
-        <v>7107774</v>
+        <v>7107948</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1415,6 +1390,7 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
+      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
@@ -1433,15 +1409,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>125222073</v>
+        <v>125232024</v>
       </c>
       <c r="B9" t="n">
-        <v>91166</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91220</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1467,11 +1438,7 @@
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+      <c r="J9" t="inlineStr"/>
       <c r="K9" t="inlineStr"/>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
@@ -1480,10 +1447,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>745262</v>
+        <v>745288</v>
       </c>
       <c r="R9" t="n">
-        <v>7107946</v>
+        <v>7107786</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1531,55 +1498,49 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Patrik Nygren</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Patrik Nygren</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>125231948</v>
+        <v>125231464</v>
       </c>
       <c r="B10" t="n">
-        <v>98269</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79974</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>220787</v>
+        <v>6456</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="J10" t="inlineStr"/>
       <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr"/>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
@@ -1587,10 +1548,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>745279</v>
+        <v>745287</v>
       </c>
       <c r="R10" t="n">
-        <v>7107754</v>
+        <v>7107886</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1650,15 +1611,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>125231309</v>
+        <v>125222361</v>
       </c>
       <c r="B11" t="n">
-        <v>98269</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>98324</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1684,7 +1640,11 @@
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="J11" t="inlineStr"/>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K11" t="inlineStr"/>
       <c r="L11" t="inlineStr"/>
       <c r="N11" t="inlineStr"/>
@@ -1694,10 +1654,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>745268</v>
+        <v>745280</v>
       </c>
       <c r="R11" t="n">
-        <v>7107926</v>
+        <v>7107886</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1745,27 +1705,22 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Patrik Nygren</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Patrik Nygren</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>125231888</v>
+        <v>125230982</v>
       </c>
       <c r="B12" t="n">
-        <v>98269</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>98324</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1801,10 +1756,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>745297</v>
+        <v>745259</v>
       </c>
       <c r="R12" t="n">
-        <v>7107757</v>
+        <v>7107964</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1864,15 +1819,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>125227728</v>
+        <v>125231983</v>
       </c>
       <c r="B13" t="n">
-        <v>98269</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>98324</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1898,11 +1848,7 @@
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="J13" t="inlineStr"/>
       <c r="K13" t="inlineStr"/>
       <c r="L13" t="inlineStr"/>
       <c r="N13" t="inlineStr"/>
@@ -1915,7 +1861,7 @@
         <v>745279</v>
       </c>
       <c r="R13" t="n">
-        <v>7107831</v>
+        <v>7107767</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1963,27 +1909,22 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Patrik Nygren</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Patrik Nygren</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>125232212</v>
+        <v>125225982</v>
       </c>
       <c r="B14" t="n">
-        <v>98269</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>98324</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2009,7 +1950,11 @@
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
-      <c r="J14" t="inlineStr"/>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K14" t="inlineStr"/>
       <c r="L14" t="inlineStr"/>
       <c r="N14" t="inlineStr"/>
@@ -2019,10 +1964,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>745252</v>
+        <v>745327</v>
       </c>
       <c r="R14" t="n">
-        <v>7107940</v>
+        <v>7107834</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2070,27 +2015,22 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Patrik Nygren</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Patrik Nygren</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>125222017</v>
+        <v>125223807</v>
       </c>
       <c r="B15" t="n">
-        <v>98269</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>98324</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2130,10 +2070,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>745243</v>
+        <v>745315</v>
       </c>
       <c r="R15" t="n">
-        <v>7107977</v>
+        <v>7107851</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2166,6 +2106,11 @@
       <c r="AA15" t="inlineStr">
         <is>
           <t>2025-05-18</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>Rikligt med bladrosetter!</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2193,46 +2138,42 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>125222055</v>
+        <v>125222999</v>
       </c>
       <c r="B16" t="n">
-        <v>91166</v>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>98324</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
       <c r="J16" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
       <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
@@ -2240,10 +2181,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>745262</v>
+        <v>745290</v>
       </c>
       <c r="R16" t="n">
-        <v>7107948</v>
+        <v>7107864</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2303,32 +2244,27 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>125228007</v>
+        <v>125232283</v>
       </c>
       <c r="B17" t="n">
-        <v>57632</v>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58019</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100049</v>
+        <v>103015</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -2339,11 +2275,7 @@
       <c r="I17" t="inlineStr"/>
       <c r="K17" t="inlineStr"/>
       <c r="L17" t="inlineStr"/>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
+      <c r="M17" t="inlineStr"/>
       <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
@@ -2351,13 +2283,13 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>745249</v>
+        <v>745254</v>
       </c>
       <c r="R17" t="n">
-        <v>7107940</v>
+        <v>7107972</v>
       </c>
       <c r="S17" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2387,11 +2319,6 @@
       <c r="AA17" t="inlineStr">
         <is>
           <t>2025-05-18</t>
-        </is>
-      </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>hackat hål i gran</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2406,44 +2333,39 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Patrik Nygren</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Patrik Nygren</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>125232283</v>
+        <v>125232181</v>
       </c>
       <c r="B18" t="n">
-        <v>58001</v>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57648</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>103015</v>
+        <v>100049</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -2462,13 +2384,13 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>745254</v>
+        <v>745227</v>
       </c>
       <c r="R18" t="n">
-        <v>7107972</v>
+        <v>7107774</v>
       </c>
       <c r="S18" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2524,15 +2446,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>125223425</v>
+        <v>125231888</v>
       </c>
       <c r="B19" t="n">
-        <v>98269</v>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>98324</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2558,11 +2475,7 @@
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
-      <c r="J19" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="J19" t="inlineStr"/>
       <c r="K19" t="inlineStr"/>
       <c r="L19" t="inlineStr"/>
       <c r="N19" t="inlineStr"/>
@@ -2572,10 +2485,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>745298</v>
+        <v>745297</v>
       </c>
       <c r="R19" t="n">
-        <v>7107856</v>
+        <v>7107757</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2623,59 +2536,53 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Patrik Nygren</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Patrik Nygren</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>125222754</v>
+        <v>125222246</v>
       </c>
       <c r="B20" t="n">
-        <v>98269</v>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91220</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
       <c r="J20" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K20" t="inlineStr"/>
-      <c r="L20" t="inlineStr"/>
       <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
@@ -2683,10 +2590,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>745306</v>
+        <v>745262</v>
       </c>
       <c r="R20" t="n">
-        <v>7107877</v>
+        <v>7107944</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2746,42 +2653,42 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>125231545</v>
+        <v>125222545</v>
       </c>
       <c r="B21" t="n">
-        <v>79932</v>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>98324</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6456</v>
+        <v>220787</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
-      <c r="J21" t="inlineStr"/>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K21" t="inlineStr"/>
+      <c r="L21" t="inlineStr"/>
       <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
@@ -2789,10 +2696,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>745310</v>
+        <v>745294</v>
       </c>
       <c r="R21" t="n">
-        <v>7107876</v>
+        <v>7107877</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2840,59 +2747,54 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Patrik Nygren</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Patrik Nygren</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>125227847</v>
+        <v>125226783</v>
       </c>
       <c r="B22" t="n">
-        <v>57632</v>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>98324</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K22" t="inlineStr"/>
       <c r="L22" t="inlineStr"/>
-      <c r="M22" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
@@ -2900,10 +2802,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>745285</v>
+        <v>745294</v>
       </c>
       <c r="R22" t="n">
-        <v>7107862</v>
+        <v>7107772</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2938,17 +2840,13 @@
           <t>2025-05-18</t>
         </is>
       </c>
-      <c r="AC22" t="inlineStr">
-        <is>
-          <t>hack i död gran</t>
-        </is>
-      </c>
       <c r="AD22" t="b">
         <v>0</v>
       </c>
       <c r="AE22" t="b">
         <v>0</v>
       </c>
+      <c r="AF22" t="inlineStr"/>
       <c r="AG22" t="b">
         <v>0</v>
       </c>
@@ -2967,15 +2865,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>125223807</v>
+        <v>125223590</v>
       </c>
       <c r="B23" t="n">
-        <v>98269</v>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>98324</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3015,7 +2908,7 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>745315</v>
+        <v>745299</v>
       </c>
       <c r="R23" t="n">
         <v>7107851</v>
@@ -3051,11 +2944,6 @@
       <c r="AA23" t="inlineStr">
         <is>
           <t>2025-05-18</t>
-        </is>
-      </c>
-      <c r="AC23" t="inlineStr">
-        <is>
-          <t>Rikligt med bladrosetter!</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3083,15 +2971,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>125230982</v>
+        <v>125228040</v>
       </c>
       <c r="B24" t="n">
-        <v>98269</v>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>98324</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3117,7 +3000,11 @@
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
-      <c r="J24" t="inlineStr"/>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K24" t="inlineStr"/>
       <c r="L24" t="inlineStr"/>
       <c r="N24" t="inlineStr"/>
@@ -3127,10 +3014,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>745259</v>
+        <v>745249</v>
       </c>
       <c r="R24" t="n">
-        <v>7107964</v>
+        <v>7107940</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3165,6 +3052,11 @@
           <t>2025-05-18</t>
         </is>
       </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>rikligt med bladrosetter!</t>
+        </is>
+      </c>
       <c r="AD24" t="b">
         <v>0</v>
       </c>
@@ -3178,27 +3070,22 @@
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Patrik Nygren</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Patrik Nygren</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>125227327</v>
+        <v>125223203</v>
       </c>
       <c r="B25" t="n">
-        <v>98269</v>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>98324</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3238,10 +3125,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>745280</v>
+        <v>745293</v>
       </c>
       <c r="R25" t="n">
-        <v>7107795</v>
+        <v>7107855</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3301,15 +3188,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>125228040</v>
+        <v>125223425</v>
       </c>
       <c r="B26" t="n">
-        <v>98269</v>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>98324</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3349,10 +3231,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>745249</v>
+        <v>745298</v>
       </c>
       <c r="R26" t="n">
-        <v>7107940</v>
+        <v>7107856</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3385,11 +3267,6 @@
       <c r="AA26" t="inlineStr">
         <is>
           <t>2025-05-18</t>
-        </is>
-      </c>
-      <c r="AC26" t="inlineStr">
-        <is>
-          <t>rikligt med bladrosetter!</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3417,42 +3294,38 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>125232195</v>
+        <v>125231838</v>
       </c>
       <c r="B27" t="n">
-        <v>80028</v>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>98324</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
       <c r="J27" t="inlineStr"/>
       <c r="K27" t="inlineStr"/>
+      <c r="L27" t="inlineStr"/>
       <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
@@ -3460,10 +3333,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>745215</v>
+        <v>745310</v>
       </c>
       <c r="R27" t="n">
-        <v>7107730</v>
+        <v>7107765</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3523,46 +3396,38 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>125226477</v>
+        <v>125231696</v>
       </c>
       <c r="B28" t="n">
-        <v>91166</v>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>98345</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>1202</v>
+        <v>221952</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
-      <c r="J28" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+      <c r="J28" t="inlineStr"/>
       <c r="K28" t="inlineStr"/>
+      <c r="L28" t="inlineStr"/>
       <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
@@ -3570,10 +3435,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>745445</v>
+        <v>745356</v>
       </c>
       <c r="R28" t="n">
-        <v>7107841</v>
+        <v>7107793</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3621,54 +3486,54 @@
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Patrik Nygren</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Patrik Nygren</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>125231105</v>
+        <v>125222288</v>
       </c>
       <c r="B29" t="n">
-        <v>80057</v>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>98324</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6462</v>
+        <v>220787</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
-      <c r="J29" t="inlineStr"/>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K29" t="inlineStr"/>
+      <c r="L29" t="inlineStr"/>
       <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
@@ -3676,10 +3541,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>745259</v>
+        <v>745266</v>
       </c>
       <c r="R29" t="n">
-        <v>7107964</v>
+        <v>7107910</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3727,27 +3592,22 @@
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Patrik Nygren</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Patrik Nygren</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>125222404</v>
+        <v>125222083</v>
       </c>
       <c r="B30" t="n">
-        <v>98269</v>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91575</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3755,31 +3615,30 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>220787</v>
+        <v>2062</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ulltickeporing</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Skeletocutis brevispora</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
       <c r="J30" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K30" t="inlineStr"/>
-      <c r="L30" t="inlineStr"/>
       <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
@@ -3787,10 +3646,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>745290</v>
+        <v>745262</v>
       </c>
       <c r="R30" t="n">
-        <v>7107886</v>
+        <v>7107946</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3823,11 +3682,6 @@
       <c r="AA30" t="inlineStr">
         <is>
           <t>2025-05-18</t>
-        </is>
-      </c>
-      <c r="AC30" t="inlineStr">
-        <is>
-          <t>några kvadratmeter med bladrosetter</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3855,43 +3709,37 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>125231342</v>
+        <v>125232195</v>
       </c>
       <c r="B31" t="n">
-        <v>98269</v>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80070</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
       <c r="J31" t="inlineStr"/>
       <c r="K31" t="inlineStr"/>
-      <c r="L31" t="inlineStr"/>
       <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
@@ -3899,10 +3747,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>745267</v>
+        <v>745215</v>
       </c>
       <c r="R31" t="n">
-        <v>7107907</v>
+        <v>7107730</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3962,15 +3810,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>125231983</v>
+        <v>125222404</v>
       </c>
       <c r="B32" t="n">
-        <v>98269</v>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>98324</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3996,7 +3839,11 @@
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
-      <c r="J32" t="inlineStr"/>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K32" t="inlineStr"/>
       <c r="L32" t="inlineStr"/>
       <c r="N32" t="inlineStr"/>
@@ -4006,10 +3853,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>745279</v>
+        <v>745290</v>
       </c>
       <c r="R32" t="n">
-        <v>7107767</v>
+        <v>7107886</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4044,6 +3891,11 @@
           <t>2025-05-18</t>
         </is>
       </c>
+      <c r="AC32" t="inlineStr">
+        <is>
+          <t>några kvadratmeter med bladrosetter</t>
+        </is>
+      </c>
       <c r="AD32" t="b">
         <v>0</v>
       </c>
@@ -4057,27 +3909,22 @@
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Patrik Nygren</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Patrik Nygren</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>125222083</v>
+        <v>125225490</v>
       </c>
       <c r="B33" t="n">
-        <v>91521</v>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91575</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4116,10 +3963,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>745262</v>
+        <v>745321</v>
       </c>
       <c r="R33" t="n">
-        <v>7107946</v>
+        <v>7107841</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4179,41 +4026,40 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>125231464</v>
+        <v>125222073</v>
       </c>
       <c r="B34" t="n">
-        <v>79932</v>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91220</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6456</v>
+        <v>1202</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
-      <c r="J34" t="inlineStr"/>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K34" t="inlineStr"/>
       <c r="N34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
@@ -4222,10 +4068,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>745287</v>
+        <v>745262</v>
       </c>
       <c r="R34" t="n">
-        <v>7107886</v>
+        <v>7107946</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4273,59 +4119,49 @@
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Patrik Nygren</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Patrik Nygren</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>125226783</v>
+        <v>125231545</v>
       </c>
       <c r="B35" t="n">
-        <v>98269</v>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79974</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>220787</v>
+        <v>6456</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
-      <c r="J35" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="J35" t="inlineStr"/>
       <c r="K35" t="inlineStr"/>
-      <c r="L35" t="inlineStr"/>
       <c r="N35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
@@ -4333,10 +4169,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>745294</v>
+        <v>745310</v>
       </c>
       <c r="R35" t="n">
-        <v>7107772</v>
+        <v>7107876</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4384,59 +4220,49 @@
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Patrik Nygren</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Patrik Nygren</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>125227446</v>
+        <v>125231779</v>
       </c>
       <c r="B36" t="n">
-        <v>98269</v>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80099</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>220787</v>
+        <v>6462</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
-      <c r="J36" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="J36" t="inlineStr"/>
       <c r="K36" t="inlineStr"/>
-      <c r="L36" t="inlineStr"/>
       <c r="N36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
@@ -4444,10 +4270,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>745280</v>
+        <v>745323</v>
       </c>
       <c r="R36" t="n">
-        <v>7107802</v>
+        <v>7107772</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4495,27 +4321,22 @@
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Patrik Nygren</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Patrik Nygren</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>125223203</v>
+        <v>125227728</v>
       </c>
       <c r="B37" t="n">
-        <v>98269</v>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>98324</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4555,10 +4376,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>745293</v>
+        <v>745279</v>
       </c>
       <c r="R37" t="n">
-        <v>7107855</v>
+        <v>7107831</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4618,41 +4439,40 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>125231696</v>
+        <v>125227446</v>
       </c>
       <c r="B38" t="n">
-        <v>98290</v>
-      </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>98324</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>221952</v>
+        <v>220787</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
-      <c r="J38" t="inlineStr"/>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K38" t="inlineStr"/>
       <c r="L38" t="inlineStr"/>
       <c r="N38" t="inlineStr"/>
@@ -4662,10 +4482,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>745356</v>
+        <v>745280</v>
       </c>
       <c r="R38" t="n">
-        <v>7107793</v>
+        <v>7107802</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4713,27 +4533,22 @@
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Patrik Nygren</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Patrik Nygren</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>125222545</v>
+        <v>125227797</v>
       </c>
       <c r="B39" t="n">
-        <v>98269</v>
-      </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>98324</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4773,10 +4588,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>745294</v>
+        <v>745277</v>
       </c>
       <c r="R39" t="n">
-        <v>7107877</v>
+        <v>7107838</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4836,15 +4651,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>125227797</v>
+        <v>125222017</v>
       </c>
       <c r="B40" t="n">
-        <v>98269</v>
-      </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>98324</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4884,10 +4694,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>745277</v>
+        <v>745243</v>
       </c>
       <c r="R40" t="n">
-        <v>7107838</v>
+        <v>7107977</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4947,42 +4757,38 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>125231618</v>
+        <v>125231309</v>
       </c>
       <c r="B41" t="n">
-        <v>79932</v>
-      </c>
-      <c r="C41" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>98324</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6456</v>
+        <v>220787</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
       <c r="J41" t="inlineStr"/>
       <c r="K41" t="inlineStr"/>
+      <c r="L41" t="inlineStr"/>
       <c r="N41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
@@ -4990,10 +4796,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>745381</v>
+        <v>745268</v>
       </c>
       <c r="R41" t="n">
-        <v>7107841</v>
+        <v>7107926</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5053,46 +4859,42 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>125226206</v>
+        <v>125227661</v>
       </c>
       <c r="B42" t="n">
-        <v>91166</v>
-      </c>
-      <c r="C42" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>98324</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
       <c r="J42" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K42" t="inlineStr"/>
+      <c r="L42" t="inlineStr"/>
       <c r="N42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
@@ -5100,7 +4902,7 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>745327</v>
+        <v>745280</v>
       </c>
       <c r="R42" t="n">
         <v>7107827</v>
@@ -5163,46 +4965,38 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>125225686</v>
+        <v>125231948</v>
       </c>
       <c r="B43" t="n">
-        <v>91166</v>
-      </c>
-      <c r="C43" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>98324</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
-      <c r="J43" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+      <c r="J43" t="inlineStr"/>
       <c r="K43" t="inlineStr"/>
+      <c r="L43" t="inlineStr"/>
       <c r="N43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
@@ -5210,10 +5004,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>745321</v>
+        <v>745279</v>
       </c>
       <c r="R43" t="n">
-        <v>7107841</v>
+        <v>7107754</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5261,54 +5055,50 @@
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Patrik Nygren</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Patrik Nygren</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>125232024</v>
+        <v>125232212</v>
       </c>
       <c r="B44" t="n">
-        <v>91166</v>
-      </c>
-      <c r="C44" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>98324</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
       <c r="J44" t="inlineStr"/>
       <c r="K44" t="inlineStr"/>
+      <c r="L44" t="inlineStr"/>
       <c r="N44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
@@ -5316,10 +5106,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>745288</v>
+        <v>745252</v>
       </c>
       <c r="R44" t="n">
-        <v>7107786</v>
+        <v>7107940</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5379,46 +5169,38 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>125222246</v>
+        <v>125231342</v>
       </c>
       <c r="B45" t="n">
-        <v>91166</v>
-      </c>
-      <c r="C45" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>98324</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
-      <c r="J45" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+      <c r="J45" t="inlineStr"/>
       <c r="K45" t="inlineStr"/>
+      <c r="L45" t="inlineStr"/>
       <c r="N45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
@@ -5426,10 +5208,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>745262</v>
+        <v>745267</v>
       </c>
       <c r="R45" t="n">
-        <v>7107944</v>
+        <v>7107907</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5477,59 +5259,53 @@
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>Patrik Nygren</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Patrik Nygren</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>125225982</v>
+        <v>125225686</v>
       </c>
       <c r="B46" t="n">
-        <v>98269</v>
-      </c>
-      <c r="C46" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91220</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
       <c r="J46" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K46" t="inlineStr"/>
-      <c r="L46" t="inlineStr"/>
       <c r="N46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
@@ -5537,10 +5313,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>745327</v>
+        <v>745321</v>
       </c>
       <c r="R46" t="n">
-        <v>7107834</v>
+        <v>7107841</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5600,47 +5376,37 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>125222288</v>
+        <v>125231618</v>
       </c>
       <c r="B47" t="n">
-        <v>98269</v>
-      </c>
-      <c r="C47" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79974</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>220787</v>
+        <v>6456</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
-      <c r="J47" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="J47" t="inlineStr"/>
       <c r="K47" t="inlineStr"/>
-      <c r="L47" t="inlineStr"/>
       <c r="N47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
@@ -5648,10 +5414,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>745266</v>
+        <v>745381</v>
       </c>
       <c r="R47" t="n">
-        <v>7107910</v>
+        <v>7107841</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5699,59 +5465,49 @@
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>Patrik Nygren</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Patrik Nygren</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>125227661</v>
+        <v>125231658</v>
       </c>
       <c r="B48" t="n">
-        <v>98269</v>
-      </c>
-      <c r="C48" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91185</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>220787</v>
+        <v>5447</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
-      <c r="J48" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="J48" t="inlineStr"/>
       <c r="K48" t="inlineStr"/>
-      <c r="L48" t="inlineStr"/>
       <c r="N48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
@@ -5759,10 +5515,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>745280</v>
+        <v>745405</v>
       </c>
       <c r="R48" t="n">
-        <v>7107827</v>
+        <v>7107837</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5810,54 +5566,54 @@
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>Patrik Nygren</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>Patrik Nygren</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>125231658</v>
+        <v>125228007</v>
       </c>
       <c r="B49" t="n">
-        <v>91131</v>
-      </c>
-      <c r="C49" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57648</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>5447</v>
+        <v>100049</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
-      <c r="J49" t="inlineStr"/>
       <c r="K49" t="inlineStr"/>
+      <c r="L49" t="inlineStr"/>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
@@ -5865,10 +5621,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>745405</v>
+        <v>745249</v>
       </c>
       <c r="R49" t="n">
-        <v>7107837</v>
+        <v>7107940</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5903,40 +5659,39 @@
           <t>2025-05-18</t>
         </is>
       </c>
+      <c r="AC49" t="inlineStr">
+        <is>
+          <t>hackat hål i gran</t>
+        </is>
+      </c>
       <c r="AD49" t="b">
         <v>0</v>
       </c>
       <c r="AE49" t="b">
         <v>0</v>
       </c>
-      <c r="AF49" t="inlineStr"/>
       <c r="AG49" t="b">
         <v>0</v>
       </c>
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Patrik Nygren</t>
         </is>
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Patrik Nygren</t>
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>125222999</v>
+        <v>125222754</v>
       </c>
       <c r="B50" t="n">
-        <v>98269</v>
-      </c>
-      <c r="C50" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>98324</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5976,10 +5731,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>745290</v>
+        <v>745306</v>
       </c>
       <c r="R50" t="n">
-        <v>7107864</v>
+        <v>7107877</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>

--- a/artfynd/A 53969-2024 artfynd.xlsx
+++ b/artfynd/A 53969-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>125227847</v>
+        <v>125226206</v>
       </c>
       <c r="B2" t="n">
-        <v>57648</v>
+        <v>91220</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,31 +686,30 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100049</v>
+        <v>1202</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -718,10 +717,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>745285</v>
+        <v>745327</v>
       </c>
       <c r="R2" t="n">
-        <v>7107862</v>
+        <v>7107827</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -756,17 +755,13 @@
           <t>2025-05-18</t>
         </is>
       </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>hack i död gran</t>
-        </is>
-      </c>
       <c r="AD2" t="b">
         <v>0</v>
       </c>
       <c r="AE2" t="b">
         <v>0</v>
       </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
@@ -785,42 +780,42 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>125227327</v>
+        <v>125227847</v>
       </c>
       <c r="B3" t="n">
-        <v>98324</v>
+        <v>57648</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -828,10 +823,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>745280</v>
+        <v>745285</v>
       </c>
       <c r="R3" t="n">
-        <v>7107795</v>
+        <v>7107862</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -866,13 +861,17 @@
           <t>2025-05-18</t>
         </is>
       </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>hack i död gran</t>
+        </is>
+      </c>
       <c r="AD3" t="b">
         <v>0</v>
       </c>
       <c r="AE3" t="b">
         <v>0</v>
       </c>
-      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -891,41 +890,42 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>125226206</v>
+        <v>125227327</v>
       </c>
       <c r="B4" t="n">
-        <v>91220</v>
+        <v>98324</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="J4" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -933,10 +933,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>745327</v>
+        <v>745280</v>
       </c>
       <c r="R4" t="n">
-        <v>7107827</v>
+        <v>7107795</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1307,38 +1307,37 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>125231249</v>
+        <v>125232024</v>
       </c>
       <c r="B8" t="n">
-        <v>98324</v>
+        <v>91220</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
@@ -1346,10 +1345,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>745260</v>
+        <v>745288</v>
       </c>
       <c r="R8" t="n">
-        <v>7107948</v>
+        <v>7107786</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1409,32 +1408,32 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>125232024</v>
+        <v>125231464</v>
       </c>
       <c r="B9" t="n">
-        <v>91220</v>
+        <v>79974</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1202</v>
+        <v>6456</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1447,10 +1446,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>745288</v>
+        <v>745287</v>
       </c>
       <c r="R9" t="n">
-        <v>7107786</v>
+        <v>7107886</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1510,37 +1509,38 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>125231464</v>
+        <v>125231249</v>
       </c>
       <c r="B10" t="n">
-        <v>79974</v>
+        <v>98324</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6456</v>
+        <v>220787</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="J10" t="inlineStr"/>
       <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
@@ -1548,10 +1548,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>745287</v>
+        <v>745260</v>
       </c>
       <c r="R10" t="n">
-        <v>7107886</v>
+        <v>7107948</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>

--- a/artfynd/A 53969-2024 artfynd.xlsx
+++ b/artfynd/A 53969-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>125226206</v>
+        <v>125227847</v>
       </c>
       <c r="B2" t="n">
-        <v>91220</v>
+        <v>57648</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,30 +686,31 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1202</v>
+        <v>100049</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
       <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -717,10 +718,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>745327</v>
+        <v>745285</v>
       </c>
       <c r="R2" t="n">
-        <v>7107827</v>
+        <v>7107862</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -755,13 +756,17 @@
           <t>2025-05-18</t>
         </is>
       </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>hack i död gran</t>
+        </is>
+      </c>
       <c r="AD2" t="b">
         <v>0</v>
       </c>
       <c r="AE2" t="b">
         <v>0</v>
       </c>
-      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
@@ -780,42 +785,42 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>125227847</v>
+        <v>125227327</v>
       </c>
       <c r="B3" t="n">
-        <v>57648</v>
+        <v>98331</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -823,10 +828,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>745285</v>
+        <v>745280</v>
       </c>
       <c r="R3" t="n">
-        <v>7107862</v>
+        <v>7107795</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -861,17 +866,13 @@
           <t>2025-05-18</t>
         </is>
       </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>hack i död gran</t>
-        </is>
-      </c>
       <c r="AD3" t="b">
         <v>0</v>
       </c>
       <c r="AE3" t="b">
         <v>0</v>
       </c>
+      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -890,42 +891,41 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>125227327</v>
+        <v>125226206</v>
       </c>
       <c r="B4" t="n">
-        <v>98324</v>
+        <v>91227</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="J4" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -933,10 +933,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>745280</v>
+        <v>745327</v>
       </c>
       <c r="R4" t="n">
-        <v>7107795</v>
+        <v>7107827</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -999,7 +999,7 @@
         <v>125222055</v>
       </c>
       <c r="B5" t="n">
-        <v>91220</v>
+        <v>91227</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1104,7 +1104,7 @@
         <v>125226477</v>
       </c>
       <c r="B6" t="n">
-        <v>91220</v>
+        <v>91227</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1310,7 +1310,7 @@
         <v>125232024</v>
       </c>
       <c r="B8" t="n">
-        <v>91220</v>
+        <v>91227</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1512,7 +1512,7 @@
         <v>125231249</v>
       </c>
       <c r="B10" t="n">
-        <v>98324</v>
+        <v>98331</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1614,7 +1614,7 @@
         <v>125222361</v>
       </c>
       <c r="B11" t="n">
-        <v>98324</v>
+        <v>98331</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1720,7 +1720,7 @@
         <v>125230982</v>
       </c>
       <c r="B12" t="n">
-        <v>98324</v>
+        <v>98331</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1822,7 +1822,7 @@
         <v>125231983</v>
       </c>
       <c r="B13" t="n">
-        <v>98324</v>
+        <v>98331</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1924,7 +1924,7 @@
         <v>125225982</v>
       </c>
       <c r="B14" t="n">
-        <v>98324</v>
+        <v>98331</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2030,7 +2030,7 @@
         <v>125223807</v>
       </c>
       <c r="B15" t="n">
-        <v>98324</v>
+        <v>98331</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2141,7 +2141,7 @@
         <v>125222999</v>
       </c>
       <c r="B16" t="n">
-        <v>98324</v>
+        <v>98331</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2449,7 +2449,7 @@
         <v>125231888</v>
       </c>
       <c r="B19" t="n">
-        <v>98324</v>
+        <v>98331</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2548,41 +2548,42 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>125222246</v>
+        <v>125222545</v>
       </c>
       <c r="B20" t="n">
-        <v>91220</v>
+        <v>98331</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
       <c r="J20" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K20" t="inlineStr"/>
+      <c r="L20" t="inlineStr"/>
       <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
@@ -2590,10 +2591,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>745262</v>
+        <v>745294</v>
       </c>
       <c r="R20" t="n">
-        <v>7107944</v>
+        <v>7107877</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2653,42 +2654,41 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>125222545</v>
+        <v>125222246</v>
       </c>
       <c r="B21" t="n">
-        <v>98324</v>
+        <v>91227</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
       <c r="J21" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K21" t="inlineStr"/>
-      <c r="L21" t="inlineStr"/>
       <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
@@ -2696,10 +2696,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>745294</v>
+        <v>745262</v>
       </c>
       <c r="R21" t="n">
-        <v>7107877</v>
+        <v>7107944</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2762,7 +2762,7 @@
         <v>125226783</v>
       </c>
       <c r="B22" t="n">
-        <v>98324</v>
+        <v>98331</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2868,7 +2868,7 @@
         <v>125223590</v>
       </c>
       <c r="B23" t="n">
-        <v>98324</v>
+        <v>98331</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2974,7 +2974,7 @@
         <v>125228040</v>
       </c>
       <c r="B24" t="n">
-        <v>98324</v>
+        <v>98331</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3085,7 +3085,7 @@
         <v>125223203</v>
       </c>
       <c r="B25" t="n">
-        <v>98324</v>
+        <v>98331</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3191,7 +3191,7 @@
         <v>125223425</v>
       </c>
       <c r="B26" t="n">
-        <v>98324</v>
+        <v>98331</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3297,7 +3297,7 @@
         <v>125231838</v>
       </c>
       <c r="B27" t="n">
-        <v>98324</v>
+        <v>98331</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3399,7 +3399,7 @@
         <v>125231696</v>
       </c>
       <c r="B28" t="n">
-        <v>98345</v>
+        <v>98352</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3501,7 +3501,7 @@
         <v>125222288</v>
       </c>
       <c r="B29" t="n">
-        <v>98324</v>
+        <v>98331</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3607,7 +3607,7 @@
         <v>125222083</v>
       </c>
       <c r="B30" t="n">
-        <v>91575</v>
+        <v>91582</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3813,7 +3813,7 @@
         <v>125222404</v>
       </c>
       <c r="B32" t="n">
-        <v>98324</v>
+        <v>98331</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3924,7 +3924,7 @@
         <v>125225490</v>
       </c>
       <c r="B33" t="n">
-        <v>91575</v>
+        <v>91582</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4029,7 +4029,7 @@
         <v>125222073</v>
       </c>
       <c r="B34" t="n">
-        <v>91220</v>
+        <v>91227</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4333,10 +4333,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>125227728</v>
+        <v>125222017</v>
       </c>
       <c r="B37" t="n">
-        <v>98324</v>
+        <v>98331</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4376,10 +4376,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>745279</v>
+        <v>745243</v>
       </c>
       <c r="R37" t="n">
-        <v>7107831</v>
+        <v>7107977</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4439,10 +4439,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>125227446</v>
+        <v>125231309</v>
       </c>
       <c r="B38" t="n">
-        <v>98324</v>
+        <v>98331</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4468,11 +4468,7 @@
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
-      <c r="J38" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="J38" t="inlineStr"/>
       <c r="K38" t="inlineStr"/>
       <c r="L38" t="inlineStr"/>
       <c r="N38" t="inlineStr"/>
@@ -4482,10 +4478,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>745280</v>
+        <v>745268</v>
       </c>
       <c r="R38" t="n">
-        <v>7107802</v>
+        <v>7107926</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4533,22 +4529,22 @@
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Patrik Nygren</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Patrik Nygren</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>125227797</v>
+        <v>125227728</v>
       </c>
       <c r="B39" t="n">
-        <v>98324</v>
+        <v>98331</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4588,10 +4584,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>745277</v>
+        <v>745279</v>
       </c>
       <c r="R39" t="n">
-        <v>7107838</v>
+        <v>7107831</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4651,10 +4647,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>125222017</v>
+        <v>125227446</v>
       </c>
       <c r="B40" t="n">
-        <v>98324</v>
+        <v>98331</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4694,10 +4690,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>745243</v>
+        <v>745280</v>
       </c>
       <c r="R40" t="n">
-        <v>7107977</v>
+        <v>7107802</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4757,10 +4753,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>125231309</v>
+        <v>125227797</v>
       </c>
       <c r="B41" t="n">
-        <v>98324</v>
+        <v>98331</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4786,7 +4782,11 @@
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
-      <c r="J41" t="inlineStr"/>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K41" t="inlineStr"/>
       <c r="L41" t="inlineStr"/>
       <c r="N41" t="inlineStr"/>
@@ -4796,10 +4796,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>745268</v>
+        <v>745277</v>
       </c>
       <c r="R41" t="n">
-        <v>7107926</v>
+        <v>7107838</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4847,12 +4847,12 @@
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Patrik Nygren</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Patrik Nygren</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
@@ -4862,7 +4862,7 @@
         <v>125227661</v>
       </c>
       <c r="B42" t="n">
-        <v>98324</v>
+        <v>98331</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4968,7 +4968,7 @@
         <v>125231948</v>
       </c>
       <c r="B43" t="n">
-        <v>98324</v>
+        <v>98331</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5070,7 +5070,7 @@
         <v>125232212</v>
       </c>
       <c r="B44" t="n">
-        <v>98324</v>
+        <v>98331</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5172,7 +5172,7 @@
         <v>125231342</v>
       </c>
       <c r="B45" t="n">
-        <v>98324</v>
+        <v>98331</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5271,40 +5271,36 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>125225686</v>
+        <v>125231618</v>
       </c>
       <c r="B46" t="n">
-        <v>91220</v>
+        <v>79974</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>1202</v>
+        <v>6456</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
-      <c r="J46" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+      <c r="J46" t="inlineStr"/>
       <c r="K46" t="inlineStr"/>
       <c r="N46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
@@ -5313,7 +5309,7 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>745321</v>
+        <v>745381</v>
       </c>
       <c r="R46" t="n">
         <v>7107841</v>
@@ -5364,22 +5360,22 @@
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>Patrik Nygren</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Patrik Nygren</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>125231618</v>
+        <v>125231658</v>
       </c>
       <c r="B47" t="n">
-        <v>79974</v>
+        <v>91192</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5387,21 +5383,21 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6456</v>
+        <v>5447</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5414,10 +5410,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>745381</v>
+        <v>745405</v>
       </c>
       <c r="R47" t="n">
-        <v>7107841</v>
+        <v>7107837</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5477,37 +5473,42 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>125231658</v>
+        <v>125222754</v>
       </c>
       <c r="B48" t="n">
-        <v>91185</v>
+        <v>98331</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>5447</v>
+        <v>220787</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
-      <c r="J48" t="inlineStr"/>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K48" t="inlineStr"/>
+      <c r="L48" t="inlineStr"/>
       <c r="N48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
@@ -5515,10 +5516,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>745405</v>
+        <v>745306</v>
       </c>
       <c r="R48" t="n">
-        <v>7107837</v>
+        <v>7107877</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5566,22 +5567,22 @@
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Patrik Nygren</t>
         </is>
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Patrik Nygren</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>125228007</v>
+        <v>125225686</v>
       </c>
       <c r="B49" t="n">
-        <v>57648</v>
+        <v>91227</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5589,31 +5590,30 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>100049</v>
+        <v>1202</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K49" t="inlineStr"/>
-      <c r="L49" t="inlineStr"/>
-      <c r="M49" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
@@ -5621,10 +5621,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>745249</v>
+        <v>745321</v>
       </c>
       <c r="R49" t="n">
-        <v>7107940</v>
+        <v>7107841</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5659,17 +5659,13 @@
           <t>2025-05-18</t>
         </is>
       </c>
-      <c r="AC49" t="inlineStr">
-        <is>
-          <t>hackat hål i gran</t>
-        </is>
-      </c>
       <c r="AD49" t="b">
         <v>0</v>
       </c>
       <c r="AE49" t="b">
         <v>0</v>
       </c>
+      <c r="AF49" t="inlineStr"/>
       <c r="AG49" t="b">
         <v>0</v>
       </c>
@@ -5688,42 +5684,42 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>125222754</v>
+        <v>125228007</v>
       </c>
       <c r="B50" t="n">
-        <v>98324</v>
+        <v>57648</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
-      <c r="J50" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
       <c r="K50" t="inlineStr"/>
       <c r="L50" t="inlineStr"/>
+      <c r="M50" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
@@ -5731,10 +5727,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>745306</v>
+        <v>745249</v>
       </c>
       <c r="R50" t="n">
-        <v>7107877</v>
+        <v>7107940</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5769,13 +5765,17 @@
           <t>2025-05-18</t>
         </is>
       </c>
+      <c r="AC50" t="inlineStr">
+        <is>
+          <t>hackat hål i gran</t>
+        </is>
+      </c>
       <c r="AD50" t="b">
         <v>0</v>
       </c>
       <c r="AE50" t="b">
         <v>0</v>
       </c>
-      <c r="AF50" t="inlineStr"/>
       <c r="AG50" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 53969-2024 artfynd.xlsx
+++ b/artfynd/A 53969-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>125227847</v>
+        <v>125226206</v>
       </c>
       <c r="B2" t="n">
-        <v>57648</v>
+        <v>91227</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,31 +686,30 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100049</v>
+        <v>1202</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -718,10 +717,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>745285</v>
+        <v>745327</v>
       </c>
       <c r="R2" t="n">
-        <v>7107862</v>
+        <v>7107827</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -756,17 +755,13 @@
           <t>2025-05-18</t>
         </is>
       </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>hack i död gran</t>
-        </is>
-      </c>
       <c r="AD2" t="b">
         <v>0</v>
       </c>
       <c r="AE2" t="b">
         <v>0</v>
       </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
@@ -785,42 +780,42 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>125227327</v>
+        <v>125227847</v>
       </c>
       <c r="B3" t="n">
-        <v>98331</v>
+        <v>57648</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -828,10 +823,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>745280</v>
+        <v>745285</v>
       </c>
       <c r="R3" t="n">
-        <v>7107795</v>
+        <v>7107862</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -866,13 +861,17 @@
           <t>2025-05-18</t>
         </is>
       </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>hack i död gran</t>
+        </is>
+      </c>
       <c r="AD3" t="b">
         <v>0</v>
       </c>
       <c r="AE3" t="b">
         <v>0</v>
       </c>
-      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -891,41 +890,42 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>125226206</v>
+        <v>125227327</v>
       </c>
       <c r="B4" t="n">
-        <v>91227</v>
+        <v>98331</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="J4" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -933,10 +933,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>745327</v>
+        <v>745280</v>
       </c>
       <c r="R4" t="n">
-        <v>7107827</v>
+        <v>7107795</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1307,37 +1307,38 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>125232024</v>
+        <v>125231249</v>
       </c>
       <c r="B8" t="n">
-        <v>91227</v>
+        <v>98331</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
@@ -1345,10 +1346,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>745288</v>
+        <v>745260</v>
       </c>
       <c r="R8" t="n">
-        <v>7107786</v>
+        <v>7107948</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1408,32 +1409,32 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>125231464</v>
+        <v>125232024</v>
       </c>
       <c r="B9" t="n">
-        <v>79974</v>
+        <v>91227</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6456</v>
+        <v>1202</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1446,10 +1447,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>745287</v>
+        <v>745288</v>
       </c>
       <c r="R9" t="n">
-        <v>7107886</v>
+        <v>7107786</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1509,38 +1510,37 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>125231249</v>
+        <v>125231464</v>
       </c>
       <c r="B10" t="n">
-        <v>98331</v>
+        <v>79974</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>220787</v>
+        <v>6456</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="J10" t="inlineStr"/>
       <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr"/>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
@@ -1548,10 +1548,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>745260</v>
+        <v>745287</v>
       </c>
       <c r="R10" t="n">
-        <v>7107948</v>
+        <v>7107886</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -2244,27 +2244,27 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>125232283</v>
+        <v>125232181</v>
       </c>
       <c r="B17" t="n">
-        <v>58019</v>
+        <v>57648</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>103015</v>
+        <v>100049</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -2283,13 +2283,13 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>745254</v>
+        <v>745227</v>
       </c>
       <c r="R17" t="n">
-        <v>7107972</v>
+        <v>7107774</v>
       </c>
       <c r="S17" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2345,27 +2345,27 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>125232181</v>
+        <v>125232283</v>
       </c>
       <c r="B18" t="n">
-        <v>57648</v>
+        <v>58019</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100049</v>
+        <v>103015</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -2384,13 +2384,13 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>745227</v>
+        <v>745254</v>
       </c>
       <c r="R18" t="n">
-        <v>7107774</v>
+        <v>7107972</v>
       </c>
       <c r="S18" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -3396,36 +3396,40 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>125231696</v>
+        <v>125222288</v>
       </c>
       <c r="B28" t="n">
-        <v>98352</v>
+        <v>98331</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>221952</v>
+        <v>220787</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
-      <c r="J28" t="inlineStr"/>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K28" t="inlineStr"/>
       <c r="L28" t="inlineStr"/>
       <c r="N28" t="inlineStr"/>
@@ -3435,10 +3439,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>745356</v>
+        <v>745266</v>
       </c>
       <c r="R28" t="n">
-        <v>7107793</v>
+        <v>7107910</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3486,52 +3490,48 @@
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Patrik Nygren</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Patrik Nygren</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>125222288</v>
+        <v>125231696</v>
       </c>
       <c r="B29" t="n">
-        <v>98331</v>
+        <v>98352</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>220787</v>
+        <v>221952</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
-      <c r="J29" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="J29" t="inlineStr"/>
       <c r="K29" t="inlineStr"/>
       <c r="L29" t="inlineStr"/>
       <c r="N29" t="inlineStr"/>
@@ -3541,10 +3541,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>745266</v>
+        <v>745356</v>
       </c>
       <c r="R29" t="n">
-        <v>7107910</v>
+        <v>7107793</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3592,12 +3592,12 @@
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Patrik Nygren</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Patrik Nygren</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
@@ -3709,37 +3709,42 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>125232195</v>
+        <v>125222404</v>
       </c>
       <c r="B31" t="n">
-        <v>80070</v>
+        <v>98331</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
-      <c r="J31" t="inlineStr"/>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K31" t="inlineStr"/>
+      <c r="L31" t="inlineStr"/>
       <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
@@ -3747,10 +3752,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>745215</v>
+        <v>745290</v>
       </c>
       <c r="R31" t="n">
-        <v>7107730</v>
+        <v>7107886</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3785,6 +3790,11 @@
           <t>2025-05-18</t>
         </is>
       </c>
+      <c r="AC31" t="inlineStr">
+        <is>
+          <t>några kvadratmeter med bladrosetter</t>
+        </is>
+      </c>
       <c r="AD31" t="b">
         <v>0</v>
       </c>
@@ -3798,54 +3808,49 @@
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Patrik Nygren</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Patrik Nygren</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>125222404</v>
+        <v>125232195</v>
       </c>
       <c r="B32" t="n">
-        <v>98331</v>
+        <v>80070</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
-      <c r="J32" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="J32" t="inlineStr"/>
       <c r="K32" t="inlineStr"/>
-      <c r="L32" t="inlineStr"/>
       <c r="N32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
@@ -3853,10 +3858,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>745290</v>
+        <v>745215</v>
       </c>
       <c r="R32" t="n">
-        <v>7107886</v>
+        <v>7107730</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3891,11 +3896,6 @@
           <t>2025-05-18</t>
         </is>
       </c>
-      <c r="AC32" t="inlineStr">
-        <is>
-          <t>några kvadratmeter med bladrosetter</t>
-        </is>
-      </c>
       <c r="AD32" t="b">
         <v>0</v>
       </c>
@@ -3909,12 +3909,12 @@
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Patrik Nygren</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Patrik Nygren</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
@@ -4333,7 +4333,7 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>125222017</v>
+        <v>125227728</v>
       </c>
       <c r="B37" t="n">
         <v>98331</v>
@@ -4376,10 +4376,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>745243</v>
+        <v>745279</v>
       </c>
       <c r="R37" t="n">
-        <v>7107977</v>
+        <v>7107831</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4439,7 +4439,7 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>125231309</v>
+        <v>125227446</v>
       </c>
       <c r="B38" t="n">
         <v>98331</v>
@@ -4468,7 +4468,11 @@
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
-      <c r="J38" t="inlineStr"/>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K38" t="inlineStr"/>
       <c r="L38" t="inlineStr"/>
       <c r="N38" t="inlineStr"/>
@@ -4478,10 +4482,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>745268</v>
+        <v>745280</v>
       </c>
       <c r="R38" t="n">
-        <v>7107926</v>
+        <v>7107802</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4529,19 +4533,19 @@
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Patrik Nygren</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Patrik Nygren</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>125227728</v>
+        <v>125222017</v>
       </c>
       <c r="B39" t="n">
         <v>98331</v>
@@ -4584,10 +4588,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>745279</v>
+        <v>745243</v>
       </c>
       <c r="R39" t="n">
-        <v>7107831</v>
+        <v>7107977</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4647,7 +4651,7 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>125227446</v>
+        <v>125231309</v>
       </c>
       <c r="B40" t="n">
         <v>98331</v>
@@ -4676,11 +4680,7 @@
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
-      <c r="J40" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="J40" t="inlineStr"/>
       <c r="K40" t="inlineStr"/>
       <c r="L40" t="inlineStr"/>
       <c r="N40" t="inlineStr"/>
@@ -4690,10 +4690,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>745280</v>
+        <v>745268</v>
       </c>
       <c r="R40" t="n">
-        <v>7107802</v>
+        <v>7107926</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4741,19 +4741,19 @@
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>Patrik Nygren</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Patrik Nygren</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>125227797</v>
+        <v>125227661</v>
       </c>
       <c r="B41" t="n">
         <v>98331</v>
@@ -4796,10 +4796,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>745277</v>
+        <v>745280</v>
       </c>
       <c r="R41" t="n">
-        <v>7107838</v>
+        <v>7107827</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4859,7 +4859,7 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>125227661</v>
+        <v>125227797</v>
       </c>
       <c r="B42" t="n">
         <v>98331</v>
@@ -4902,10 +4902,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>745280</v>
+        <v>745277</v>
       </c>
       <c r="R42" t="n">
-        <v>7107827</v>
+        <v>7107838</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4965,7 +4965,7 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>125231948</v>
+        <v>125232212</v>
       </c>
       <c r="B43" t="n">
         <v>98331</v>
@@ -5004,10 +5004,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>745279</v>
+        <v>745252</v>
       </c>
       <c r="R43" t="n">
-        <v>7107754</v>
+        <v>7107940</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5067,7 +5067,7 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>125232212</v>
+        <v>125231342</v>
       </c>
       <c r="B44" t="n">
         <v>98331</v>
@@ -5106,10 +5106,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>745252</v>
+        <v>745267</v>
       </c>
       <c r="R44" t="n">
-        <v>7107940</v>
+        <v>7107907</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5169,7 +5169,7 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>125231342</v>
+        <v>125231948</v>
       </c>
       <c r="B45" t="n">
         <v>98331</v>
@@ -5208,10 +5208,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>745267</v>
+        <v>745279</v>
       </c>
       <c r="R45" t="n">
-        <v>7107907</v>
+        <v>7107754</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5473,42 +5473,41 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>125222754</v>
+        <v>125225686</v>
       </c>
       <c r="B48" t="n">
-        <v>98331</v>
+        <v>91227</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
       <c r="J48" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K48" t="inlineStr"/>
-      <c r="L48" t="inlineStr"/>
       <c r="N48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
@@ -5516,10 +5515,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>745306</v>
+        <v>745321</v>
       </c>
       <c r="R48" t="n">
-        <v>7107877</v>
+        <v>7107841</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5579,10 +5578,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>125225686</v>
+        <v>125228007</v>
       </c>
       <c r="B49" t="n">
-        <v>91227</v>
+        <v>57648</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5590,30 +5589,31 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>1202</v>
+        <v>100049</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
-      <c r="J49" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
       <c r="K49" t="inlineStr"/>
+      <c r="L49" t="inlineStr"/>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
@@ -5621,10 +5621,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>745321</v>
+        <v>745249</v>
       </c>
       <c r="R49" t="n">
-        <v>7107841</v>
+        <v>7107940</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5659,13 +5659,17 @@
           <t>2025-05-18</t>
         </is>
       </c>
+      <c r="AC49" t="inlineStr">
+        <is>
+          <t>hackat hål i gran</t>
+        </is>
+      </c>
       <c r="AD49" t="b">
         <v>0</v>
       </c>
       <c r="AE49" t="b">
         <v>0</v>
       </c>
-      <c r="AF49" t="inlineStr"/>
       <c r="AG49" t="b">
         <v>0</v>
       </c>
@@ -5684,42 +5688,42 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>125228007</v>
+        <v>125222754</v>
       </c>
       <c r="B50" t="n">
-        <v>57648</v>
+        <v>98331</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
+      <c r="J50" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K50" t="inlineStr"/>
       <c r="L50" t="inlineStr"/>
-      <c r="M50" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
@@ -5727,10 +5731,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>745249</v>
+        <v>745306</v>
       </c>
       <c r="R50" t="n">
-        <v>7107940</v>
+        <v>7107877</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5765,17 +5769,13 @@
           <t>2025-05-18</t>
         </is>
       </c>
-      <c r="AC50" t="inlineStr">
-        <is>
-          <t>hackat hål i gran</t>
-        </is>
-      </c>
       <c r="AD50" t="b">
         <v>0</v>
       </c>
       <c r="AE50" t="b">
         <v>0</v>
       </c>
+      <c r="AF50" t="inlineStr"/>
       <c r="AG50" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 53969-2024 artfynd.xlsx
+++ b/artfynd/A 53969-2024 artfynd.xlsx
@@ -2244,27 +2244,27 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>125232181</v>
+        <v>125232283</v>
       </c>
       <c r="B17" t="n">
-        <v>57648</v>
+        <v>58019</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100049</v>
+        <v>103015</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -2283,13 +2283,13 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>745227</v>
+        <v>745254</v>
       </c>
       <c r="R17" t="n">
-        <v>7107774</v>
+        <v>7107972</v>
       </c>
       <c r="S17" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2345,27 +2345,27 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>125232283</v>
+        <v>125232181</v>
       </c>
       <c r="B18" t="n">
-        <v>58019</v>
+        <v>57648</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>103015</v>
+        <v>100049</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -2384,13 +2384,13 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>745254</v>
+        <v>745227</v>
       </c>
       <c r="R18" t="n">
-        <v>7107972</v>
+        <v>7107774</v>
       </c>
       <c r="S18" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -3709,42 +3709,37 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>125222404</v>
+        <v>125232195</v>
       </c>
       <c r="B31" t="n">
-        <v>98331</v>
+        <v>80070</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
-      <c r="J31" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="J31" t="inlineStr"/>
       <c r="K31" t="inlineStr"/>
-      <c r="L31" t="inlineStr"/>
       <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
@@ -3752,10 +3747,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>745290</v>
+        <v>745215</v>
       </c>
       <c r="R31" t="n">
-        <v>7107886</v>
+        <v>7107730</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3790,11 +3785,6 @@
           <t>2025-05-18</t>
         </is>
       </c>
-      <c r="AC31" t="inlineStr">
-        <is>
-          <t>några kvadratmeter med bladrosetter</t>
-        </is>
-      </c>
       <c r="AD31" t="b">
         <v>0</v>
       </c>
@@ -3808,49 +3798,54 @@
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Patrik Nygren</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Patrik Nygren</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>125232195</v>
+        <v>125222404</v>
       </c>
       <c r="B32" t="n">
-        <v>80070</v>
+        <v>98331</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
-      <c r="J32" t="inlineStr"/>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K32" t="inlineStr"/>
+      <c r="L32" t="inlineStr"/>
       <c r="N32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
@@ -3858,10 +3853,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>745215</v>
+        <v>745290</v>
       </c>
       <c r="R32" t="n">
-        <v>7107730</v>
+        <v>7107886</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3896,6 +3891,11 @@
           <t>2025-05-18</t>
         </is>
       </c>
+      <c r="AC32" t="inlineStr">
+        <is>
+          <t>några kvadratmeter med bladrosetter</t>
+        </is>
+      </c>
       <c r="AD32" t="b">
         <v>0</v>
       </c>
@@ -3909,12 +3909,12 @@
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Patrik Nygren</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Patrik Nygren</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
@@ -4333,7 +4333,7 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>125227728</v>
+        <v>125222017</v>
       </c>
       <c r="B37" t="n">
         <v>98331</v>
@@ -4376,10 +4376,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>745279</v>
+        <v>745243</v>
       </c>
       <c r="R37" t="n">
-        <v>7107831</v>
+        <v>7107977</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4439,7 +4439,7 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>125227446</v>
+        <v>125231309</v>
       </c>
       <c r="B38" t="n">
         <v>98331</v>
@@ -4468,11 +4468,7 @@
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
-      <c r="J38" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="J38" t="inlineStr"/>
       <c r="K38" t="inlineStr"/>
       <c r="L38" t="inlineStr"/>
       <c r="N38" t="inlineStr"/>
@@ -4482,10 +4478,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>745280</v>
+        <v>745268</v>
       </c>
       <c r="R38" t="n">
-        <v>7107802</v>
+        <v>7107926</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4533,19 +4529,19 @@
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Patrik Nygren</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Patrik Nygren</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>125222017</v>
+        <v>125227728</v>
       </c>
       <c r="B39" t="n">
         <v>98331</v>
@@ -4588,10 +4584,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>745243</v>
+        <v>745279</v>
       </c>
       <c r="R39" t="n">
-        <v>7107977</v>
+        <v>7107831</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4651,7 +4647,7 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>125231309</v>
+        <v>125227446</v>
       </c>
       <c r="B40" t="n">
         <v>98331</v>
@@ -4680,7 +4676,11 @@
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
-      <c r="J40" t="inlineStr"/>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K40" t="inlineStr"/>
       <c r="L40" t="inlineStr"/>
       <c r="N40" t="inlineStr"/>
@@ -4690,10 +4690,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>745268</v>
+        <v>745280</v>
       </c>
       <c r="R40" t="n">
-        <v>7107926</v>
+        <v>7107802</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4741,19 +4741,19 @@
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Patrik Nygren</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Patrik Nygren</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>125227661</v>
+        <v>125227797</v>
       </c>
       <c r="B41" t="n">
         <v>98331</v>
@@ -4796,10 +4796,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>745280</v>
+        <v>745277</v>
       </c>
       <c r="R41" t="n">
-        <v>7107827</v>
+        <v>7107838</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4859,7 +4859,7 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>125227797</v>
+        <v>125227661</v>
       </c>
       <c r="B42" t="n">
         <v>98331</v>
@@ -4902,10 +4902,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>745277</v>
+        <v>745280</v>
       </c>
       <c r="R42" t="n">
-        <v>7107838</v>
+        <v>7107827</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
